--- a/output/2025-08-09.xlsx
+++ b/output/2025-08-09.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="F14" t="n">
-        <v>9.300000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>287.9</v>
+        <v>310.4</v>
       </c>
       <c r="H14" t="n">
-        <v>85.7</v>
+        <v>85.5</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>53.32</v>
+        <v>35.08</v>
       </c>
       <c r="K14" t="n">
-        <v>37.48</v>
+        <v>108.86</v>
       </c>
       <c r="L14" t="n">
-        <v>65.17</v>
+        <v>114.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:37:03</t>
+          <t>05:36:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="F15" t="n">
-        <v>9.06</v>
+        <v>9.92</v>
       </c>
       <c r="G15" t="n">
-        <v>297.8</v>
+        <v>299.1</v>
       </c>
       <c r="H15" t="n">
-        <v>84.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>-120.12</v>
+        <v>47.23</v>
       </c>
       <c r="K15" t="n">
-        <v>80.73999999999999</v>
+        <v>-44.53</v>
       </c>
       <c r="L15" t="n">
-        <v>144.73</v>
+        <v>64.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:38:48</t>
+          <t>05:38:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="F16" t="n">
-        <v>9.630000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="G16" t="n">
-        <v>280.6</v>
+        <v>289.7</v>
       </c>
       <c r="H16" t="n">
-        <v>89.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>13.98</v>
+        <v>-105.93</v>
       </c>
       <c r="K16" t="n">
-        <v>17.38</v>
+        <v>122.71</v>
       </c>
       <c r="L16" t="n">
-        <v>22.31</v>
+        <v>162.11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:42:08</t>
+          <t>05:43:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="F17" t="n">
-        <v>9.359999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="G17" t="n">
-        <v>288.9</v>
+        <v>300.2</v>
       </c>
       <c r="H17" t="n">
-        <v>89.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="I17" t="n">
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-17.56</v>
+        <v>187.3</v>
       </c>
       <c r="K17" t="n">
-        <v>-104.83</v>
+        <v>-140.85</v>
       </c>
       <c r="L17" t="n">
-        <v>106.29</v>
+        <v>234.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:43:46</t>
+          <t>05:45:14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="F18" t="n">
-        <v>9.210000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="G18" t="n">
-        <v>291.9</v>
+        <v>281.3</v>
       </c>
       <c r="H18" t="n">
-        <v>88.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>72.09</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>184.48</v>
+        <v>29.78</v>
       </c>
       <c r="L18" t="n">
-        <v>198.07</v>
+        <v>103.38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:46:13</t>
+          <t>05:47:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="F19" t="n">
-        <v>8.619999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="G19" t="n">
-        <v>289.7</v>
+        <v>302.7</v>
       </c>
       <c r="H19" t="n">
-        <v>89.59999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>28.65</v>
+        <v>-64.3</v>
       </c>
       <c r="K19" t="n">
-        <v>73.66</v>
+        <v>-48.72</v>
       </c>
       <c r="L19" t="n">
-        <v>79.03</v>
+        <v>80.68000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:51:02</t>
+          <t>05:52:07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.81</v>
+        <v>2.89</v>
       </c>
       <c r="F20" t="n">
-        <v>9.84</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>284.7</v>
+        <v>297</v>
       </c>
       <c r="H20" t="n">
-        <v>89.3</v>
+        <v>85</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-180.23</v>
+        <v>-65.51000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>2.58</v>
+        <v>123.59</v>
       </c>
       <c r="L20" t="n">
-        <v>180.25</v>
+        <v>139.88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:53:10</t>
+          <t>05:53:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="F21" t="n">
-        <v>9.140000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="G21" t="n">
-        <v>289.1</v>
+        <v>292.5</v>
       </c>
       <c r="H21" t="n">
-        <v>84.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>-79.18000000000001</v>
+        <v>225.83</v>
       </c>
       <c r="K21" t="n">
-        <v>26.7</v>
+        <v>-98.56</v>
       </c>
       <c r="L21" t="n">
-        <v>83.56999999999999</v>
+        <v>246.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:55:31</t>
+          <t>05:54:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="F22" t="n">
-        <v>9.09</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>291</v>
+        <v>292.6</v>
       </c>
       <c r="H22" t="n">
-        <v>85.5</v>
+        <v>93.3</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-198.32</v>
+        <v>-287.56</v>
       </c>
       <c r="K22" t="n">
-        <v>-90.81</v>
+        <v>-27</v>
       </c>
       <c r="L22" t="n">
-        <v>218.12</v>
+        <v>288.83</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:00:04</t>
+          <t>06:00:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="F23" t="n">
-        <v>9.19</v>
+        <v>8.81</v>
       </c>
       <c r="G23" t="n">
-        <v>284.3</v>
+        <v>290.5</v>
       </c>
       <c r="H23" t="n">
-        <v>82.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-491.97</v>
+        <v>391.44</v>
       </c>
       <c r="K23" t="n">
-        <v>67.53</v>
+        <v>-272.26</v>
       </c>
       <c r="L23" t="n">
-        <v>496.59</v>
+        <v>476.81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:00:56</t>
+          <t>06:01:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.72</v>
+        <v>2.13</v>
       </c>
       <c r="F24" t="n">
-        <v>9.449999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="G24" t="n">
-        <v>282.5</v>
+        <v>291.5</v>
       </c>
       <c r="H24" t="n">
-        <v>91.8</v>
+        <v>87.7</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-83.51000000000001</v>
+        <v>170.91</v>
       </c>
       <c r="K24" t="n">
-        <v>242.16</v>
+        <v>-138.92</v>
       </c>
       <c r="L24" t="n">
-        <v>256.16</v>
+        <v>220.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:02:39</t>
+          <t>06:03:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="F25" t="n">
-        <v>9.109999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>284.8</v>
+        <v>299.8</v>
       </c>
       <c r="H25" t="n">
-        <v>91.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-376.11</v>
+        <v>-118.31</v>
       </c>
       <c r="K25" t="n">
-        <v>-242.17</v>
+        <v>-173.46</v>
       </c>
       <c r="L25" t="n">
-        <v>447.33</v>
+        <v>209.96</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:07:12</t>
+          <t>06:06:58</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="F26" t="n">
-        <v>9.65</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>274.5</v>
+        <v>298.2</v>
       </c>
       <c r="H26" t="n">
-        <v>93.5</v>
+        <v>88</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>213.72</v>
+        <v>174.25</v>
       </c>
       <c r="K26" t="n">
-        <v>-474.89</v>
+        <v>-222.54</v>
       </c>
       <c r="L26" t="n">
-        <v>520.76</v>
+        <v>282.64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:08:47</t>
+          <t>06:08:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.24</v>
+        <v>1.6</v>
       </c>
       <c r="F27" t="n">
-        <v>8.83</v>
+        <v>9.08</v>
       </c>
       <c r="G27" t="n">
-        <v>292.6</v>
+        <v>298.1</v>
       </c>
       <c r="H27" t="n">
-        <v>88</v>
+        <v>90.5</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>141.48</v>
+        <v>405.86</v>
       </c>
       <c r="K27" t="n">
-        <v>475.45</v>
+        <v>203.35</v>
       </c>
       <c r="L27" t="n">
-        <v>496.06</v>
+        <v>453.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:10:14</t>
+          <t>06:09:53</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.51</v>
+        <v>2.79</v>
       </c>
       <c r="F28" t="n">
-        <v>9.460000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>292.8</v>
+        <v>296.6</v>
       </c>
       <c r="H28" t="n">
-        <v>89.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-207.91</v>
+        <v>-160.57</v>
       </c>
       <c r="K28" t="n">
-        <v>705.63</v>
+        <v>713.75</v>
       </c>
       <c r="L28" t="n">
-        <v>735.63</v>
+        <v>731.59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:22:30</t>
+          <t>06:19:58</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.96</v>
+        <v>2.25</v>
       </c>
       <c r="F29" t="n">
-        <v>8.98</v>
+        <v>8.48</v>
       </c>
       <c r="G29" t="n">
-        <v>282.8</v>
+        <v>284.7</v>
       </c>
       <c r="H29" t="n">
-        <v>80.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>71.06999999999999</v>
+        <v>17.45</v>
       </c>
       <c r="K29" t="n">
-        <v>-68.40000000000001</v>
+        <v>90.64</v>
       </c>
       <c r="L29" t="n">
-        <v>98.63</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:24:09</t>
+          <t>06:21:50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="F30" t="n">
-        <v>9.52</v>
+        <v>9.25</v>
       </c>
       <c r="G30" t="n">
-        <v>287.3</v>
+        <v>284.5</v>
       </c>
       <c r="H30" t="n">
-        <v>93.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>82.66</v>
+        <v>61.12</v>
       </c>
       <c r="K30" t="n">
-        <v>-44.29</v>
+        <v>-71.11</v>
       </c>
       <c r="L30" t="n">
-        <v>93.78</v>
+        <v>93.77</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:25:20</t>
+          <t>06:23:39</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.78</v>
+        <v>2.61</v>
       </c>
       <c r="F31" t="n">
-        <v>8.93</v>
+        <v>9.32</v>
       </c>
       <c r="G31" t="n">
-        <v>281.6</v>
+        <v>298.2</v>
       </c>
       <c r="H31" t="n">
-        <v>90.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>74.94</v>
+        <v>-101.35</v>
       </c>
       <c r="K31" t="n">
-        <v>143.16</v>
+        <v>-180.31</v>
       </c>
       <c r="L31" t="n">
-        <v>161.59</v>
+        <v>206.84</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:30:45</t>
+          <t>06:27:52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.52</v>
+        <v>2.79</v>
       </c>
       <c r="F32" t="n">
-        <v>9.27</v>
+        <v>9.34</v>
       </c>
       <c r="G32" t="n">
-        <v>283.6</v>
+        <v>300.7</v>
       </c>
       <c r="H32" t="n">
-        <v>91</v>
+        <v>82.7</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-20.68</v>
+        <v>-48.14</v>
       </c>
       <c r="K32" t="n">
-        <v>-46.89</v>
+        <v>-128.29</v>
       </c>
       <c r="L32" t="n">
-        <v>51.25</v>
+        <v>137.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:32:16</t>
+          <t>06:28:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="F33" t="n">
-        <v>9.69</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>303.2</v>
+        <v>298.4</v>
       </c>
       <c r="H33" t="n">
-        <v>84.09999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-15.5</v>
+        <v>-178.18</v>
       </c>
       <c r="K33" t="n">
-        <v>254.14</v>
+        <v>169.17</v>
       </c>
       <c r="L33" t="n">
-        <v>254.61</v>
+        <v>245.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:33:45</t>
+          <t>06:31:11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.86</v>
+        <v>1.79</v>
       </c>
       <c r="F34" t="n">
-        <v>9.42</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>288.7</v>
+        <v>286.9</v>
       </c>
       <c r="H34" t="n">
-        <v>87.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>216.56</v>
+        <v>-73.02</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.84</v>
+        <v>106.57</v>
       </c>
       <c r="L34" t="n">
-        <v>216.6</v>
+        <v>129.18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:39:09</t>
+          <t>06:35:14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="F35" t="n">
-        <v>9.380000000000001</v>
+        <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>291.3</v>
+        <v>307.7</v>
       </c>
       <c r="H35" t="n">
-        <v>93.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>86.22</v>
+        <v>-382.39</v>
       </c>
       <c r="K35" t="n">
-        <v>-33.45</v>
+        <v>-173.89</v>
       </c>
       <c r="L35" t="n">
-        <v>92.48999999999999</v>
+        <v>420.07</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:40:45</t>
+          <t>06:36:45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="F36" t="n">
-        <v>9.82</v>
+        <v>9.17</v>
       </c>
       <c r="G36" t="n">
-        <v>296.2</v>
+        <v>301.3</v>
       </c>
       <c r="H36" t="n">
-        <v>92.5</v>
+        <v>89.7</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>57.04</v>
+        <v>-70.83</v>
       </c>
       <c r="K36" t="n">
-        <v>-85.5</v>
+        <v>386.35</v>
       </c>
       <c r="L36" t="n">
-        <v>102.78</v>
+        <v>392.79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:42:53</t>
+          <t>06:37:19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.71</v>
+        <v>2.12</v>
       </c>
       <c r="F37" t="n">
-        <v>9.16</v>
+        <v>10.03</v>
       </c>
       <c r="G37" t="n">
-        <v>288.9</v>
+        <v>281.7</v>
       </c>
       <c r="H37" t="n">
-        <v>91.7</v>
+        <v>91.8</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-559.3099999999999</v>
+        <v>78.3</v>
       </c>
       <c r="K37" t="n">
-        <v>-103.39</v>
+        <v>102.67</v>
       </c>
       <c r="L37" t="n">
-        <v>568.79</v>
+        <v>129.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:47:13</t>
+          <t>06:42:11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="F38" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>291.1</v>
+        <v>295</v>
       </c>
       <c r="H38" t="n">
-        <v>89.5</v>
+        <v>89.8</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-196.85</v>
+        <v>219.66</v>
       </c>
       <c r="K38" t="n">
-        <v>262.42</v>
+        <v>10.85</v>
       </c>
       <c r="L38" t="n">
-        <v>328.05</v>
+        <v>219.92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:48:15</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.47</v>
+        <v>1.88</v>
       </c>
       <c r="F39" t="n">
-        <v>9.289999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>289.3</v>
+        <v>286.6</v>
       </c>
       <c r="H39" t="n">
-        <v>94.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-691.4400000000001</v>
+        <v>-280.85</v>
       </c>
       <c r="K39" t="n">
-        <v>-495.49</v>
+        <v>102.51</v>
       </c>
       <c r="L39" t="n">
-        <v>850.65</v>
+        <v>298.98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:50:04</t>
+          <t>06:46:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="F40" t="n">
         <v>9.02</v>
       </c>
       <c r="G40" t="n">
-        <v>286.7</v>
+        <v>303</v>
       </c>
       <c r="H40" t="n">
-        <v>89</v>
+        <v>86.5</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>433.84</v>
+        <v>-119.06</v>
       </c>
       <c r="K40" t="n">
-        <v>31.19</v>
+        <v>-19.73</v>
       </c>
       <c r="L40" t="n">
-        <v>434.96</v>
+        <v>120.68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:53:50</t>
+          <t>06:52:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.93</v>
+        <v>2.64</v>
       </c>
       <c r="F41" t="n">
-        <v>8.98</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>286.1</v>
+        <v>277.3</v>
       </c>
       <c r="H41" t="n">
-        <v>90.5</v>
+        <v>99.2</v>
       </c>
       <c r="I41" t="n">
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-355.01</v>
+        <v>745.42</v>
       </c>
       <c r="K41" t="n">
-        <v>78.37</v>
+        <v>76.14</v>
       </c>
       <c r="L41" t="n">
-        <v>363.55</v>
+        <v>749.29</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:55:40</t>
+          <t>06:52:59</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.57</v>
+        <v>1.89</v>
       </c>
       <c r="F42" t="n">
-        <v>9.83</v>
+        <v>9.01</v>
       </c>
       <c r="G42" t="n">
-        <v>296.2</v>
+        <v>296.9</v>
       </c>
       <c r="H42" t="n">
-        <v>86.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-437.72</v>
+        <v>-128.04</v>
       </c>
       <c r="K42" t="n">
-        <v>-454.98</v>
+        <v>-227.95</v>
       </c>
       <c r="L42" t="n">
-        <v>631.35</v>
+        <v>261.45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:57:43</t>
+          <t>06:55:03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="F43" t="n">
-        <v>9.550000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="G43" t="n">
-        <v>274.7</v>
+        <v>295.6</v>
       </c>
       <c r="H43" t="n">
-        <v>89.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I43" t="n">
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-89.38</v>
+        <v>-363.61</v>
       </c>
       <c r="K43" t="n">
-        <v>44.86</v>
+        <v>390.33</v>
       </c>
       <c r="L43" t="n">
-        <v>100</v>
+        <v>533.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:09:10</t>
+          <t>07:05:04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="F44" t="n">
-        <v>9.74</v>
+        <v>9.07</v>
       </c>
       <c r="G44" t="n">
-        <v>282.1</v>
+        <v>273.7</v>
       </c>
       <c r="H44" t="n">
-        <v>86.2</v>
+        <v>92.5</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.8</v>
+        <v>217.37</v>
       </c>
       <c r="K44" t="n">
-        <v>50.62</v>
+        <v>-2.64</v>
       </c>
       <c r="L44" t="n">
-        <v>50.76</v>
+        <v>217.38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:10:47</t>
+          <t>07:05:55</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.43</v>
+        <v>1.8</v>
       </c>
       <c r="F45" t="n">
-        <v>9.24</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>274.5</v>
+        <v>291.2</v>
       </c>
       <c r="H45" t="n">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I45" t="n">
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>30.72</v>
+        <v>49.97</v>
       </c>
       <c r="K45" t="n">
-        <v>-46.66</v>
+        <v>-62.4</v>
       </c>
       <c r="L45" t="n">
-        <v>55.87</v>
+        <v>79.94</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:11:39</t>
+          <t>07:07:09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="F46" t="n">
-        <v>9.31</v>
+        <v>9.18</v>
       </c>
       <c r="G46" t="n">
-        <v>278.7</v>
+        <v>286.6</v>
       </c>
       <c r="H46" t="n">
-        <v>93</v>
+        <v>88.3</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-77.03</v>
+        <v>-205.57</v>
       </c>
       <c r="K46" t="n">
-        <v>-18.65</v>
+        <v>126.39</v>
       </c>
       <c r="L46" t="n">
-        <v>79.26000000000001</v>
+        <v>241.32</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:15:57</t>
+          <t>07:11:39</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="F47" t="n">
-        <v>9.76</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>303.4</v>
+        <v>277.7</v>
       </c>
       <c r="H47" t="n">
-        <v>86.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-123.39</v>
+        <v>-188.19</v>
       </c>
       <c r="K47" t="n">
-        <v>-76.78</v>
+        <v>-220.04</v>
       </c>
       <c r="L47" t="n">
-        <v>145.33</v>
+        <v>289.54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:17:47</t>
+          <t>07:13:31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.18</v>
+        <v>2.91</v>
       </c>
       <c r="F48" t="n">
-        <v>9.359999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>301.1</v>
+        <v>299.7</v>
       </c>
       <c r="H48" t="n">
-        <v>86</v>
+        <v>89.3</v>
       </c>
       <c r="I48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.77</v>
+        <v>-60.99</v>
       </c>
       <c r="K48" t="n">
-        <v>-44.43</v>
+        <v>37.52</v>
       </c>
       <c r="L48" t="n">
-        <v>44.47</v>
+        <v>71.61</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:18:57</t>
+          <t>07:15:08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.81</v>
+        <v>3.17</v>
       </c>
       <c r="F49" t="n">
-        <v>9.289999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="G49" t="n">
-        <v>276.3</v>
+        <v>293</v>
       </c>
       <c r="H49" t="n">
-        <v>89.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-83.48999999999999</v>
+        <v>71.95</v>
       </c>
       <c r="K49" t="n">
-        <v>22.97</v>
+        <v>-159.66</v>
       </c>
       <c r="L49" t="n">
-        <v>86.59999999999999</v>
+        <v>175.12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:23:12</t>
+          <t>07:19:50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.94</v>
+        <v>2.22</v>
       </c>
       <c r="F50" t="n">
-        <v>9.35</v>
+        <v>9.83</v>
       </c>
       <c r="G50" t="n">
-        <v>298.6</v>
+        <v>297.5</v>
       </c>
       <c r="H50" t="n">
-        <v>87.3</v>
+        <v>93</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-184.84</v>
+        <v>100.75</v>
       </c>
       <c r="K50" t="n">
-        <v>-32.6</v>
+        <v>116.81</v>
       </c>
       <c r="L50" t="n">
-        <v>187.69</v>
+        <v>154.26</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:25:08</t>
+          <t>07:21:36</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="F51" t="n">
-        <v>9.31</v>
+        <v>9.75</v>
       </c>
       <c r="G51" t="n">
-        <v>287.9</v>
+        <v>290</v>
       </c>
       <c r="H51" t="n">
-        <v>96</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-136.07</v>
+        <v>17.31</v>
       </c>
       <c r="K51" t="n">
-        <v>5.11</v>
+        <v>413.93</v>
       </c>
       <c r="L51" t="n">
-        <v>136.16</v>
+        <v>414.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:27:44</t>
+          <t>07:22:52</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="F52" t="n">
-        <v>9.5</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>284.8</v>
+        <v>281.7</v>
       </c>
       <c r="H52" t="n">
-        <v>95.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>100.57</v>
+        <v>-80.41</v>
       </c>
       <c r="K52" t="n">
-        <v>379.3</v>
+        <v>-111.37</v>
       </c>
       <c r="L52" t="n">
-        <v>392.41</v>
+        <v>137.36</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:32:13</t>
+          <t>07:27:49</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.16</v>
+        <v>2.57</v>
       </c>
       <c r="F53" t="n">
-        <v>9.17</v>
+        <v>9.52</v>
       </c>
       <c r="G53" t="n">
-        <v>291.7</v>
+        <v>290.8</v>
       </c>
       <c r="H53" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-364.25</v>
+        <v>5.74</v>
       </c>
       <c r="K53" t="n">
-        <v>-351.02</v>
+        <v>-244.13</v>
       </c>
       <c r="L53" t="n">
-        <v>505.86</v>
+        <v>244.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:33:24</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="F54" t="n">
-        <v>8.93</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>284.6</v>
+        <v>276.5</v>
       </c>
       <c r="H54" t="n">
-        <v>86.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-159.19</v>
+        <v>214.74</v>
       </c>
       <c r="K54" t="n">
-        <v>-616.14</v>
+        <v>-186.52</v>
       </c>
       <c r="L54" t="n">
-        <v>636.38</v>
+        <v>284.44</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:35:41</t>
+          <t>07:31:50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="F55" t="n">
-        <v>8.75</v>
+        <v>9.74</v>
       </c>
       <c r="G55" t="n">
-        <v>296.8</v>
+        <v>294.7</v>
       </c>
       <c r="H55" t="n">
-        <v>84.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>140.4</v>
+        <v>-457.76</v>
       </c>
       <c r="K55" t="n">
-        <v>71.89</v>
+        <v>152.32</v>
       </c>
       <c r="L55" t="n">
-        <v>157.73</v>
+        <v>482.43</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:40:27</t>
+          <t>07:36:33</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="F56" t="n">
-        <v>9.869999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>266.3</v>
+        <v>296.6</v>
       </c>
       <c r="H56" t="n">
-        <v>95.8</v>
+        <v>88.2</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>213.57</v>
+        <v>186.65</v>
       </c>
       <c r="K56" t="n">
-        <v>164.62</v>
+        <v>740.48</v>
       </c>
       <c r="L56" t="n">
-        <v>269.65</v>
+        <v>763.65</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:41:44</t>
+          <t>07:38:29</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.86</v>
+        <v>3.14</v>
       </c>
       <c r="F57" t="n">
-        <v>9.17</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>289.2</v>
+        <v>298.5</v>
       </c>
       <c r="H57" t="n">
-        <v>90.59999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>181.07</v>
+        <v>498.35</v>
       </c>
       <c r="K57" t="n">
-        <v>-586.3</v>
+        <v>192.8</v>
       </c>
       <c r="L57" t="n">
-        <v>613.62</v>
+        <v>534.35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:43:52</t>
+          <t>07:39:40</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.14</v>
+        <v>2.43</v>
       </c>
       <c r="F58" t="n">
-        <v>9.48</v>
+        <v>9.25</v>
       </c>
       <c r="G58" t="n">
-        <v>285.6</v>
+        <v>286.2</v>
       </c>
       <c r="H58" t="n">
-        <v>89.3</v>
+        <v>91.7</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-300.52</v>
+        <v>-303.29</v>
       </c>
       <c r="K58" t="n">
-        <v>283.18</v>
+        <v>-492.14</v>
       </c>
       <c r="L58" t="n">
-        <v>412.91</v>
+        <v>578.09</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:56:08</t>
+          <t>07:46:58</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="F59" t="n">
-        <v>9.02</v>
+        <v>9.65</v>
       </c>
       <c r="G59" t="n">
-        <v>296.6</v>
+        <v>292.7</v>
       </c>
       <c r="H59" t="n">
-        <v>94.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-48.22</v>
+        <v>-80.31999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-63.38</v>
+        <v>-21.68</v>
       </c>
       <c r="L59" t="n">
-        <v>79.63</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:57:39</t>
+          <t>07:47:52</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="F60" t="n">
-        <v>8.66</v>
+        <v>8.99</v>
       </c>
       <c r="G60" t="n">
-        <v>294.6</v>
+        <v>286.6</v>
       </c>
       <c r="H60" t="n">
-        <v>89.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>84.06999999999999</v>
+        <v>-25.66</v>
       </c>
       <c r="K60" t="n">
-        <v>-72.5</v>
+        <v>206.97</v>
       </c>
       <c r="L60" t="n">
-        <v>111.01</v>
+        <v>208.56</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:58:57</t>
+          <t>07:50:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.24</v>
+        <v>2.73</v>
       </c>
       <c r="F61" t="n">
-        <v>9.19</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>283.3</v>
+        <v>290.5</v>
       </c>
       <c r="H61" t="n">
-        <v>90.5</v>
+        <v>85.7</v>
       </c>
       <c r="I61" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-2.53</v>
+        <v>127.54</v>
       </c>
       <c r="K61" t="n">
-        <v>2.83</v>
+        <v>5.1</v>
       </c>
       <c r="L61" t="n">
-        <v>3.8</v>
+        <v>127.64</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:03:50</t>
+          <t>07:54:06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="F62" t="n">
-        <v>8.59</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>276.1</v>
+        <v>302.1</v>
       </c>
       <c r="H62" t="n">
-        <v>91</v>
+        <v>89.7</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>88.12</v>
+        <v>96.64</v>
       </c>
       <c r="K62" t="n">
-        <v>-10.03</v>
+        <v>-2.91</v>
       </c>
       <c r="L62" t="n">
-        <v>88.69</v>
+        <v>96.68000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:04:42</t>
+          <t>07:56:36</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.09</v>
+        <v>2.69</v>
       </c>
       <c r="F63" t="n">
-        <v>8.960000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="G63" t="n">
-        <v>288</v>
+        <v>287.4</v>
       </c>
       <c r="H63" t="n">
-        <v>83.8</v>
+        <v>86</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>66.5</v>
+        <v>-208.47</v>
       </c>
       <c r="K63" t="n">
-        <v>-75.08</v>
+        <v>-2.83</v>
       </c>
       <c r="L63" t="n">
-        <v>100.29</v>
+        <v>208.49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:05:44</t>
+          <t>07:57:23</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="F64" t="n">
-        <v>9.140000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="G64" t="n">
-        <v>294.3</v>
+        <v>292.7</v>
       </c>
       <c r="H64" t="n">
-        <v>92.5</v>
+        <v>93</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>62.43</v>
+        <v>263.46</v>
       </c>
       <c r="K64" t="n">
-        <v>-58.41</v>
+        <v>-109.38</v>
       </c>
       <c r="L64" t="n">
-        <v>85.48999999999999</v>
+        <v>285.26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:09:28</t>
+          <t>08:01:29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="F65" t="n">
-        <v>9.210000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="G65" t="n">
-        <v>294.8</v>
+        <v>298.8</v>
       </c>
       <c r="H65" t="n">
-        <v>91.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-77.78</v>
+        <v>35.33</v>
       </c>
       <c r="K65" t="n">
-        <v>33.38</v>
+        <v>-40.89</v>
       </c>
       <c r="L65" t="n">
-        <v>84.64</v>
+        <v>54.04</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:11:01</t>
+          <t>08:03:31</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.77</v>
+        <v>2.76</v>
       </c>
       <c r="F66" t="n">
-        <v>9.56</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>296.8</v>
+        <v>292.3</v>
       </c>
       <c r="H66" t="n">
-        <v>84.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-153.27</v>
+        <v>-373.52</v>
       </c>
       <c r="K66" t="n">
-        <v>11.09</v>
+        <v>-163.89</v>
       </c>
       <c r="L66" t="n">
-        <v>153.67</v>
+        <v>407.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:13:13</t>
+          <t>08:04:47</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.54</v>
+        <v>2.84</v>
       </c>
       <c r="F67" t="n">
-        <v>9.35</v>
+        <v>9.57</v>
       </c>
       <c r="G67" t="n">
-        <v>287.9</v>
+        <v>293.8</v>
       </c>
       <c r="H67" t="n">
-        <v>88.5</v>
+        <v>90.3</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-357.22</v>
+        <v>-240.08</v>
       </c>
       <c r="K67" t="n">
-        <v>408.27</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>542.49</v>
+        <v>258.28</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:16:26</t>
+          <t>08:09:18</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="F68" t="n">
-        <v>8.880000000000001</v>
+        <v>10.27</v>
       </c>
       <c r="G68" t="n">
-        <v>274</v>
+        <v>287.7</v>
       </c>
       <c r="H68" t="n">
-        <v>86.3</v>
+        <v>89</v>
       </c>
       <c r="I68" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>79.31999999999999</v>
+        <v>-110.08</v>
       </c>
       <c r="K68" t="n">
-        <v>60.89</v>
+        <v>-131.48</v>
       </c>
       <c r="L68" t="n">
-        <v>100</v>
+        <v>171.48</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:17:28</t>
+          <t>08:10:24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="F69" t="n">
-        <v>9.6</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>292.4</v>
+        <v>286.3</v>
       </c>
       <c r="H69" t="n">
-        <v>94.8</v>
+        <v>92.3</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>610.13</v>
+        <v>-329.26</v>
       </c>
       <c r="K69" t="n">
-        <v>-271.57</v>
+        <v>-196.87</v>
       </c>
       <c r="L69" t="n">
-        <v>667.84</v>
+        <v>383.63</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:18:44</t>
+          <t>08:11:24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2980,31 +2980,31 @@
         <v>2.67</v>
       </c>
       <c r="F70" t="n">
-        <v>8.91</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>294.9</v>
+        <v>294.7</v>
       </c>
       <c r="H70" t="n">
-        <v>90.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-69.69</v>
+        <v>-35.72</v>
       </c>
       <c r="K70" t="n">
-        <v>-158.08</v>
+        <v>-41.64</v>
       </c>
       <c r="L70" t="n">
-        <v>172.76</v>
+        <v>54.86</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:23:56</t>
+          <t>08:15:57</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="F71" t="n">
-        <v>9.5</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>308</v>
+        <v>292.9</v>
       </c>
       <c r="H71" t="n">
-        <v>87.2</v>
+        <v>87.5</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>141.47</v>
+        <v>335.11</v>
       </c>
       <c r="K71" t="n">
-        <v>304.31</v>
+        <v>147.83</v>
       </c>
       <c r="L71" t="n">
-        <v>335.59</v>
+        <v>366.27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:25:34</t>
+          <t>08:16:34</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.76</v>
+        <v>3.03</v>
       </c>
       <c r="F72" t="n">
-        <v>9.380000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="G72" t="n">
-        <v>295.1</v>
+        <v>287.7</v>
       </c>
       <c r="H72" t="n">
-        <v>95.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>237.86</v>
+        <v>-317.09</v>
       </c>
       <c r="K72" t="n">
-        <v>452.18</v>
+        <v>561.41</v>
       </c>
       <c r="L72" t="n">
-        <v>510.93</v>
+        <v>644.77</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:27:24</t>
+          <t>08:18:03</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="F73" t="n">
-        <v>9.199999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="G73" t="n">
-        <v>280.5</v>
+        <v>287.5</v>
       </c>
       <c r="H73" t="n">
-        <v>87.09999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>238.44</v>
+        <v>15.4</v>
       </c>
       <c r="K73" t="n">
-        <v>432.39</v>
+        <v>622.96</v>
       </c>
       <c r="L73" t="n">
-        <v>493.77</v>
+        <v>623.15</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:38:15</t>
+          <t>08:28:36</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="F74" t="n">
-        <v>9.15</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>283.8</v>
+        <v>294.3</v>
       </c>
       <c r="H74" t="n">
-        <v>86.5</v>
+        <v>89.2</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-68.73</v>
+        <v>-53.09</v>
       </c>
       <c r="K74" t="n">
-        <v>-30.99</v>
+        <v>-72.14</v>
       </c>
       <c r="L74" t="n">
-        <v>75.40000000000001</v>
+        <v>89.56999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:39:55</t>
+          <t>08:30:43</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="F75" t="n">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>296.6</v>
+        <v>305.4</v>
       </c>
       <c r="H75" t="n">
-        <v>92.3</v>
+        <v>88.5</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>59.6</v>
+        <v>-52.89</v>
       </c>
       <c r="K75" t="n">
-        <v>-86.05</v>
+        <v>75.53</v>
       </c>
       <c r="L75" t="n">
-        <v>104.67</v>
+        <v>92.20999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:42:27</t>
+          <t>08:31:38</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.63</v>
+        <v>3.29</v>
       </c>
       <c r="F76" t="n">
-        <v>9.539999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>288</v>
+        <v>297.7</v>
       </c>
       <c r="H76" t="n">
-        <v>86.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.63</v>
+        <v>-54.4</v>
       </c>
       <c r="K76" t="n">
-        <v>61.48</v>
+        <v>30.21</v>
       </c>
       <c r="L76" t="n">
-        <v>62.76</v>
+        <v>62.23</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:47:28</t>
+          <t>08:36:51</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.36</v>
+        <v>2.85</v>
       </c>
       <c r="F77" t="n">
-        <v>8.98</v>
+        <v>8.77</v>
       </c>
       <c r="G77" t="n">
-        <v>285.3</v>
+        <v>278.5</v>
       </c>
       <c r="H77" t="n">
-        <v>87.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>138.6</v>
+        <v>69.95</v>
       </c>
       <c r="K77" t="n">
-        <v>-65.33</v>
+        <v>189.55</v>
       </c>
       <c r="L77" t="n">
-        <v>153.22</v>
+        <v>202.04</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:48:35</t>
+          <t>08:37:38</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="F78" t="n">
-        <v>9.529999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="G78" t="n">
-        <v>292.7</v>
+        <v>287.4</v>
       </c>
       <c r="H78" t="n">
-        <v>91.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="I78" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>-33.55</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-58.4</v>
+        <v>-10.37</v>
       </c>
       <c r="L78" t="n">
-        <v>67.34999999999999</v>
+        <v>77.76000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:50:31</t>
+          <t>08:39:26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.72</v>
+        <v>2.28</v>
       </c>
       <c r="F79" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="G79" t="n">
-        <v>294.2</v>
+        <v>287.2</v>
       </c>
       <c r="H79" t="n">
-        <v>87.7</v>
+        <v>90</v>
       </c>
       <c r="I79" t="n">
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>151.23</v>
+        <v>49.11</v>
       </c>
       <c r="K79" t="n">
-        <v>-76.98999999999999</v>
+        <v>227.4</v>
       </c>
       <c r="L79" t="n">
-        <v>169.7</v>
+        <v>232.64</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:55:48</t>
+          <t>08:45:28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="F80" t="n">
-        <v>9.380000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>302.2</v>
+        <v>289</v>
       </c>
       <c r="H80" t="n">
-        <v>95.3</v>
+        <v>88.5</v>
       </c>
       <c r="I80" t="n">
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>49.18</v>
+        <v>72.81</v>
       </c>
       <c r="K80" t="n">
-        <v>-57.25</v>
+        <v>-145.15</v>
       </c>
       <c r="L80" t="n">
-        <v>75.47</v>
+        <v>162.38</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:57:30</t>
+          <t>08:47:16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="F81" t="n">
-        <v>8.789999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G81" t="n">
         <v>293.9</v>
       </c>
       <c r="H81" t="n">
-        <v>98.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-121.54</v>
+        <v>114.03</v>
       </c>
       <c r="K81" t="n">
-        <v>-152.41</v>
+        <v>214.39</v>
       </c>
       <c r="L81" t="n">
-        <v>194.94</v>
+        <v>242.83</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:58:51</t>
+          <t>08:49:54</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.57</v>
+        <v>3.05</v>
       </c>
       <c r="F82" t="n">
-        <v>8.869999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>277.6</v>
+        <v>293.6</v>
       </c>
       <c r="H82" t="n">
-        <v>91.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-95.14</v>
+        <v>-75.48999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>287.97</v>
+        <v>118.21</v>
       </c>
       <c r="L82" t="n">
-        <v>303.28</v>
+        <v>140.26</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:02:22</t>
+          <t>08:54:19</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="F83" t="n">
-        <v>9.77</v>
+        <v>10.17</v>
       </c>
       <c r="G83" t="n">
-        <v>284.8</v>
+        <v>281.8</v>
       </c>
       <c r="H83" t="n">
-        <v>91.8</v>
+        <v>92.2</v>
       </c>
       <c r="I83" t="n">
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>26.96</v>
+        <v>544.65</v>
       </c>
       <c r="K83" t="n">
-        <v>422.55</v>
+        <v>-31.69</v>
       </c>
       <c r="L83" t="n">
-        <v>423.41</v>
+        <v>545.5700000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:03:25</t>
+          <t>08:55:45</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="F84" t="n">
-        <v>8.57</v>
+        <v>9.56</v>
       </c>
       <c r="G84" t="n">
-        <v>299.6</v>
+        <v>287.2</v>
       </c>
       <c r="H84" t="n">
-        <v>88.2</v>
+        <v>89.8</v>
       </c>
       <c r="I84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-54.06</v>
+        <v>77.61</v>
       </c>
       <c r="K84" t="n">
-        <v>-87.77</v>
+        <v>263.62</v>
       </c>
       <c r="L84" t="n">
-        <v>103.08</v>
+        <v>274.8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:05:29</t>
+          <t>08:57:05</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="F85" t="n">
-        <v>9.85</v>
+        <v>8.85</v>
       </c>
       <c r="G85" t="n">
-        <v>295.4</v>
+        <v>286.7</v>
       </c>
       <c r="H85" t="n">
-        <v>93.59999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-501.83</v>
+        <v>-108.1</v>
       </c>
       <c r="K85" t="n">
-        <v>-114.57</v>
+        <v>275.46</v>
       </c>
       <c r="L85" t="n">
-        <v>514.74</v>
+        <v>295.91</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:09:29</t>
+          <t>09:02:51</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="F86" t="n">
-        <v>9.210000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="G86" t="n">
-        <v>295.1</v>
+        <v>271.1</v>
       </c>
       <c r="H86" t="n">
-        <v>95.3</v>
+        <v>87</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>186.95</v>
+        <v>159.72</v>
       </c>
       <c r="K86" t="n">
-        <v>548.4400000000001</v>
+        <v>-63.63</v>
       </c>
       <c r="L86" t="n">
-        <v>579.4299999999999</v>
+        <v>171.93</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:10:25</t>
+          <t>09:03:47</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.91</v>
+        <v>2.41</v>
       </c>
       <c r="F87" t="n">
-        <v>9</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G87" t="n">
         <v>290.1</v>
       </c>
       <c r="H87" t="n">
-        <v>81.7</v>
+        <v>90.5</v>
       </c>
       <c r="I87" t="n">
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-184.83</v>
+        <v>-231.61</v>
       </c>
       <c r="K87" t="n">
-        <v>269.58</v>
+        <v>742.7</v>
       </c>
       <c r="L87" t="n">
-        <v>326.86</v>
+        <v>777.98</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:13:19</t>
+          <t>09:05:37</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="F88" t="n">
-        <v>9.9</v>
+        <v>9.91</v>
       </c>
       <c r="G88" t="n">
-        <v>289.1</v>
+        <v>299.7</v>
       </c>
       <c r="H88" t="n">
-        <v>89.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-452.72</v>
+        <v>-503.02</v>
       </c>
       <c r="K88" t="n">
-        <v>-299.08</v>
+        <v>149.55</v>
       </c>
       <c r="L88" t="n">
-        <v>542.59</v>
+        <v>524.78</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-09.xlsx
+++ b/output/2025-08-09.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>35.08</v>
+        <v>33.6</v>
       </c>
       <c r="K14" t="n">
-        <v>108.86</v>
+        <v>104.26</v>
       </c>
       <c r="L14" t="n">
-        <v>114.37</v>
+        <v>109.54</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>47.23</v>
+        <v>60.24</v>
       </c>
       <c r="K15" t="n">
-        <v>-44.53</v>
+        <v>-56.81</v>
       </c>
       <c r="L15" t="n">
-        <v>64.91</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-105.93</v>
+        <v>-94.06999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>122.71</v>
+        <v>108.97</v>
       </c>
       <c r="L16" t="n">
-        <v>162.11</v>
+        <v>143.96</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>187.3</v>
+        <v>192.52</v>
       </c>
       <c r="K17" t="n">
-        <v>-140.85</v>
+        <v>-144.77</v>
       </c>
       <c r="L17" t="n">
-        <v>234.35</v>
+        <v>240.88</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>98.98999999999999</v>
+        <v>117.42</v>
       </c>
       <c r="K18" t="n">
-        <v>29.78</v>
+        <v>35.33</v>
       </c>
       <c r="L18" t="n">
-        <v>103.38</v>
+        <v>122.62</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-64.3</v>
+        <v>-89.79000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-48.72</v>
+        <v>-68.04000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>80.68000000000001</v>
+        <v>112.66</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-65.51000000000001</v>
+        <v>-105.48</v>
       </c>
       <c r="K20" t="n">
-        <v>123.59</v>
+        <v>198.97</v>
       </c>
       <c r="L20" t="n">
-        <v>139.88</v>
+        <v>225.2</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>225.83</v>
+        <v>259.26</v>
       </c>
       <c r="K21" t="n">
-        <v>-98.56</v>
+        <v>-113.15</v>
       </c>
       <c r="L21" t="n">
-        <v>246.4</v>
+        <v>282.87</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-287.56</v>
+        <v>-327.48</v>
       </c>
       <c r="K22" t="n">
-        <v>-27</v>
+        <v>-30.75</v>
       </c>
       <c r="L22" t="n">
-        <v>288.83</v>
+        <v>328.92</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>391.44</v>
+        <v>460.43</v>
       </c>
       <c r="K23" t="n">
-        <v>-272.26</v>
+        <v>-320.25</v>
       </c>
       <c r="L23" t="n">
-        <v>476.81</v>
+        <v>560.86</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>170.91</v>
+        <v>221.45</v>
       </c>
       <c r="K24" t="n">
-        <v>-138.92</v>
+        <v>-179.99</v>
       </c>
       <c r="L24" t="n">
-        <v>220.25</v>
+        <v>285.37</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-118.31</v>
+        <v>-165.57</v>
       </c>
       <c r="K25" t="n">
-        <v>-173.46</v>
+        <v>-242.75</v>
       </c>
       <c r="L25" t="n">
-        <v>209.96</v>
+        <v>293.84</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>174.25</v>
+        <v>286.54</v>
       </c>
       <c r="K26" t="n">
-        <v>-222.54</v>
+        <v>-365.94</v>
       </c>
       <c r="L26" t="n">
-        <v>282.64</v>
+        <v>464.78</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>405.86</v>
+        <v>509.27</v>
       </c>
       <c r="K27" t="n">
-        <v>203.35</v>
+        <v>255.16</v>
       </c>
       <c r="L27" t="n">
-        <v>453.95</v>
+        <v>569.62</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-160.57</v>
+        <v>-201.27</v>
       </c>
       <c r="K28" t="n">
-        <v>713.75</v>
+        <v>894.63</v>
       </c>
       <c r="L28" t="n">
-        <v>731.59</v>
+        <v>916.99</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>17.45</v>
+        <v>18.32</v>
       </c>
       <c r="K29" t="n">
-        <v>90.64</v>
+        <v>95.19</v>
       </c>
       <c r="L29" t="n">
-        <v>92.31</v>
+        <v>96.93000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>61.12</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-71.11</v>
+        <v>-75.42</v>
       </c>
       <c r="L30" t="n">
-        <v>93.77</v>
+        <v>99.45</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-101.35</v>
+        <v>-89.64</v>
       </c>
       <c r="K31" t="n">
-        <v>-180.31</v>
+        <v>-159.46</v>
       </c>
       <c r="L31" t="n">
-        <v>206.84</v>
+        <v>182.93</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-48.14</v>
+        <v>-61.73</v>
       </c>
       <c r="K32" t="n">
-        <v>-128.29</v>
+        <v>-164.53</v>
       </c>
       <c r="L32" t="n">
-        <v>137.03</v>
+        <v>175.73</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-178.18</v>
+        <v>-170.97</v>
       </c>
       <c r="K33" t="n">
-        <v>169.17</v>
+        <v>162.33</v>
       </c>
       <c r="L33" t="n">
-        <v>245.7</v>
+        <v>235.76</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-73.02</v>
+        <v>-77.56</v>
       </c>
       <c r="K34" t="n">
-        <v>106.57</v>
+        <v>113.2</v>
       </c>
       <c r="L34" t="n">
-        <v>129.18</v>
+        <v>137.22</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-382.39</v>
+        <v>-395.59</v>
       </c>
       <c r="K35" t="n">
-        <v>-173.89</v>
+        <v>-179.89</v>
       </c>
       <c r="L35" t="n">
-        <v>420.07</v>
+        <v>434.57</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-70.83</v>
+        <v>-66.27</v>
       </c>
       <c r="K36" t="n">
-        <v>386.35</v>
+        <v>361.49</v>
       </c>
       <c r="L36" t="n">
-        <v>392.79</v>
+        <v>367.51</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>78.3</v>
+        <v>106.44</v>
       </c>
       <c r="K37" t="n">
-        <v>102.67</v>
+        <v>139.55</v>
       </c>
       <c r="L37" t="n">
-        <v>129.12</v>
+        <v>175.51</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>219.66</v>
+        <v>323.72</v>
       </c>
       <c r="K38" t="n">
-        <v>10.85</v>
+        <v>15.98</v>
       </c>
       <c r="L38" t="n">
-        <v>219.92</v>
+        <v>324.12</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-280.85</v>
+        <v>-336.9</v>
       </c>
       <c r="K39" t="n">
-        <v>102.51</v>
+        <v>122.97</v>
       </c>
       <c r="L39" t="n">
-        <v>298.98</v>
+        <v>358.64</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-119.06</v>
+        <v>-244.49</v>
       </c>
       <c r="K40" t="n">
-        <v>-19.73</v>
+        <v>-40.52</v>
       </c>
       <c r="L40" t="n">
-        <v>120.68</v>
+        <v>247.82</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>745.42</v>
+        <v>906.36</v>
       </c>
       <c r="K41" t="n">
-        <v>76.14</v>
+        <v>92.58</v>
       </c>
       <c r="L41" t="n">
-        <v>749.29</v>
+        <v>911.08</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-128.04</v>
+        <v>-196.49</v>
       </c>
       <c r="K42" t="n">
-        <v>-227.95</v>
+        <v>-349.81</v>
       </c>
       <c r="L42" t="n">
-        <v>261.45</v>
+        <v>401.22</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-363.61</v>
+        <v>-487</v>
       </c>
       <c r="K43" t="n">
-        <v>390.33</v>
+        <v>522.79</v>
       </c>
       <c r="L43" t="n">
-        <v>533.45</v>
+        <v>714.47</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>217.37</v>
+        <v>196.71</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.64</v>
+        <v>-2.39</v>
       </c>
       <c r="L44" t="n">
-        <v>217.38</v>
+        <v>196.73</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>49.97</v>
+        <v>53.85</v>
       </c>
       <c r="K45" t="n">
-        <v>-62.4</v>
+        <v>-67.26000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>79.94</v>
+        <v>86.16</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-205.57</v>
+        <v>-181.99</v>
       </c>
       <c r="K46" t="n">
-        <v>126.39</v>
+        <v>111.89</v>
       </c>
       <c r="L46" t="n">
-        <v>241.32</v>
+        <v>213.63</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-188.19</v>
+        <v>-176.88</v>
       </c>
       <c r="K47" t="n">
-        <v>-220.04</v>
+        <v>-206.81</v>
       </c>
       <c r="L47" t="n">
-        <v>289.54</v>
+        <v>272.13</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-60.99</v>
+        <v>-105.63</v>
       </c>
       <c r="K48" t="n">
-        <v>37.52</v>
+        <v>64.98</v>
       </c>
       <c r="L48" t="n">
-        <v>71.61</v>
+        <v>124.02</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>71.95</v>
+        <v>90.59</v>
       </c>
       <c r="K49" t="n">
-        <v>-159.66</v>
+        <v>-201.02</v>
       </c>
       <c r="L49" t="n">
-        <v>175.12</v>
+        <v>220.49</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>100.75</v>
+        <v>129.86</v>
       </c>
       <c r="K50" t="n">
-        <v>116.81</v>
+        <v>150.56</v>
       </c>
       <c r="L50" t="n">
-        <v>154.26</v>
+        <v>198.83</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>17.31</v>
+        <v>17.5</v>
       </c>
       <c r="K51" t="n">
-        <v>413.93</v>
+        <v>418.42</v>
       </c>
       <c r="L51" t="n">
-        <v>414.3</v>
+        <v>418.79</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-80.41</v>
+        <v>-126.98</v>
       </c>
       <c r="K52" t="n">
-        <v>-111.37</v>
+        <v>-175.87</v>
       </c>
       <c r="L52" t="n">
-        <v>137.36</v>
+        <v>216.92</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>5.74</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>-244.13</v>
+        <v>-352.39</v>
       </c>
       <c r="L53" t="n">
-        <v>244.2</v>
+        <v>352.49</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>214.74</v>
+        <v>281.5</v>
       </c>
       <c r="K54" t="n">
-        <v>-186.52</v>
+        <v>-244.51</v>
       </c>
       <c r="L54" t="n">
-        <v>284.44</v>
+        <v>372.87</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-457.76</v>
+        <v>-481.9</v>
       </c>
       <c r="K55" t="n">
-        <v>152.32</v>
+        <v>160.35</v>
       </c>
       <c r="L55" t="n">
-        <v>482.43</v>
+        <v>507.88</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>186.65</v>
+        <v>218.5</v>
       </c>
       <c r="K56" t="n">
-        <v>740.48</v>
+        <v>866.85</v>
       </c>
       <c r="L56" t="n">
-        <v>763.65</v>
+        <v>893.96</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>498.35</v>
+        <v>733.74</v>
       </c>
       <c r="K57" t="n">
-        <v>192.8</v>
+        <v>283.87</v>
       </c>
       <c r="L57" t="n">
-        <v>534.35</v>
+        <v>786.74</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-303.29</v>
+        <v>-380.19</v>
       </c>
       <c r="K58" t="n">
-        <v>-492.14</v>
+        <v>-616.9299999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>578.09</v>
+        <v>724.67</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-80.31999999999999</v>
+        <v>-94.06</v>
       </c>
       <c r="K59" t="n">
-        <v>-21.68</v>
+        <v>-25.39</v>
       </c>
       <c r="L59" t="n">
-        <v>83.2</v>
+        <v>97.43000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-25.66</v>
+        <v>-21.21</v>
       </c>
       <c r="K60" t="n">
-        <v>206.97</v>
+        <v>171.06</v>
       </c>
       <c r="L60" t="n">
-        <v>208.56</v>
+        <v>172.37</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>127.54</v>
+        <v>144.59</v>
       </c>
       <c r="K61" t="n">
-        <v>5.1</v>
+        <v>5.79</v>
       </c>
       <c r="L61" t="n">
-        <v>127.64</v>
+        <v>144.71</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>96.64</v>
+        <v>122.52</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.91</v>
+        <v>-3.69</v>
       </c>
       <c r="L62" t="n">
-        <v>96.68000000000001</v>
+        <v>122.58</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-208.47</v>
+        <v>-220.7</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.83</v>
+        <v>-2.99</v>
       </c>
       <c r="L63" t="n">
-        <v>208.49</v>
+        <v>220.72</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>263.46</v>
+        <v>241.65</v>
       </c>
       <c r="K64" t="n">
-        <v>-109.38</v>
+        <v>-100.33</v>
       </c>
       <c r="L64" t="n">
-        <v>285.26</v>
+        <v>261.65</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>35.33</v>
+        <v>115.47</v>
       </c>
       <c r="K65" t="n">
-        <v>-40.89</v>
+        <v>-133.64</v>
       </c>
       <c r="L65" t="n">
-        <v>54.04</v>
+        <v>176.61</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-373.52</v>
+        <v>-402.56</v>
       </c>
       <c r="K66" t="n">
-        <v>-163.89</v>
+        <v>-176.63</v>
       </c>
       <c r="L66" t="n">
-        <v>407.9</v>
+        <v>439.6</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-240.08</v>
+        <v>-305.69</v>
       </c>
       <c r="K67" t="n">
-        <v>95.26000000000001</v>
+        <v>121.29</v>
       </c>
       <c r="L67" t="n">
-        <v>258.28</v>
+        <v>328.87</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-110.08</v>
+        <v>-228.7</v>
       </c>
       <c r="K68" t="n">
-        <v>-131.48</v>
+        <v>-273.17</v>
       </c>
       <c r="L68" t="n">
-        <v>171.48</v>
+        <v>356.27</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-329.26</v>
+        <v>-368.71</v>
       </c>
       <c r="K69" t="n">
-        <v>-196.87</v>
+        <v>-220.46</v>
       </c>
       <c r="L69" t="n">
-        <v>383.63</v>
+        <v>429.59</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-35.72</v>
+        <v>-133.57</v>
       </c>
       <c r="K70" t="n">
-        <v>-41.64</v>
+        <v>-155.7</v>
       </c>
       <c r="L70" t="n">
-        <v>54.86</v>
+        <v>205.15</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>335.11</v>
+        <v>560.61</v>
       </c>
       <c r="K71" t="n">
-        <v>147.83</v>
+        <v>247.31</v>
       </c>
       <c r="L71" t="n">
-        <v>366.27</v>
+        <v>612.73</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-317.09</v>
+        <v>-430.05</v>
       </c>
       <c r="K72" t="n">
-        <v>561.41</v>
+        <v>761.42</v>
       </c>
       <c r="L72" t="n">
-        <v>644.77</v>
+        <v>874.47</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>15.4</v>
+        <v>20.42</v>
       </c>
       <c r="K73" t="n">
-        <v>622.96</v>
+        <v>826.21</v>
       </c>
       <c r="L73" t="n">
-        <v>623.15</v>
+        <v>826.46</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-53.09</v>
+        <v>-74.56999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>-72.14</v>
+        <v>-101.33</v>
       </c>
       <c r="L74" t="n">
-        <v>89.56999999999999</v>
+        <v>125.81</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-52.89</v>
+        <v>-60.84</v>
       </c>
       <c r="K75" t="n">
-        <v>75.53</v>
+        <v>86.88</v>
       </c>
       <c r="L75" t="n">
-        <v>92.20999999999999</v>
+        <v>106.07</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-54.4</v>
+        <v>-107.86</v>
       </c>
       <c r="K76" t="n">
-        <v>30.21</v>
+        <v>59.9</v>
       </c>
       <c r="L76" t="n">
-        <v>62.23</v>
+        <v>123.38</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>69.95</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>189.55</v>
+        <v>210.78</v>
       </c>
       <c r="L77" t="n">
-        <v>202.04</v>
+        <v>224.67</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>77.06999999999999</v>
+        <v>128.98</v>
       </c>
       <c r="K78" t="n">
-        <v>-10.37</v>
+        <v>-17.36</v>
       </c>
       <c r="L78" t="n">
-        <v>77.76000000000001</v>
+        <v>130.15</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>49.11</v>
+        <v>44.89</v>
       </c>
       <c r="K79" t="n">
-        <v>227.4</v>
+        <v>207.9</v>
       </c>
       <c r="L79" t="n">
-        <v>232.64</v>
+        <v>212.69</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>72.81</v>
+        <v>101.16</v>
       </c>
       <c r="K80" t="n">
-        <v>-145.15</v>
+        <v>-201.66</v>
       </c>
       <c r="L80" t="n">
-        <v>162.38</v>
+        <v>225.61</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>114.03</v>
+        <v>171.96</v>
       </c>
       <c r="K81" t="n">
-        <v>214.39</v>
+        <v>323.3</v>
       </c>
       <c r="L81" t="n">
-        <v>242.83</v>
+        <v>366.18</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-75.48999999999999</v>
+        <v>-130.65</v>
       </c>
       <c r="K82" t="n">
-        <v>118.21</v>
+        <v>204.58</v>
       </c>
       <c r="L82" t="n">
-        <v>140.26</v>
+        <v>242.74</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>544.65</v>
+        <v>629.27</v>
       </c>
       <c r="K83" t="n">
-        <v>-31.69</v>
+        <v>-36.62</v>
       </c>
       <c r="L83" t="n">
-        <v>545.5700000000001</v>
+        <v>630.34</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>77.61</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>263.62</v>
+        <v>298.9</v>
       </c>
       <c r="L84" t="n">
-        <v>274.8</v>
+        <v>311.58</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-108.1</v>
+        <v>-147.52</v>
       </c>
       <c r="K85" t="n">
-        <v>275.46</v>
+        <v>375.9</v>
       </c>
       <c r="L85" t="n">
-        <v>295.91</v>
+        <v>403.81</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>159.72</v>
+        <v>337.76</v>
       </c>
       <c r="K86" t="n">
-        <v>-63.63</v>
+        <v>-134.56</v>
       </c>
       <c r="L86" t="n">
-        <v>171.93</v>
+        <v>363.57</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-231.61</v>
+        <v>-266.14</v>
       </c>
       <c r="K87" t="n">
-        <v>742.7</v>
+        <v>853.4</v>
       </c>
       <c r="L87" t="n">
-        <v>777.98</v>
+        <v>893.9400000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-503.02</v>
+        <v>-721.86</v>
       </c>
       <c r="K88" t="n">
-        <v>149.55</v>
+        <v>214.61</v>
       </c>
       <c r="L88" t="n">
-        <v>524.78</v>
+        <v>753.09</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-09.xlsx
+++ b/output/2025-08-09.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>33.6</v>
+        <v>24.75</v>
       </c>
       <c r="K14" t="n">
-        <v>104.26</v>
+        <v>76.81</v>
       </c>
       <c r="L14" t="n">
-        <v>109.54</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>60.24</v>
+        <v>45.04</v>
       </c>
       <c r="K15" t="n">
-        <v>-56.81</v>
+        <v>-42.47</v>
       </c>
       <c r="L15" t="n">
-        <v>82.8</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-94.06999999999999</v>
+        <v>-67.93000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>108.97</v>
+        <v>78.69</v>
       </c>
       <c r="L16" t="n">
-        <v>143.96</v>
+        <v>103.95</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>192.52</v>
+        <v>122.61</v>
       </c>
       <c r="K17" t="n">
-        <v>-144.77</v>
+        <v>-92.2</v>
       </c>
       <c r="L17" t="n">
-        <v>240.88</v>
+        <v>153.41</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>117.42</v>
+        <v>79.69</v>
       </c>
       <c r="K18" t="n">
-        <v>35.33</v>
+        <v>23.98</v>
       </c>
       <c r="L18" t="n">
-        <v>122.62</v>
+        <v>83.22</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-89.79000000000001</v>
+        <v>-60.01</v>
       </c>
       <c r="K19" t="n">
-        <v>-68.04000000000001</v>
+        <v>-45.47</v>
       </c>
       <c r="L19" t="n">
-        <v>112.66</v>
+        <v>75.29000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-105.48</v>
+        <v>-60.04</v>
       </c>
       <c r="K20" t="n">
-        <v>198.97</v>
+        <v>113.27</v>
       </c>
       <c r="L20" t="n">
-        <v>225.2</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>259.26</v>
+        <v>150.06</v>
       </c>
       <c r="K21" t="n">
-        <v>-113.15</v>
+        <v>-65.48999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>282.87</v>
+        <v>163.73</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-327.48</v>
+        <v>-183.52</v>
       </c>
       <c r="K22" t="n">
-        <v>-30.75</v>
+        <v>-17.23</v>
       </c>
       <c r="L22" t="n">
-        <v>328.92</v>
+        <v>184.33</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>460.43</v>
+        <v>224.92</v>
       </c>
       <c r="K23" t="n">
-        <v>-320.25</v>
+        <v>-156.44</v>
       </c>
       <c r="L23" t="n">
-        <v>560.86</v>
+        <v>273.97</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>221.45</v>
+        <v>115.84</v>
       </c>
       <c r="K24" t="n">
-        <v>-179.99</v>
+        <v>-94.15000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>285.37</v>
+        <v>149.28</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-165.57</v>
+        <v>-84.78</v>
       </c>
       <c r="K25" t="n">
-        <v>-242.75</v>
+        <v>-124.3</v>
       </c>
       <c r="L25" t="n">
-        <v>293.84</v>
+        <v>150.46</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>286.54</v>
+        <v>129.24</v>
       </c>
       <c r="K26" t="n">
-        <v>-365.94</v>
+        <v>-165.05</v>
       </c>
       <c r="L26" t="n">
-        <v>464.78</v>
+        <v>209.63</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>509.27</v>
+        <v>232.98</v>
       </c>
       <c r="K27" t="n">
-        <v>255.16</v>
+        <v>116.73</v>
       </c>
       <c r="L27" t="n">
-        <v>569.62</v>
+        <v>260.58</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-201.27</v>
+        <v>-88.20999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>894.63</v>
+        <v>392.1</v>
       </c>
       <c r="L28" t="n">
-        <v>916.99</v>
+        <v>401.9</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>18.32</v>
+        <v>13.53</v>
       </c>
       <c r="K29" t="n">
-        <v>95.19</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>96.93000000000001</v>
+        <v>71.58</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>64.81999999999999</v>
+        <v>47.53</v>
       </c>
       <c r="K30" t="n">
-        <v>-75.42</v>
+        <v>-55.31</v>
       </c>
       <c r="L30" t="n">
-        <v>99.45</v>
+        <v>72.93000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-89.64</v>
+        <v>-64.73</v>
       </c>
       <c r="K31" t="n">
-        <v>-159.46</v>
+        <v>-115.15</v>
       </c>
       <c r="L31" t="n">
-        <v>182.93</v>
+        <v>132.1</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-61.73</v>
+        <v>-39.07</v>
       </c>
       <c r="K32" t="n">
-        <v>-164.53</v>
+        <v>-104.12</v>
       </c>
       <c r="L32" t="n">
-        <v>175.73</v>
+        <v>111.2</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-170.97</v>
+        <v>-113.09</v>
       </c>
       <c r="K33" t="n">
-        <v>162.33</v>
+        <v>107.37</v>
       </c>
       <c r="L33" t="n">
-        <v>235.76</v>
+        <v>155.94</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-77.56</v>
+        <v>-50.01</v>
       </c>
       <c r="K34" t="n">
-        <v>113.2</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>137.22</v>
+        <v>88.47</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-395.59</v>
+        <v>-220.7</v>
       </c>
       <c r="K35" t="n">
-        <v>-179.89</v>
+        <v>-100.36</v>
       </c>
       <c r="L35" t="n">
-        <v>434.57</v>
+        <v>242.45</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-66.27</v>
+        <v>-39.45</v>
       </c>
       <c r="K36" t="n">
-        <v>361.49</v>
+        <v>215.21</v>
       </c>
       <c r="L36" t="n">
-        <v>367.51</v>
+        <v>218.79</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>106.44</v>
+        <v>63.62</v>
       </c>
       <c r="K37" t="n">
-        <v>139.55</v>
+        <v>83.41</v>
       </c>
       <c r="L37" t="n">
-        <v>175.51</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>323.72</v>
+        <v>162.13</v>
       </c>
       <c r="K38" t="n">
-        <v>15.98</v>
+        <v>8</v>
       </c>
       <c r="L38" t="n">
-        <v>324.12</v>
+        <v>162.33</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-336.9</v>
+        <v>-160.77</v>
       </c>
       <c r="K39" t="n">
-        <v>122.97</v>
+        <v>58.68</v>
       </c>
       <c r="L39" t="n">
-        <v>358.64</v>
+        <v>171.15</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-244.49</v>
+        <v>-122.03</v>
       </c>
       <c r="K40" t="n">
-        <v>-40.52</v>
+        <v>-20.22</v>
       </c>
       <c r="L40" t="n">
-        <v>247.82</v>
+        <v>123.7</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>906.36</v>
+        <v>401.34</v>
       </c>
       <c r="K41" t="n">
-        <v>92.58</v>
+        <v>40.99</v>
       </c>
       <c r="L41" t="n">
-        <v>911.08</v>
+        <v>403.43</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-196.49</v>
+        <v>-90.41</v>
       </c>
       <c r="K42" t="n">
-        <v>-349.81</v>
+        <v>-160.95</v>
       </c>
       <c r="L42" t="n">
-        <v>401.22</v>
+        <v>184.6</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-487</v>
+        <v>-216.27</v>
       </c>
       <c r="K43" t="n">
-        <v>522.79</v>
+        <v>232.16</v>
       </c>
       <c r="L43" t="n">
-        <v>714.47</v>
+        <v>317.29</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>196.71</v>
+        <v>135.74</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.39</v>
+        <v>-1.65</v>
       </c>
       <c r="L44" t="n">
-        <v>196.73</v>
+        <v>135.75</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>53.85</v>
+        <v>35.45</v>
       </c>
       <c r="K45" t="n">
-        <v>-67.26000000000001</v>
+        <v>-44.27</v>
       </c>
       <c r="L45" t="n">
-        <v>86.16</v>
+        <v>56.72</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-181.99</v>
+        <v>-128.96</v>
       </c>
       <c r="K46" t="n">
-        <v>111.89</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>213.63</v>
+        <v>151.39</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-176.88</v>
+        <v>-114.11</v>
       </c>
       <c r="K47" t="n">
-        <v>-206.81</v>
+        <v>-133.42</v>
       </c>
       <c r="L47" t="n">
-        <v>272.13</v>
+        <v>175.56</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-105.63</v>
+        <v>-69.34</v>
       </c>
       <c r="K48" t="n">
-        <v>64.98</v>
+        <v>42.66</v>
       </c>
       <c r="L48" t="n">
-        <v>124.02</v>
+        <v>81.41</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>90.59</v>
+        <v>55.63</v>
       </c>
       <c r="K49" t="n">
-        <v>-201.02</v>
+        <v>-123.46</v>
       </c>
       <c r="L49" t="n">
-        <v>220.49</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>129.86</v>
+        <v>76.38</v>
       </c>
       <c r="K50" t="n">
-        <v>150.56</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>198.83</v>
+        <v>116.93</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>17.5</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>418.42</v>
+        <v>235.85</v>
       </c>
       <c r="L51" t="n">
-        <v>418.79</v>
+        <v>236.06</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-126.98</v>
+        <v>-70.84</v>
       </c>
       <c r="K52" t="n">
-        <v>-175.87</v>
+        <v>-98.12</v>
       </c>
       <c r="L52" t="n">
-        <v>216.92</v>
+        <v>121.02</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>8.279999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="K53" t="n">
-        <v>-352.39</v>
+        <v>-174.38</v>
       </c>
       <c r="L53" t="n">
-        <v>352.49</v>
+        <v>174.43</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>281.5</v>
+        <v>140.99</v>
       </c>
       <c r="K54" t="n">
-        <v>-244.51</v>
+        <v>-122.46</v>
       </c>
       <c r="L54" t="n">
-        <v>372.87</v>
+        <v>186.74</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-481.9</v>
+        <v>-253.25</v>
       </c>
       <c r="K55" t="n">
-        <v>160.35</v>
+        <v>84.27</v>
       </c>
       <c r="L55" t="n">
-        <v>507.88</v>
+        <v>266.9</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>218.5</v>
+        <v>97.92</v>
       </c>
       <c r="K56" t="n">
-        <v>866.85</v>
+        <v>388.47</v>
       </c>
       <c r="L56" t="n">
-        <v>893.96</v>
+        <v>400.62</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>733.74</v>
+        <v>314.9</v>
       </c>
       <c r="K57" t="n">
-        <v>283.87</v>
+        <v>121.83</v>
       </c>
       <c r="L57" t="n">
-        <v>786.74</v>
+        <v>337.65</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-380.19</v>
+        <v>-171.06</v>
       </c>
       <c r="K58" t="n">
-        <v>-616.9299999999999</v>
+        <v>-277.57</v>
       </c>
       <c r="L58" t="n">
-        <v>724.67</v>
+        <v>326.05</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-94.06</v>
+        <v>-68.39</v>
       </c>
       <c r="K59" t="n">
-        <v>-25.39</v>
+        <v>-18.46</v>
       </c>
       <c r="L59" t="n">
-        <v>97.43000000000001</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-21.21</v>
+        <v>-15.31</v>
       </c>
       <c r="K60" t="n">
-        <v>171.06</v>
+        <v>123.52</v>
       </c>
       <c r="L60" t="n">
-        <v>172.37</v>
+        <v>124.47</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>144.59</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>5.79</v>
+        <v>3.92</v>
       </c>
       <c r="L61" t="n">
-        <v>144.71</v>
+        <v>97.98</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>122.52</v>
+        <v>84.42</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.69</v>
+        <v>-2.54</v>
       </c>
       <c r="L62" t="n">
-        <v>122.58</v>
+        <v>84.45999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-220.7</v>
+        <v>-140.96</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.99</v>
+        <v>-1.91</v>
       </c>
       <c r="L63" t="n">
-        <v>220.72</v>
+        <v>140.97</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>241.65</v>
+        <v>157.76</v>
       </c>
       <c r="K64" t="n">
-        <v>-100.33</v>
+        <v>-65.5</v>
       </c>
       <c r="L64" t="n">
-        <v>261.65</v>
+        <v>170.82</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>115.47</v>
+        <v>62.03</v>
       </c>
       <c r="K65" t="n">
-        <v>-133.64</v>
+        <v>-71.79000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>176.61</v>
+        <v>94.87</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-402.56</v>
+        <v>-221.33</v>
       </c>
       <c r="K66" t="n">
-        <v>-176.63</v>
+        <v>-97.12</v>
       </c>
       <c r="L66" t="n">
-        <v>439.6</v>
+        <v>241.7</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-305.69</v>
+        <v>-166.79</v>
       </c>
       <c r="K67" t="n">
-        <v>121.29</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>328.87</v>
+        <v>179.44</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-228.7</v>
+        <v>-106.98</v>
       </c>
       <c r="K68" t="n">
-        <v>-273.17</v>
+        <v>-127.78</v>
       </c>
       <c r="L68" t="n">
-        <v>356.27</v>
+        <v>166.65</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-368.71</v>
+        <v>-188.55</v>
       </c>
       <c r="K69" t="n">
-        <v>-220.46</v>
+        <v>-112.74</v>
       </c>
       <c r="L69" t="n">
-        <v>429.59</v>
+        <v>219.69</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-133.57</v>
+        <v>-65.44</v>
       </c>
       <c r="K70" t="n">
-        <v>-155.7</v>
+        <v>-76.28</v>
       </c>
       <c r="L70" t="n">
-        <v>205.15</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>560.61</v>
+        <v>242.37</v>
       </c>
       <c r="K71" t="n">
-        <v>247.31</v>
+        <v>106.92</v>
       </c>
       <c r="L71" t="n">
-        <v>612.73</v>
+        <v>264.91</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-430.05</v>
+        <v>-185.71</v>
       </c>
       <c r="K72" t="n">
-        <v>761.42</v>
+        <v>328.81</v>
       </c>
       <c r="L72" t="n">
-        <v>874.47</v>
+        <v>377.63</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>20.42</v>
+        <v>8.92</v>
       </c>
       <c r="K73" t="n">
-        <v>826.21</v>
+        <v>360.94</v>
       </c>
       <c r="L73" t="n">
-        <v>826.46</v>
+        <v>361.05</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-74.56999999999999</v>
+        <v>-49.53</v>
       </c>
       <c r="K74" t="n">
-        <v>-101.33</v>
+        <v>-67.31</v>
       </c>
       <c r="L74" t="n">
-        <v>125.81</v>
+        <v>83.56999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-60.84</v>
+        <v>-43.15</v>
       </c>
       <c r="K75" t="n">
-        <v>86.88</v>
+        <v>61.63</v>
       </c>
       <c r="L75" t="n">
-        <v>106.07</v>
+        <v>75.23</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-107.86</v>
+        <v>-68.81</v>
       </c>
       <c r="K76" t="n">
-        <v>59.9</v>
+        <v>38.21</v>
       </c>
       <c r="L76" t="n">
-        <v>123.38</v>
+        <v>78.70999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>77.79000000000001</v>
+        <v>48.97</v>
       </c>
       <c r="K77" t="n">
-        <v>210.78</v>
+        <v>132.68</v>
       </c>
       <c r="L77" t="n">
-        <v>224.67</v>
+        <v>141.43</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>128.98</v>
+        <v>83</v>
       </c>
       <c r="K78" t="n">
-        <v>-17.36</v>
+        <v>-11.17</v>
       </c>
       <c r="L78" t="n">
-        <v>130.15</v>
+        <v>83.75</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>44.89</v>
+        <v>30.04</v>
       </c>
       <c r="K79" t="n">
-        <v>207.9</v>
+        <v>139.12</v>
       </c>
       <c r="L79" t="n">
-        <v>212.69</v>
+        <v>142.33</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>101.16</v>
+        <v>58.14</v>
       </c>
       <c r="K80" t="n">
-        <v>-201.66</v>
+        <v>-115.89</v>
       </c>
       <c r="L80" t="n">
-        <v>225.61</v>
+        <v>129.66</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>171.96</v>
+        <v>89.52</v>
       </c>
       <c r="K81" t="n">
-        <v>323.3</v>
+        <v>168.31</v>
       </c>
       <c r="L81" t="n">
-        <v>366.18</v>
+        <v>190.63</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-130.65</v>
+        <v>-71.63</v>
       </c>
       <c r="K82" t="n">
-        <v>204.58</v>
+        <v>112.16</v>
       </c>
       <c r="L82" t="n">
-        <v>242.74</v>
+        <v>133.09</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>629.27</v>
+        <v>305.14</v>
       </c>
       <c r="K83" t="n">
-        <v>-36.62</v>
+        <v>-17.75</v>
       </c>
       <c r="L83" t="n">
-        <v>630.34</v>
+        <v>305.65</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>87.98999999999999</v>
+        <v>47.76</v>
       </c>
       <c r="K84" t="n">
-        <v>298.9</v>
+        <v>162.23</v>
       </c>
       <c r="L84" t="n">
-        <v>311.58</v>
+        <v>169.11</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-147.52</v>
+        <v>-74.64</v>
       </c>
       <c r="K85" t="n">
-        <v>375.9</v>
+        <v>190.2</v>
       </c>
       <c r="L85" t="n">
-        <v>403.81</v>
+        <v>204.33</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>337.76</v>
+        <v>153.1</v>
       </c>
       <c r="K86" t="n">
-        <v>-134.56</v>
+        <v>-60.99</v>
       </c>
       <c r="L86" t="n">
-        <v>363.57</v>
+        <v>164.81</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-266.14</v>
+        <v>-119.94</v>
       </c>
       <c r="K87" t="n">
-        <v>853.4</v>
+        <v>384.59</v>
       </c>
       <c r="L87" t="n">
-        <v>893.9400000000001</v>
+        <v>402.86</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-721.86</v>
+        <v>-313.02</v>
       </c>
       <c r="K88" t="n">
-        <v>214.61</v>
+        <v>93.06</v>
       </c>
       <c r="L88" t="n">
-        <v>753.09</v>
+        <v>326.56</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-09.xlsx
+++ b/output/2025-08-09.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>24.75</v>
+        <v>26.5</v>
       </c>
       <c r="K14" t="n">
-        <v>76.81</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>80.7</v>
+        <v>86.41</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>45.04</v>
+        <v>48.44</v>
       </c>
       <c r="K15" t="n">
-        <v>-42.47</v>
+        <v>-45.68</v>
       </c>
       <c r="L15" t="n">
-        <v>61.91</v>
+        <v>66.58</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-67.93000000000001</v>
+        <v>-72.31999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>78.69</v>
+        <v>83.77</v>
       </c>
       <c r="L16" t="n">
-        <v>103.95</v>
+        <v>110.67</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>122.61</v>
+        <v>137.03</v>
       </c>
       <c r="K17" t="n">
-        <v>-92.2</v>
+        <v>-103.04</v>
       </c>
       <c r="L17" t="n">
-        <v>153.41</v>
+        <v>171.45</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>79.69</v>
+        <v>88.92</v>
       </c>
       <c r="K18" t="n">
-        <v>23.98</v>
+        <v>26.75</v>
       </c>
       <c r="L18" t="n">
-        <v>83.22</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-60.01</v>
+        <v>-66.62</v>
       </c>
       <c r="K19" t="n">
-        <v>-45.47</v>
+        <v>-50.48</v>
       </c>
       <c r="L19" t="n">
-        <v>75.29000000000001</v>
+        <v>83.58</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-60.04</v>
+        <v>-68.61</v>
       </c>
       <c r="K20" t="n">
-        <v>113.27</v>
+        <v>129.43</v>
       </c>
       <c r="L20" t="n">
-        <v>128.2</v>
+        <v>146.49</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>150.06</v>
+        <v>172.07</v>
       </c>
       <c r="K21" t="n">
-        <v>-65.48999999999999</v>
+        <v>-75.09999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>163.73</v>
+        <v>187.75</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-183.52</v>
+        <v>-213.7</v>
       </c>
       <c r="K22" t="n">
-        <v>-17.23</v>
+        <v>-20.07</v>
       </c>
       <c r="L22" t="n">
-        <v>184.33</v>
+        <v>214.64</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>224.92</v>
+        <v>265.94</v>
       </c>
       <c r="K23" t="n">
-        <v>-156.44</v>
+        <v>-184.97</v>
       </c>
       <c r="L23" t="n">
-        <v>273.97</v>
+        <v>323.94</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>115.84</v>
+        <v>138.19</v>
       </c>
       <c r="K24" t="n">
-        <v>-94.15000000000001</v>
+        <v>-112.32</v>
       </c>
       <c r="L24" t="n">
-        <v>149.28</v>
+        <v>178.08</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-84.78</v>
+        <v>-101.47</v>
       </c>
       <c r="K25" t="n">
-        <v>-124.3</v>
+        <v>-148.77</v>
       </c>
       <c r="L25" t="n">
-        <v>150.46</v>
+        <v>180.09</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>129.24</v>
+        <v>155.38</v>
       </c>
       <c r="K26" t="n">
-        <v>-165.05</v>
+        <v>-198.44</v>
       </c>
       <c r="L26" t="n">
-        <v>209.63</v>
+        <v>252.03</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>232.98</v>
+        <v>281.17</v>
       </c>
       <c r="K27" t="n">
-        <v>116.73</v>
+        <v>140.88</v>
       </c>
       <c r="L27" t="n">
-        <v>260.58</v>
+        <v>314.49</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-88.20999999999999</v>
+        <v>-105.19</v>
       </c>
       <c r="K28" t="n">
-        <v>392.1</v>
+        <v>467.55</v>
       </c>
       <c r="L28" t="n">
-        <v>401.9</v>
+        <v>479.24</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>13.53</v>
+        <v>14.6</v>
       </c>
       <c r="K29" t="n">
-        <v>70.29000000000001</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>71.58</v>
+        <v>77.23999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>47.53</v>
+        <v>51.41</v>
       </c>
       <c r="K30" t="n">
-        <v>-55.31</v>
+        <v>-59.82</v>
       </c>
       <c r="L30" t="n">
-        <v>72.93000000000001</v>
+        <v>78.88</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-64.73</v>
+        <v>-69.48</v>
       </c>
       <c r="K31" t="n">
-        <v>-115.15</v>
+        <v>-123.62</v>
       </c>
       <c r="L31" t="n">
-        <v>132.1</v>
+        <v>141.81</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-39.07</v>
+        <v>-43.33</v>
       </c>
       <c r="K32" t="n">
-        <v>-104.12</v>
+        <v>-115.48</v>
       </c>
       <c r="L32" t="n">
-        <v>111.2</v>
+        <v>123.34</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-113.09</v>
+        <v>-126.52</v>
       </c>
       <c r="K33" t="n">
-        <v>107.37</v>
+        <v>120.12</v>
       </c>
       <c r="L33" t="n">
-        <v>155.94</v>
+        <v>174.46</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-50.01</v>
+        <v>-54.9</v>
       </c>
       <c r="K34" t="n">
-        <v>72.98999999999999</v>
+        <v>80.12</v>
       </c>
       <c r="L34" t="n">
-        <v>88.47</v>
+        <v>97.12</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-220.7</v>
+        <v>-255.58</v>
       </c>
       <c r="K35" t="n">
-        <v>-100.36</v>
+        <v>-116.22</v>
       </c>
       <c r="L35" t="n">
-        <v>242.45</v>
+        <v>280.77</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-39.45</v>
+        <v>-45.54</v>
       </c>
       <c r="K36" t="n">
-        <v>215.21</v>
+        <v>248.45</v>
       </c>
       <c r="L36" t="n">
-        <v>218.79</v>
+        <v>252.59</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>63.62</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>83.41</v>
+        <v>96.94</v>
       </c>
       <c r="L37" t="n">
-        <v>104.9</v>
+        <v>121.91</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>162.13</v>
+        <v>193.05</v>
       </c>
       <c r="K38" t="n">
-        <v>8</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>162.33</v>
+        <v>193.29</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-160.77</v>
+        <v>-192.96</v>
       </c>
       <c r="K39" t="n">
-        <v>58.68</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>171.15</v>
+        <v>205.41</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-122.03</v>
+        <v>-144.62</v>
       </c>
       <c r="K40" t="n">
-        <v>-20.22</v>
+        <v>-23.97</v>
       </c>
       <c r="L40" t="n">
-        <v>123.7</v>
+        <v>146.59</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>401.34</v>
+        <v>488.5</v>
       </c>
       <c r="K41" t="n">
-        <v>40.99</v>
+        <v>49.9</v>
       </c>
       <c r="L41" t="n">
-        <v>403.43</v>
+        <v>491.04</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-90.41</v>
+        <v>-108.88</v>
       </c>
       <c r="K42" t="n">
-        <v>-160.95</v>
+        <v>-193.83</v>
       </c>
       <c r="L42" t="n">
-        <v>184.6</v>
+        <v>222.32</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-216.27</v>
+        <v>-260.04</v>
       </c>
       <c r="K43" t="n">
-        <v>232.16</v>
+        <v>279.16</v>
       </c>
       <c r="L43" t="n">
-        <v>317.29</v>
+        <v>381.51</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>135.74</v>
+        <v>146.69</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.65</v>
+        <v>-1.78</v>
       </c>
       <c r="L44" t="n">
-        <v>135.75</v>
+        <v>146.7</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>35.45</v>
+        <v>38.28</v>
       </c>
       <c r="K45" t="n">
-        <v>-44.27</v>
+        <v>-47.81</v>
       </c>
       <c r="L45" t="n">
-        <v>56.72</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-128.96</v>
+        <v>-137.5</v>
       </c>
       <c r="K46" t="n">
-        <v>79.29000000000001</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>151.39</v>
+        <v>161.41</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-114.11</v>
+        <v>-126.71</v>
       </c>
       <c r="K47" t="n">
-        <v>-133.42</v>
+        <v>-148.15</v>
       </c>
       <c r="L47" t="n">
-        <v>175.56</v>
+        <v>194.95</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-69.34</v>
+        <v>-77.09999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>42.66</v>
+        <v>47.43</v>
       </c>
       <c r="L48" t="n">
-        <v>81.41</v>
+        <v>90.52</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>55.63</v>
+        <v>63.32</v>
       </c>
       <c r="K49" t="n">
-        <v>-123.46</v>
+        <v>-140.51</v>
       </c>
       <c r="L49" t="n">
-        <v>135.41</v>
+        <v>154.12</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>76.38</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>88.54000000000001</v>
+        <v>103.07</v>
       </c>
       <c r="L50" t="n">
-        <v>116.93</v>
+        <v>136.11</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>9.859999999999999</v>
+        <v>11.42</v>
       </c>
       <c r="K51" t="n">
-        <v>235.85</v>
+        <v>273.06</v>
       </c>
       <c r="L51" t="n">
-        <v>236.06</v>
+        <v>273.3</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-70.84</v>
+        <v>-82.04000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-98.12</v>
+        <v>-113.63</v>
       </c>
       <c r="L52" t="n">
-        <v>121.02</v>
+        <v>140.15</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>4.1</v>
+        <v>4.92</v>
       </c>
       <c r="K53" t="n">
-        <v>-174.38</v>
+        <v>-209.33</v>
       </c>
       <c r="L53" t="n">
-        <v>174.43</v>
+        <v>209.39</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>140.99</v>
+        <v>168.16</v>
       </c>
       <c r="K54" t="n">
-        <v>-122.46</v>
+        <v>-146.06</v>
       </c>
       <c r="L54" t="n">
-        <v>186.74</v>
+        <v>222.74</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-253.25</v>
+        <v>-300.61</v>
       </c>
       <c r="K55" t="n">
-        <v>84.27</v>
+        <v>100.03</v>
       </c>
       <c r="L55" t="n">
-        <v>266.9</v>
+        <v>316.82</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>97.92</v>
+        <v>117.66</v>
       </c>
       <c r="K56" t="n">
-        <v>388.47</v>
+        <v>466.78</v>
       </c>
       <c r="L56" t="n">
-        <v>400.62</v>
+        <v>481.38</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>314.9</v>
+        <v>381.21</v>
       </c>
       <c r="K57" t="n">
-        <v>121.83</v>
+        <v>147.48</v>
       </c>
       <c r="L57" t="n">
-        <v>337.65</v>
+        <v>408.74</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-171.06</v>
+        <v>-206.6</v>
       </c>
       <c r="K58" t="n">
-        <v>-277.57</v>
+        <v>-335.24</v>
       </c>
       <c r="L58" t="n">
-        <v>326.05</v>
+        <v>393.79</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-68.39</v>
+        <v>-72.66</v>
       </c>
       <c r="K59" t="n">
-        <v>-18.46</v>
+        <v>-19.61</v>
       </c>
       <c r="L59" t="n">
-        <v>70.84</v>
+        <v>75.26000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-15.31</v>
+        <v>-16.41</v>
       </c>
       <c r="K60" t="n">
-        <v>123.52</v>
+        <v>132.33</v>
       </c>
       <c r="L60" t="n">
-        <v>124.47</v>
+        <v>133.34</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>97.90000000000001</v>
+        <v>104.85</v>
       </c>
       <c r="K61" t="n">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="L61" t="n">
-        <v>97.98</v>
+        <v>104.93</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>84.42</v>
+        <v>93.2</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.54</v>
+        <v>-2.81</v>
       </c>
       <c r="L62" t="n">
-        <v>84.45999999999999</v>
+        <v>93.23999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-140.96</v>
+        <v>-156.8</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.91</v>
+        <v>-2.12</v>
       </c>
       <c r="L63" t="n">
-        <v>140.97</v>
+        <v>156.81</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>157.76</v>
+        <v>176.5</v>
       </c>
       <c r="K64" t="n">
-        <v>-65.5</v>
+        <v>-73.28</v>
       </c>
       <c r="L64" t="n">
-        <v>170.82</v>
+        <v>191.11</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>62.03</v>
+        <v>72.33</v>
       </c>
       <c r="K65" t="n">
-        <v>-71.79000000000001</v>
+        <v>-83.70999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>94.87</v>
+        <v>110.63</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-221.33</v>
+        <v>-257.09</v>
       </c>
       <c r="K66" t="n">
-        <v>-97.12</v>
+        <v>-112.81</v>
       </c>
       <c r="L66" t="n">
-        <v>241.7</v>
+        <v>280.75</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-166.79</v>
+        <v>-193.46</v>
       </c>
       <c r="K67" t="n">
-        <v>66.18000000000001</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>179.44</v>
+        <v>208.13</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-106.98</v>
+        <v>-126.25</v>
       </c>
       <c r="K68" t="n">
-        <v>-127.78</v>
+        <v>-150.8</v>
       </c>
       <c r="L68" t="n">
-        <v>166.65</v>
+        <v>196.68</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-188.55</v>
+        <v>-225.76</v>
       </c>
       <c r="K69" t="n">
-        <v>-112.74</v>
+        <v>-134.99</v>
       </c>
       <c r="L69" t="n">
-        <v>219.69</v>
+        <v>263.04</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-65.44</v>
+        <v>-77.61</v>
       </c>
       <c r="K70" t="n">
-        <v>-76.28</v>
+        <v>-90.47</v>
       </c>
       <c r="L70" t="n">
-        <v>100.5</v>
+        <v>119.2</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>242.37</v>
+        <v>289.6</v>
       </c>
       <c r="K71" t="n">
-        <v>106.92</v>
+        <v>127.76</v>
       </c>
       <c r="L71" t="n">
-        <v>264.91</v>
+        <v>316.53</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-185.71</v>
+        <v>-220.4</v>
       </c>
       <c r="K72" t="n">
-        <v>328.81</v>
+        <v>390.22</v>
       </c>
       <c r="L72" t="n">
-        <v>377.63</v>
+        <v>448.16</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>8.92</v>
+        <v>10.77</v>
       </c>
       <c r="K73" t="n">
-        <v>360.94</v>
+        <v>435.86</v>
       </c>
       <c r="L73" t="n">
-        <v>361.05</v>
+        <v>435.99</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-49.53</v>
+        <v>-53.3</v>
       </c>
       <c r="K74" t="n">
-        <v>-67.31</v>
+        <v>-72.42</v>
       </c>
       <c r="L74" t="n">
-        <v>83.56999999999999</v>
+        <v>89.92</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-43.15</v>
+        <v>-46.39</v>
       </c>
       <c r="K75" t="n">
-        <v>61.63</v>
+        <v>66.25</v>
       </c>
       <c r="L75" t="n">
-        <v>75.23</v>
+        <v>80.87</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-68.81</v>
+        <v>-73.48</v>
       </c>
       <c r="K76" t="n">
-        <v>38.21</v>
+        <v>40.81</v>
       </c>
       <c r="L76" t="n">
-        <v>78.70999999999999</v>
+        <v>84.05</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>48.97</v>
+        <v>54.97</v>
       </c>
       <c r="K77" t="n">
-        <v>132.68</v>
+        <v>148.93</v>
       </c>
       <c r="L77" t="n">
-        <v>141.43</v>
+        <v>158.75</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>83</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>-11.17</v>
+        <v>-12.55</v>
       </c>
       <c r="L78" t="n">
-        <v>83.75</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>30.04</v>
+        <v>33.35</v>
       </c>
       <c r="K79" t="n">
-        <v>139.12</v>
+        <v>154.43</v>
       </c>
       <c r="L79" t="n">
-        <v>142.33</v>
+        <v>157.99</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>58.14</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-115.89</v>
+        <v>-133.58</v>
       </c>
       <c r="L80" t="n">
-        <v>129.66</v>
+        <v>149.44</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>89.52</v>
+        <v>103.44</v>
       </c>
       <c r="K81" t="n">
-        <v>168.31</v>
+        <v>194.47</v>
       </c>
       <c r="L81" t="n">
-        <v>190.63</v>
+        <v>220.27</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-71.63</v>
+        <v>-83.61</v>
       </c>
       <c r="K82" t="n">
-        <v>112.16</v>
+        <v>130.92</v>
       </c>
       <c r="L82" t="n">
-        <v>133.09</v>
+        <v>155.34</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>305.14</v>
+        <v>363.16</v>
       </c>
       <c r="K83" t="n">
-        <v>-17.75</v>
+        <v>-21.13</v>
       </c>
       <c r="L83" t="n">
-        <v>305.65</v>
+        <v>363.77</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>47.76</v>
+        <v>56.72</v>
       </c>
       <c r="K84" t="n">
-        <v>162.23</v>
+        <v>192.66</v>
       </c>
       <c r="L84" t="n">
-        <v>169.11</v>
+        <v>200.84</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-74.64</v>
+        <v>-88.13</v>
       </c>
       <c r="K85" t="n">
-        <v>190.2</v>
+        <v>224.58</v>
       </c>
       <c r="L85" t="n">
-        <v>204.33</v>
+        <v>241.26</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>153.1</v>
+        <v>183.95</v>
       </c>
       <c r="K86" t="n">
-        <v>-60.99</v>
+        <v>-73.28</v>
       </c>
       <c r="L86" t="n">
-        <v>164.81</v>
+        <v>198.01</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-119.94</v>
+        <v>-144.66</v>
       </c>
       <c r="K87" t="n">
-        <v>384.59</v>
+        <v>463.86</v>
       </c>
       <c r="L87" t="n">
-        <v>402.86</v>
+        <v>485.9</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-313.02</v>
+        <v>-373.22</v>
       </c>
       <c r="K88" t="n">
-        <v>93.06</v>
+        <v>110.96</v>
       </c>
       <c r="L88" t="n">
-        <v>326.56</v>
+        <v>389.36</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-09.xlsx
+++ b/output/2025-08-09.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>26.5</v>
+        <v>17.42</v>
       </c>
       <c r="K14" t="n">
-        <v>82.23999999999999</v>
+        <v>54.06</v>
       </c>
       <c r="L14" t="n">
-        <v>86.41</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>48.44</v>
+        <v>30.67</v>
       </c>
       <c r="K15" t="n">
-        <v>-45.68</v>
+        <v>-28.92</v>
       </c>
       <c r="L15" t="n">
-        <v>66.58</v>
+        <v>42.15</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-72.31999999999999</v>
+        <v>-46.45</v>
       </c>
       <c r="K16" t="n">
-        <v>83.77</v>
+        <v>53.81</v>
       </c>
       <c r="L16" t="n">
-        <v>110.67</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>137.03</v>
+        <v>81.7</v>
       </c>
       <c r="K17" t="n">
-        <v>-103.04</v>
+        <v>-61.44</v>
       </c>
       <c r="L17" t="n">
-        <v>171.45</v>
+        <v>102.22</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>88.92</v>
+        <v>60.35</v>
       </c>
       <c r="K18" t="n">
-        <v>26.75</v>
+        <v>18.16</v>
       </c>
       <c r="L18" t="n">
-        <v>92.86</v>
+        <v>63.02</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-66.62</v>
+        <v>-43.9</v>
       </c>
       <c r="K19" t="n">
-        <v>-50.48</v>
+        <v>-33.27</v>
       </c>
       <c r="L19" t="n">
-        <v>83.58</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-68.61</v>
+        <v>-38.12</v>
       </c>
       <c r="K20" t="n">
-        <v>129.43</v>
+        <v>71.91</v>
       </c>
       <c r="L20" t="n">
-        <v>146.49</v>
+        <v>81.39</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>172.07</v>
+        <v>105.12</v>
       </c>
       <c r="K21" t="n">
-        <v>-75.09999999999999</v>
+        <v>-45.88</v>
       </c>
       <c r="L21" t="n">
-        <v>187.75</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-213.7</v>
+        <v>-127.86</v>
       </c>
       <c r="K22" t="n">
-        <v>-20.07</v>
+        <v>-12.01</v>
       </c>
       <c r="L22" t="n">
-        <v>214.64</v>
+        <v>128.42</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>265.94</v>
+        <v>167.05</v>
       </c>
       <c r="K23" t="n">
-        <v>-184.97</v>
+        <v>-116.19</v>
       </c>
       <c r="L23" t="n">
-        <v>323.94</v>
+        <v>203.48</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>138.19</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-112.32</v>
+        <v>-78.76000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>178.08</v>
+        <v>124.88</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-101.47</v>
+        <v>-68.91</v>
       </c>
       <c r="K25" t="n">
-        <v>-148.77</v>
+        <v>-101.03</v>
       </c>
       <c r="L25" t="n">
-        <v>180.09</v>
+        <v>122.3</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>155.38</v>
+        <v>102.95</v>
       </c>
       <c r="K26" t="n">
-        <v>-198.44</v>
+        <v>-131.49</v>
       </c>
       <c r="L26" t="n">
-        <v>252.03</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>281.17</v>
+        <v>210.88</v>
       </c>
       <c r="K27" t="n">
-        <v>140.88</v>
+        <v>105.66</v>
       </c>
       <c r="L27" t="n">
-        <v>314.49</v>
+        <v>235.87</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-105.19</v>
+        <v>-64.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>467.55</v>
+        <v>287.13</v>
       </c>
       <c r="L28" t="n">
-        <v>479.24</v>
+        <v>294.3</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>14.6</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>75.84999999999999</v>
+        <v>49.99</v>
       </c>
       <c r="L29" t="n">
-        <v>77.23999999999999</v>
+        <v>50.91</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>51.41</v>
+        <v>33.62</v>
       </c>
       <c r="K30" t="n">
-        <v>-59.82</v>
+        <v>-39.12</v>
       </c>
       <c r="L30" t="n">
-        <v>78.88</v>
+        <v>51.58</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-69.48</v>
+        <v>-42.11</v>
       </c>
       <c r="K31" t="n">
-        <v>-123.62</v>
+        <v>-74.92</v>
       </c>
       <c r="L31" t="n">
-        <v>141.81</v>
+        <v>85.94</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-43.33</v>
+        <v>-25.46</v>
       </c>
       <c r="K32" t="n">
-        <v>-115.48</v>
+        <v>-67.86</v>
       </c>
       <c r="L32" t="n">
-        <v>123.34</v>
+        <v>72.48</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-126.52</v>
+        <v>-77.93000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>120.12</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>174.46</v>
+        <v>107.46</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-54.9</v>
+        <v>-41.17</v>
       </c>
       <c r="K34" t="n">
-        <v>80.12</v>
+        <v>60.09</v>
       </c>
       <c r="L34" t="n">
-        <v>97.12</v>
+        <v>72.84</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-255.58</v>
+        <v>-151.37</v>
       </c>
       <c r="K35" t="n">
-        <v>-116.22</v>
+        <v>-68.83</v>
       </c>
       <c r="L35" t="n">
-        <v>280.77</v>
+        <v>166.29</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-45.54</v>
+        <v>-29.51</v>
       </c>
       <c r="K36" t="n">
-        <v>248.45</v>
+        <v>160.97</v>
       </c>
       <c r="L36" t="n">
-        <v>252.59</v>
+        <v>163.65</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>73.93000000000001</v>
+        <v>50.48</v>
       </c>
       <c r="K37" t="n">
-        <v>96.94</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>121.91</v>
+        <v>83.23999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>193.05</v>
+        <v>126.55</v>
       </c>
       <c r="K38" t="n">
-        <v>9.529999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="L38" t="n">
-        <v>193.29</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-192.96</v>
+        <v>-143.6</v>
       </c>
       <c r="K39" t="n">
-        <v>70.43000000000001</v>
+        <v>52.41</v>
       </c>
       <c r="L39" t="n">
-        <v>205.41</v>
+        <v>152.87</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-144.62</v>
+        <v>-94.27</v>
       </c>
       <c r="K40" t="n">
-        <v>-23.97</v>
+        <v>-15.62</v>
       </c>
       <c r="L40" t="n">
-        <v>146.59</v>
+        <v>95.56</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>488.5</v>
+        <v>308.58</v>
       </c>
       <c r="K41" t="n">
-        <v>49.9</v>
+        <v>31.52</v>
       </c>
       <c r="L41" t="n">
-        <v>491.04</v>
+        <v>310.18</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-108.88</v>
+        <v>-80.86</v>
       </c>
       <c r="K42" t="n">
-        <v>-193.83</v>
+        <v>-143.96</v>
       </c>
       <c r="L42" t="n">
-        <v>222.32</v>
+        <v>165.11</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-260.04</v>
+        <v>-165.54</v>
       </c>
       <c r="K43" t="n">
-        <v>279.16</v>
+        <v>177.71</v>
       </c>
       <c r="L43" t="n">
-        <v>381.51</v>
+        <v>242.87</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>146.69</v>
+        <v>89.08</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.78</v>
+        <v>-1.08</v>
       </c>
       <c r="L44" t="n">
-        <v>146.7</v>
+        <v>89.09</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>38.28</v>
+        <v>28.71</v>
       </c>
       <c r="K45" t="n">
-        <v>-47.81</v>
+        <v>-35.86</v>
       </c>
       <c r="L45" t="n">
-        <v>61.25</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-137.5</v>
+        <v>-81.26000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>84.54000000000001</v>
+        <v>49.96</v>
       </c>
       <c r="L46" t="n">
-        <v>161.41</v>
+        <v>95.39</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-126.71</v>
+        <v>-77.7</v>
       </c>
       <c r="K47" t="n">
-        <v>-148.15</v>
+        <v>-90.84999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>194.95</v>
+        <v>119.54</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-77.09999999999999</v>
+        <v>-44.25</v>
       </c>
       <c r="K48" t="n">
-        <v>47.43</v>
+        <v>27.22</v>
       </c>
       <c r="L48" t="n">
-        <v>90.52</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>63.32</v>
+        <v>34.66</v>
       </c>
       <c r="K49" t="n">
-        <v>-140.51</v>
+        <v>-76.91</v>
       </c>
       <c r="L49" t="n">
-        <v>154.12</v>
+        <v>84.36</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>88.90000000000001</v>
+        <v>58.82</v>
       </c>
       <c r="K50" t="n">
-        <v>103.07</v>
+        <v>68.19</v>
       </c>
       <c r="L50" t="n">
-        <v>136.11</v>
+        <v>90.06</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>11.42</v>
+        <v>6.92</v>
       </c>
       <c r="K51" t="n">
-        <v>273.06</v>
+        <v>165.5</v>
       </c>
       <c r="L51" t="n">
-        <v>273.3</v>
+        <v>165.64</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-82.04000000000001</v>
+        <v>-48.59</v>
       </c>
       <c r="K52" t="n">
-        <v>-113.63</v>
+        <v>-67.3</v>
       </c>
       <c r="L52" t="n">
-        <v>140.15</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>4.92</v>
+        <v>3.16</v>
       </c>
       <c r="K53" t="n">
-        <v>-209.33</v>
+        <v>-134.48</v>
       </c>
       <c r="L53" t="n">
-        <v>209.39</v>
+        <v>134.52</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>168.16</v>
+        <v>110.23</v>
       </c>
       <c r="K54" t="n">
-        <v>-146.06</v>
+        <v>-95.73999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>222.74</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-300.61</v>
+        <v>-197.42</v>
       </c>
       <c r="K55" t="n">
-        <v>100.03</v>
+        <v>65.69</v>
       </c>
       <c r="L55" t="n">
-        <v>316.82</v>
+        <v>208.06</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>117.66</v>
+        <v>76.7</v>
       </c>
       <c r="K56" t="n">
-        <v>466.78</v>
+        <v>304.29</v>
       </c>
       <c r="L56" t="n">
-        <v>481.38</v>
+        <v>313.81</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>381.21</v>
+        <v>220.14</v>
       </c>
       <c r="K57" t="n">
-        <v>147.48</v>
+        <v>85.17</v>
       </c>
       <c r="L57" t="n">
-        <v>408.74</v>
+        <v>236.04</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-206.6</v>
+        <v>-136.05</v>
       </c>
       <c r="K58" t="n">
-        <v>-335.24</v>
+        <v>-220.77</v>
       </c>
       <c r="L58" t="n">
-        <v>393.79</v>
+        <v>259.33</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-72.66</v>
+        <v>-45.79</v>
       </c>
       <c r="K59" t="n">
-        <v>-19.61</v>
+        <v>-12.36</v>
       </c>
       <c r="L59" t="n">
-        <v>75.26000000000001</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-16.41</v>
+        <v>-10.54</v>
       </c>
       <c r="K60" t="n">
-        <v>132.33</v>
+        <v>85</v>
       </c>
       <c r="L60" t="n">
-        <v>133.34</v>
+        <v>85.65000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>104.85</v>
+        <v>62.08</v>
       </c>
       <c r="K61" t="n">
-        <v>4.2</v>
+        <v>2.48</v>
       </c>
       <c r="L61" t="n">
-        <v>104.93</v>
+        <v>62.13</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>93.2</v>
+        <v>59.45</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.81</v>
+        <v>-1.79</v>
       </c>
       <c r="L62" t="n">
-        <v>93.23999999999999</v>
+        <v>59.48</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-156.8</v>
+        <v>-94.08</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.12</v>
+        <v>-1.27</v>
       </c>
       <c r="L63" t="n">
-        <v>156.81</v>
+        <v>94.09</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>176.5</v>
+        <v>110.99</v>
       </c>
       <c r="K64" t="n">
-        <v>-73.28</v>
+        <v>-46.08</v>
       </c>
       <c r="L64" t="n">
-        <v>191.11</v>
+        <v>120.18</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>72.33</v>
+        <v>10.01</v>
       </c>
       <c r="K65" t="n">
-        <v>-83.70999999999999</v>
+        <v>-11.59</v>
       </c>
       <c r="L65" t="n">
-        <v>110.63</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-257.09</v>
+        <v>-147.16</v>
       </c>
       <c r="K66" t="n">
-        <v>-112.81</v>
+        <v>-64.56999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>280.75</v>
+        <v>160.7</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-193.46</v>
+        <v>-108.7</v>
       </c>
       <c r="K67" t="n">
-        <v>76.76000000000001</v>
+        <v>43.13</v>
       </c>
       <c r="L67" t="n">
-        <v>208.13</v>
+        <v>116.95</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-126.25</v>
+        <v>-73.05</v>
       </c>
       <c r="K68" t="n">
-        <v>-150.8</v>
+        <v>-87.25</v>
       </c>
       <c r="L68" t="n">
-        <v>196.68</v>
+        <v>113.79</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-225.76</v>
+        <v>-153</v>
       </c>
       <c r="K69" t="n">
-        <v>-134.99</v>
+        <v>-91.48</v>
       </c>
       <c r="L69" t="n">
-        <v>263.04</v>
+        <v>178.26</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-77.61</v>
+        <v>-6.29</v>
       </c>
       <c r="K70" t="n">
-        <v>-90.47</v>
+        <v>-7.34</v>
       </c>
       <c r="L70" t="n">
-        <v>119.2</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>289.6</v>
+        <v>170.99</v>
       </c>
       <c r="K71" t="n">
-        <v>127.76</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>316.53</v>
+        <v>186.89</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-220.4</v>
+        <v>-129.68</v>
       </c>
       <c r="K72" t="n">
-        <v>390.22</v>
+        <v>229.6</v>
       </c>
       <c r="L72" t="n">
-        <v>448.16</v>
+        <v>263.69</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>10.77</v>
+        <v>6.55</v>
       </c>
       <c r="K73" t="n">
-        <v>435.86</v>
+        <v>265.23</v>
       </c>
       <c r="L73" t="n">
-        <v>435.99</v>
+        <v>265.31</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-53.3</v>
+        <v>-30.73</v>
       </c>
       <c r="K74" t="n">
-        <v>-72.42</v>
+        <v>-41.76</v>
       </c>
       <c r="L74" t="n">
-        <v>89.92</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-46.39</v>
+        <v>-29.16</v>
       </c>
       <c r="K75" t="n">
-        <v>66.25</v>
+        <v>41.65</v>
       </c>
       <c r="L75" t="n">
-        <v>80.87</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-73.48</v>
+        <v>-39.64</v>
       </c>
       <c r="K76" t="n">
-        <v>40.81</v>
+        <v>22.01</v>
       </c>
       <c r="L76" t="n">
-        <v>84.05</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>54.97</v>
+        <v>31.92</v>
       </c>
       <c r="K77" t="n">
-        <v>148.93</v>
+        <v>86.48</v>
       </c>
       <c r="L77" t="n">
-        <v>158.75</v>
+        <v>92.18000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>93.26000000000001</v>
+        <v>54.04</v>
       </c>
       <c r="K78" t="n">
-        <v>-12.55</v>
+        <v>-7.27</v>
       </c>
       <c r="L78" t="n">
-        <v>94.09999999999999</v>
+        <v>54.53</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>33.35</v>
+        <v>22.04</v>
       </c>
       <c r="K79" t="n">
-        <v>154.43</v>
+        <v>102.04</v>
       </c>
       <c r="L79" t="n">
-        <v>157.99</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>67.01000000000001</v>
+        <v>40.3</v>
       </c>
       <c r="K80" t="n">
-        <v>-133.58</v>
+        <v>-80.33</v>
       </c>
       <c r="L80" t="n">
-        <v>149.44</v>
+        <v>89.87</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>103.44</v>
+        <v>52.48</v>
       </c>
       <c r="K81" t="n">
-        <v>194.47</v>
+        <v>98.67</v>
       </c>
       <c r="L81" t="n">
-        <v>220.27</v>
+        <v>111.75</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-83.61</v>
+        <v>-44.88</v>
       </c>
       <c r="K82" t="n">
-        <v>130.92</v>
+        <v>70.27</v>
       </c>
       <c r="L82" t="n">
-        <v>155.34</v>
+        <v>83.38</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>363.16</v>
+        <v>225.12</v>
       </c>
       <c r="K83" t="n">
-        <v>-21.13</v>
+        <v>-13.1</v>
       </c>
       <c r="L83" t="n">
-        <v>363.77</v>
+        <v>225.5</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>56.72</v>
+        <v>40.13</v>
       </c>
       <c r="K84" t="n">
-        <v>192.66</v>
+        <v>136.32</v>
       </c>
       <c r="L84" t="n">
-        <v>200.84</v>
+        <v>142.1</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-88.13</v>
+        <v>-54.2</v>
       </c>
       <c r="K85" t="n">
-        <v>224.58</v>
+        <v>138.11</v>
       </c>
       <c r="L85" t="n">
-        <v>241.26</v>
+        <v>148.36</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>183.95</v>
+        <v>123.42</v>
       </c>
       <c r="K86" t="n">
-        <v>-73.28</v>
+        <v>-49.17</v>
       </c>
       <c r="L86" t="n">
-        <v>198.01</v>
+        <v>132.85</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-144.66</v>
+        <v>-95.65000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>463.86</v>
+        <v>306.73</v>
       </c>
       <c r="L87" t="n">
-        <v>485.9</v>
+        <v>321.3</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-373.22</v>
+        <v>-222.29</v>
       </c>
       <c r="K88" t="n">
-        <v>110.96</v>
+        <v>66.09</v>
       </c>
       <c r="L88" t="n">
-        <v>389.36</v>
+        <v>231.91</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-09.xlsx
+++ b/output/2025-08-09.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>17.42</v>
+        <v>17.61</v>
       </c>
       <c r="K14" t="n">
-        <v>54.06</v>
+        <v>54.64</v>
       </c>
       <c r="L14" t="n">
-        <v>56.8</v>
+        <v>57.41</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>30.67</v>
+        <v>32.53</v>
       </c>
       <c r="K15" t="n">
-        <v>-28.92</v>
+        <v>-30.68</v>
       </c>
       <c r="L15" t="n">
-        <v>42.15</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-46.45</v>
+        <v>-45.81</v>
       </c>
       <c r="K16" t="n">
-        <v>53.81</v>
+        <v>53.06</v>
       </c>
       <c r="L16" t="n">
-        <v>71.09</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>81.7</v>
+        <v>80.19</v>
       </c>
       <c r="K17" t="n">
-        <v>-61.44</v>
+        <v>-60.3</v>
       </c>
       <c r="L17" t="n">
-        <v>102.22</v>
+        <v>100.34</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>60.35</v>
+        <v>62.54</v>
       </c>
       <c r="K18" t="n">
-        <v>18.16</v>
+        <v>18.81</v>
       </c>
       <c r="L18" t="n">
-        <v>63.02</v>
+        <v>65.31</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-43.9</v>
+        <v>-46.56</v>
       </c>
       <c r="K19" t="n">
-        <v>-33.27</v>
+        <v>-35.28</v>
       </c>
       <c r="L19" t="n">
-        <v>55.08</v>
+        <v>58.42</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-38.12</v>
+        <v>-40.29</v>
       </c>
       <c r="K20" t="n">
-        <v>71.91</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>81.39</v>
+        <v>86.03</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>105.12</v>
+        <v>105.32</v>
       </c>
       <c r="K21" t="n">
-        <v>-45.88</v>
+        <v>-45.97</v>
       </c>
       <c r="L21" t="n">
-        <v>114.7</v>
+        <v>114.91</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-127.86</v>
+        <v>-126.94</v>
       </c>
       <c r="K22" t="n">
-        <v>-12.01</v>
+        <v>-11.92</v>
       </c>
       <c r="L22" t="n">
-        <v>128.42</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>167.05</v>
+        <v>163.24</v>
       </c>
       <c r="K23" t="n">
-        <v>-116.19</v>
+        <v>-113.54</v>
       </c>
       <c r="L23" t="n">
-        <v>203.48</v>
+        <v>198.85</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>96.90000000000001</v>
+        <v>99.36</v>
       </c>
       <c r="K24" t="n">
-        <v>-78.76000000000001</v>
+        <v>-80.76000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>124.88</v>
+        <v>128.04</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-68.91</v>
+        <v>-71.20999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-101.03</v>
+        <v>-104.4</v>
       </c>
       <c r="L25" t="n">
-        <v>122.3</v>
+        <v>126.37</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>102.95</v>
+        <v>107.38</v>
       </c>
       <c r="K26" t="n">
-        <v>-131.49</v>
+        <v>-137.13</v>
       </c>
       <c r="L26" t="n">
-        <v>167</v>
+        <v>174.17</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>210.88</v>
+        <v>207.63</v>
       </c>
       <c r="K27" t="n">
-        <v>105.66</v>
+        <v>104.03</v>
       </c>
       <c r="L27" t="n">
-        <v>235.87</v>
+        <v>232.23</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-64.59999999999999</v>
+        <v>-62.88</v>
       </c>
       <c r="K28" t="n">
-        <v>287.13</v>
+        <v>279.49</v>
       </c>
       <c r="L28" t="n">
-        <v>294.3</v>
+        <v>286.48</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>9.619999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="K29" t="n">
-        <v>49.99</v>
+        <v>51.59</v>
       </c>
       <c r="L29" t="n">
-        <v>50.91</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>33.62</v>
+        <v>34.69</v>
       </c>
       <c r="K30" t="n">
-        <v>-39.12</v>
+        <v>-40.36</v>
       </c>
       <c r="L30" t="n">
-        <v>51.58</v>
+        <v>53.21</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-42.11</v>
+        <v>-41.07</v>
       </c>
       <c r="K31" t="n">
-        <v>-74.92</v>
+        <v>-73.06</v>
       </c>
       <c r="L31" t="n">
-        <v>85.94</v>
+        <v>83.81</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-25.46</v>
+        <v>-26.21</v>
       </c>
       <c r="K32" t="n">
-        <v>-67.86</v>
+        <v>-69.86</v>
       </c>
       <c r="L32" t="n">
-        <v>72.48</v>
+        <v>74.62</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-77.93000000000001</v>
+        <v>-76.13</v>
       </c>
       <c r="K33" t="n">
-        <v>73.98999999999999</v>
+        <v>72.28</v>
       </c>
       <c r="L33" t="n">
-        <v>107.46</v>
+        <v>104.97</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-41.17</v>
+        <v>-41.61</v>
       </c>
       <c r="K34" t="n">
-        <v>60.09</v>
+        <v>60.74</v>
       </c>
       <c r="L34" t="n">
-        <v>72.84</v>
+        <v>73.63</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-151.37</v>
+        <v>-146.73</v>
       </c>
       <c r="K35" t="n">
-        <v>-68.83</v>
+        <v>-66.72</v>
       </c>
       <c r="L35" t="n">
-        <v>166.29</v>
+        <v>161.19</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-29.51</v>
+        <v>-28.51</v>
       </c>
       <c r="K36" t="n">
-        <v>160.97</v>
+        <v>155.52</v>
       </c>
       <c r="L36" t="n">
-        <v>163.65</v>
+        <v>158.11</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>50.48</v>
+        <v>53.12</v>
       </c>
       <c r="K37" t="n">
-        <v>66.18000000000001</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>83.23999999999999</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>126.55</v>
+        <v>131.28</v>
       </c>
       <c r="K38" t="n">
-        <v>6.25</v>
+        <v>6.48</v>
       </c>
       <c r="L38" t="n">
-        <v>126.7</v>
+        <v>131.44</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-143.6</v>
+        <v>-143.16</v>
       </c>
       <c r="K39" t="n">
-        <v>52.41</v>
+        <v>52.25</v>
       </c>
       <c r="L39" t="n">
-        <v>152.87</v>
+        <v>152.4</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-94.27</v>
+        <v>-102.74</v>
       </c>
       <c r="K40" t="n">
-        <v>-15.62</v>
+        <v>-17.03</v>
       </c>
       <c r="L40" t="n">
-        <v>95.56</v>
+        <v>104.14</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>308.58</v>
+        <v>300.06</v>
       </c>
       <c r="K41" t="n">
-        <v>31.52</v>
+        <v>30.65</v>
       </c>
       <c r="L41" t="n">
-        <v>310.18</v>
+        <v>301.62</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-80.86</v>
+        <v>-84.03</v>
       </c>
       <c r="K42" t="n">
-        <v>-143.96</v>
+        <v>-149.59</v>
       </c>
       <c r="L42" t="n">
-        <v>165.11</v>
+        <v>171.58</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-165.54</v>
+        <v>-165.03</v>
       </c>
       <c r="K43" t="n">
-        <v>177.71</v>
+        <v>177.16</v>
       </c>
       <c r="L43" t="n">
-        <v>242.87</v>
+        <v>242.12</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>89.08</v>
+        <v>86.59</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.08</v>
+        <v>-1.05</v>
       </c>
       <c r="L44" t="n">
-        <v>89.09</v>
+        <v>86.59</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>28.71</v>
+        <v>29.41</v>
       </c>
       <c r="K45" t="n">
-        <v>-35.86</v>
+        <v>-36.73</v>
       </c>
       <c r="L45" t="n">
-        <v>45.94</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-81.26000000000001</v>
+        <v>-78.44</v>
       </c>
       <c r="K46" t="n">
-        <v>49.96</v>
+        <v>48.23</v>
       </c>
       <c r="L46" t="n">
-        <v>95.39</v>
+        <v>92.08</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-77.7</v>
+        <v>-74.98</v>
       </c>
       <c r="K47" t="n">
-        <v>-90.84999999999999</v>
+        <v>-87.67</v>
       </c>
       <c r="L47" t="n">
-        <v>119.54</v>
+        <v>115.36</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-44.25</v>
+        <v>-47.84</v>
       </c>
       <c r="K48" t="n">
-        <v>27.22</v>
+        <v>29.43</v>
       </c>
       <c r="L48" t="n">
-        <v>51.95</v>
+        <v>56.17</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>34.66</v>
+        <v>35.12</v>
       </c>
       <c r="K49" t="n">
-        <v>-76.91</v>
+        <v>-77.93000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>84.36</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>58.82</v>
+        <v>60.97</v>
       </c>
       <c r="K50" t="n">
-        <v>68.19</v>
+        <v>70.69</v>
       </c>
       <c r="L50" t="n">
-        <v>90.06</v>
+        <v>93.34999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>6.92</v>
+        <v>6.69</v>
       </c>
       <c r="K51" t="n">
-        <v>165.5</v>
+        <v>159.91</v>
       </c>
       <c r="L51" t="n">
-        <v>165.64</v>
+        <v>160.05</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-48.59</v>
+        <v>-51.34</v>
       </c>
       <c r="K52" t="n">
-        <v>-67.3</v>
+        <v>-71.11</v>
       </c>
       <c r="L52" t="n">
-        <v>83</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="K53" t="n">
-        <v>-134.48</v>
+        <v>-138.25</v>
       </c>
       <c r="L53" t="n">
-        <v>134.52</v>
+        <v>138.29</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>110.23</v>
+        <v>111.62</v>
       </c>
       <c r="K54" t="n">
-        <v>-95.73999999999999</v>
+        <v>-96.95</v>
       </c>
       <c r="L54" t="n">
-        <v>146</v>
+        <v>147.84</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-197.42</v>
+        <v>-191.31</v>
       </c>
       <c r="K55" t="n">
-        <v>65.69</v>
+        <v>63.66</v>
       </c>
       <c r="L55" t="n">
-        <v>208.06</v>
+        <v>201.62</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>76.7</v>
+        <v>74.12</v>
       </c>
       <c r="K56" t="n">
-        <v>304.29</v>
+        <v>294.05</v>
       </c>
       <c r="L56" t="n">
-        <v>313.81</v>
+        <v>303.25</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>220.14</v>
+        <v>220.77</v>
       </c>
       <c r="K57" t="n">
-        <v>85.17</v>
+        <v>85.41</v>
       </c>
       <c r="L57" t="n">
-        <v>236.04</v>
+        <v>236.72</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-136.05</v>
+        <v>-134.04</v>
       </c>
       <c r="K58" t="n">
-        <v>-220.77</v>
+        <v>-217.5</v>
       </c>
       <c r="L58" t="n">
-        <v>259.33</v>
+        <v>255.49</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-45.79</v>
+        <v>-47.72</v>
       </c>
       <c r="K59" t="n">
-        <v>-12.36</v>
+        <v>-12.88</v>
       </c>
       <c r="L59" t="n">
-        <v>47.43</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.54</v>
+        <v>-10.21</v>
       </c>
       <c r="K60" t="n">
-        <v>85</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>85.65000000000001</v>
+        <v>82.95</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>62.08</v>
+        <v>63.09</v>
       </c>
       <c r="K61" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="L61" t="n">
-        <v>62.13</v>
+        <v>63.15</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>59.45</v>
+        <v>62.1</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.79</v>
+        <v>-1.87</v>
       </c>
       <c r="L62" t="n">
-        <v>59.48</v>
+        <v>62.13</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-94.08</v>
+        <v>-93.15000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.27</v>
+        <v>-1.26</v>
       </c>
       <c r="L63" t="n">
-        <v>94.09</v>
+        <v>93.16</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>110.99</v>
+        <v>107</v>
       </c>
       <c r="K64" t="n">
-        <v>-46.08</v>
+        <v>-44.42</v>
       </c>
       <c r="L64" t="n">
-        <v>120.18</v>
+        <v>115.85</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>10.01</v>
+        <v>9.85</v>
       </c>
       <c r="K65" t="n">
-        <v>-11.59</v>
+        <v>-11.4</v>
       </c>
       <c r="L65" t="n">
-        <v>15.31</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-147.16</v>
+        <v>-142.95</v>
       </c>
       <c r="K66" t="n">
-        <v>-64.56999999999999</v>
+        <v>-62.73</v>
       </c>
       <c r="L66" t="n">
-        <v>160.7</v>
+        <v>156.11</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-108.7</v>
+        <v>-109.52</v>
       </c>
       <c r="K67" t="n">
-        <v>43.13</v>
+        <v>43.45</v>
       </c>
       <c r="L67" t="n">
-        <v>116.95</v>
+        <v>117.83</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-73.05</v>
+        <v>-78.44</v>
       </c>
       <c r="K68" t="n">
-        <v>-87.25</v>
+        <v>-93.69</v>
       </c>
       <c r="L68" t="n">
-        <v>113.79</v>
+        <v>122.19</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-153</v>
+        <v>-150.7</v>
       </c>
       <c r="K69" t="n">
-        <v>-91.48</v>
+        <v>-90.09999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>178.26</v>
+        <v>175.58</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.29</v>
+        <v>-6.22</v>
       </c>
       <c r="K70" t="n">
-        <v>-7.34</v>
+        <v>-7.25</v>
       </c>
       <c r="L70" t="n">
-        <v>9.67</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>170.99</v>
+        <v>176.49</v>
       </c>
       <c r="K71" t="n">
-        <v>75.43000000000001</v>
+        <v>77.86</v>
       </c>
       <c r="L71" t="n">
-        <v>186.89</v>
+        <v>192.9</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-129.68</v>
+        <v>-127.92</v>
       </c>
       <c r="K72" t="n">
-        <v>229.6</v>
+        <v>226.49</v>
       </c>
       <c r="L72" t="n">
-        <v>263.69</v>
+        <v>260.12</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>6.55</v>
+        <v>6.46</v>
       </c>
       <c r="K73" t="n">
-        <v>265.23</v>
+        <v>261.54</v>
       </c>
       <c r="L73" t="n">
-        <v>265.31</v>
+        <v>261.62</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-30.73</v>
+        <v>-32.29</v>
       </c>
       <c r="K74" t="n">
-        <v>-41.76</v>
+        <v>-43.88</v>
       </c>
       <c r="L74" t="n">
-        <v>51.85</v>
+        <v>54.48</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-29.16</v>
+        <v>-30.19</v>
       </c>
       <c r="K75" t="n">
-        <v>41.65</v>
+        <v>43.12</v>
       </c>
       <c r="L75" t="n">
-        <v>50.85</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-39.64</v>
+        <v>-43.25</v>
       </c>
       <c r="K76" t="n">
-        <v>22.01</v>
+        <v>24.02</v>
       </c>
       <c r="L76" t="n">
-        <v>45.34</v>
+        <v>49.47</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>31.92</v>
+        <v>31.77</v>
       </c>
       <c r="K77" t="n">
-        <v>86.48</v>
+        <v>86.09</v>
       </c>
       <c r="L77" t="n">
-        <v>92.18000000000001</v>
+        <v>91.76000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>54.04</v>
+        <v>58.09</v>
       </c>
       <c r="K78" t="n">
-        <v>-7.27</v>
+        <v>-7.82</v>
       </c>
       <c r="L78" t="n">
-        <v>54.53</v>
+        <v>58.61</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>22.04</v>
+        <v>21.46</v>
       </c>
       <c r="K79" t="n">
-        <v>102.04</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>104.4</v>
+        <v>101.69</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>40.3</v>
+        <v>41.85</v>
       </c>
       <c r="K80" t="n">
-        <v>-80.33</v>
+        <v>-83.43000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>89.87</v>
+        <v>93.34</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>52.48</v>
+        <v>53.63</v>
       </c>
       <c r="K81" t="n">
-        <v>98.67</v>
+        <v>100.82</v>
       </c>
       <c r="L81" t="n">
-        <v>111.75</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-44.88</v>
+        <v>-47.68</v>
       </c>
       <c r="K82" t="n">
-        <v>70.27</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>83.38</v>
+        <v>88.58</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>225.12</v>
+        <v>218.27</v>
       </c>
       <c r="K83" t="n">
-        <v>-13.1</v>
+        <v>-12.7</v>
       </c>
       <c r="L83" t="n">
-        <v>225.5</v>
+        <v>218.64</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>40.13</v>
+        <v>40.24</v>
       </c>
       <c r="K84" t="n">
-        <v>136.32</v>
+        <v>136.68</v>
       </c>
       <c r="L84" t="n">
-        <v>142.1</v>
+        <v>142.48</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-54.2</v>
+        <v>-54.95</v>
       </c>
       <c r="K85" t="n">
-        <v>138.11</v>
+        <v>140.04</v>
       </c>
       <c r="L85" t="n">
-        <v>148.36</v>
+        <v>150.43</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>123.42</v>
+        <v>133.9</v>
       </c>
       <c r="K86" t="n">
-        <v>-49.17</v>
+        <v>-53.35</v>
       </c>
       <c r="L86" t="n">
-        <v>132.85</v>
+        <v>144.14</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-95.65000000000001</v>
+        <v>-92.2</v>
       </c>
       <c r="K87" t="n">
-        <v>306.73</v>
+        <v>295.66</v>
       </c>
       <c r="L87" t="n">
-        <v>321.3</v>
+        <v>309.7</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-222.29</v>
+        <v>-222.56</v>
       </c>
       <c r="K88" t="n">
-        <v>66.09</v>
+        <v>66.17</v>
       </c>
       <c r="L88" t="n">
-        <v>231.91</v>
+        <v>232.19</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-09.xlsx
+++ b/output/2025-08-09.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>17.61</v>
+        <v>17.82</v>
       </c>
       <c r="K14" t="n">
-        <v>54.64</v>
+        <v>55.31</v>
       </c>
       <c r="L14" t="n">
-        <v>57.41</v>
+        <v>58.11</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>32.53</v>
+        <v>34.66</v>
       </c>
       <c r="K15" t="n">
-        <v>-30.68</v>
+        <v>-32.68</v>
       </c>
       <c r="L15" t="n">
-        <v>44.71</v>
+        <v>47.64</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-45.81</v>
+        <v>-45.07</v>
       </c>
       <c r="K16" t="n">
-        <v>53.06</v>
+        <v>52.21</v>
       </c>
       <c r="L16" t="n">
-        <v>70.09999999999999</v>
+        <v>68.97</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>80.19</v>
+        <v>78.47</v>
       </c>
       <c r="K17" t="n">
-        <v>-60.3</v>
+        <v>-59.01</v>
       </c>
       <c r="L17" t="n">
-        <v>100.34</v>
+        <v>98.18000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>62.54</v>
+        <v>65.03</v>
       </c>
       <c r="K18" t="n">
-        <v>18.81</v>
+        <v>19.57</v>
       </c>
       <c r="L18" t="n">
-        <v>65.31</v>
+        <v>67.91</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-46.56</v>
+        <v>-49.59</v>
       </c>
       <c r="K19" t="n">
-        <v>-35.28</v>
+        <v>-37.58</v>
       </c>
       <c r="L19" t="n">
-        <v>58.42</v>
+        <v>62.22</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-40.29</v>
+        <v>-42.78</v>
       </c>
       <c r="K20" t="n">
-        <v>76.01000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="L20" t="n">
-        <v>86.03</v>
+        <v>91.33</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>105.32</v>
+        <v>105.55</v>
       </c>
       <c r="K21" t="n">
-        <v>-45.97</v>
+        <v>-46.07</v>
       </c>
       <c r="L21" t="n">
-        <v>114.91</v>
+        <v>115.16</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-126.94</v>
+        <v>-125.89</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.92</v>
+        <v>-11.82</v>
       </c>
       <c r="L22" t="n">
-        <v>127.5</v>
+        <v>126.44</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>163.24</v>
+        <v>158.9</v>
       </c>
       <c r="K23" t="n">
-        <v>-113.54</v>
+        <v>-110.52</v>
       </c>
       <c r="L23" t="n">
-        <v>198.85</v>
+        <v>193.56</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>99.36</v>
+        <v>102.16</v>
       </c>
       <c r="K24" t="n">
-        <v>-80.76000000000001</v>
+        <v>-83.03</v>
       </c>
       <c r="L24" t="n">
-        <v>128.04</v>
+        <v>131.65</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-71.20999999999999</v>
+        <v>-73.83</v>
       </c>
       <c r="K25" t="n">
-        <v>-104.4</v>
+        <v>-108.25</v>
       </c>
       <c r="L25" t="n">
-        <v>126.37</v>
+        <v>131.03</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>107.38</v>
+        <v>112.43</v>
       </c>
       <c r="K26" t="n">
-        <v>-137.13</v>
+        <v>-143.59</v>
       </c>
       <c r="L26" t="n">
-        <v>174.17</v>
+        <v>182.37</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>207.63</v>
+        <v>203.92</v>
       </c>
       <c r="K27" t="n">
-        <v>104.03</v>
+        <v>102.17</v>
       </c>
       <c r="L27" t="n">
-        <v>232.23</v>
+        <v>228.08</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-62.88</v>
+        <v>-60.91</v>
       </c>
       <c r="K28" t="n">
-        <v>279.49</v>
+        <v>270.77</v>
       </c>
       <c r="L28" t="n">
-        <v>286.48</v>
+        <v>277.53</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>9.93</v>
+        <v>10.28</v>
       </c>
       <c r="K29" t="n">
-        <v>51.59</v>
+        <v>53.43</v>
       </c>
       <c r="L29" t="n">
-        <v>52.54</v>
+        <v>54.41</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>34.69</v>
+        <v>35.91</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.36</v>
+        <v>-41.78</v>
       </c>
       <c r="L30" t="n">
-        <v>53.21</v>
+        <v>55.09</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-41.07</v>
+        <v>-39.87</v>
       </c>
       <c r="K31" t="n">
-        <v>-73.06</v>
+        <v>-70.94</v>
       </c>
       <c r="L31" t="n">
-        <v>83.81</v>
+        <v>81.38</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-26.21</v>
+        <v>-27.07</v>
       </c>
       <c r="K32" t="n">
-        <v>-69.86</v>
+        <v>-72.14</v>
       </c>
       <c r="L32" t="n">
-        <v>74.62</v>
+        <v>77.05</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-76.13</v>
+        <v>-74.06999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>72.28</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>104.97</v>
+        <v>102.14</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-41.61</v>
+        <v>-42.12</v>
       </c>
       <c r="K34" t="n">
-        <v>60.74</v>
+        <v>61.48</v>
       </c>
       <c r="L34" t="n">
-        <v>73.63</v>
+        <v>74.52</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-146.73</v>
+        <v>-141.43</v>
       </c>
       <c r="K35" t="n">
-        <v>-66.72</v>
+        <v>-64.31</v>
       </c>
       <c r="L35" t="n">
-        <v>161.19</v>
+        <v>155.37</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-28.51</v>
+        <v>-27.37</v>
       </c>
       <c r="K36" t="n">
-        <v>155.52</v>
+        <v>149.29</v>
       </c>
       <c r="L36" t="n">
-        <v>158.11</v>
+        <v>151.78</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>53.12</v>
+        <v>56.15</v>
       </c>
       <c r="K37" t="n">
-        <v>69.65000000000001</v>
+        <v>73.61</v>
       </c>
       <c r="L37" t="n">
-        <v>87.59999999999999</v>
+        <v>92.58</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>131.28</v>
+        <v>136.7</v>
       </c>
       <c r="K38" t="n">
-        <v>6.48</v>
+        <v>6.75</v>
       </c>
       <c r="L38" t="n">
-        <v>131.44</v>
+        <v>136.87</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-143.16</v>
+        <v>-142.66</v>
       </c>
       <c r="K39" t="n">
-        <v>52.25</v>
+        <v>52.07</v>
       </c>
       <c r="L39" t="n">
-        <v>152.4</v>
+        <v>151.86</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-102.74</v>
+        <v>-112.41</v>
       </c>
       <c r="K40" t="n">
-        <v>-17.03</v>
+        <v>-18.63</v>
       </c>
       <c r="L40" t="n">
-        <v>104.14</v>
+        <v>113.95</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>300.06</v>
+        <v>290.33</v>
       </c>
       <c r="K41" t="n">
-        <v>30.65</v>
+        <v>29.66</v>
       </c>
       <c r="L41" t="n">
-        <v>301.62</v>
+        <v>291.84</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-84.03</v>
+        <v>-87.65000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>-149.59</v>
+        <v>-156.04</v>
       </c>
       <c r="L42" t="n">
-        <v>171.58</v>
+        <v>178.97</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-165.03</v>
+        <v>-164.46</v>
       </c>
       <c r="K43" t="n">
-        <v>177.16</v>
+        <v>176.54</v>
       </c>
       <c r="L43" t="n">
-        <v>242.12</v>
+        <v>241.27</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>86.59</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.05</v>
+        <v>-1.02</v>
       </c>
       <c r="L44" t="n">
-        <v>86.59</v>
+        <v>83.73999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>29.41</v>
+        <v>30.21</v>
       </c>
       <c r="K45" t="n">
-        <v>-36.73</v>
+        <v>-37.73</v>
       </c>
       <c r="L45" t="n">
-        <v>47.05</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-78.44</v>
+        <v>-75.22</v>
       </c>
       <c r="K46" t="n">
-        <v>48.23</v>
+        <v>46.25</v>
       </c>
       <c r="L46" t="n">
-        <v>92.08</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-74.98</v>
+        <v>-71.87</v>
       </c>
       <c r="K47" t="n">
-        <v>-87.67</v>
+        <v>-84.03</v>
       </c>
       <c r="L47" t="n">
-        <v>115.36</v>
+        <v>110.58</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-47.84</v>
+        <v>-51.95</v>
       </c>
       <c r="K48" t="n">
-        <v>29.43</v>
+        <v>31.96</v>
       </c>
       <c r="L48" t="n">
-        <v>56.17</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>35.12</v>
+        <v>35.64</v>
       </c>
       <c r="K49" t="n">
-        <v>-77.93000000000001</v>
+        <v>-79.09</v>
       </c>
       <c r="L49" t="n">
-        <v>85.48</v>
+        <v>86.75</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>60.97</v>
+        <v>63.43</v>
       </c>
       <c r="K50" t="n">
-        <v>70.69</v>
+        <v>73.53</v>
       </c>
       <c r="L50" t="n">
-        <v>93.34999999999999</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>6.69</v>
+        <v>6.42</v>
       </c>
       <c r="K51" t="n">
-        <v>159.91</v>
+        <v>153.53</v>
       </c>
       <c r="L51" t="n">
-        <v>160.05</v>
+        <v>153.66</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-51.34</v>
+        <v>-54.48</v>
       </c>
       <c r="K52" t="n">
-        <v>-71.11</v>
+        <v>-75.47</v>
       </c>
       <c r="L52" t="n">
-        <v>87.7</v>
+        <v>93.08</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K53" t="n">
-        <v>-138.25</v>
+        <v>-142.56</v>
       </c>
       <c r="L53" t="n">
-        <v>138.29</v>
+        <v>142.6</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>111.62</v>
+        <v>113.2</v>
       </c>
       <c r="K54" t="n">
-        <v>-96.95</v>
+        <v>-98.31999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>147.84</v>
+        <v>149.94</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-191.31</v>
+        <v>-184.32</v>
       </c>
       <c r="K55" t="n">
-        <v>63.66</v>
+        <v>61.33</v>
       </c>
       <c r="L55" t="n">
-        <v>201.62</v>
+        <v>194.26</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>74.12</v>
+        <v>71.17</v>
       </c>
       <c r="K56" t="n">
-        <v>294.05</v>
+        <v>282.34</v>
       </c>
       <c r="L56" t="n">
-        <v>303.25</v>
+        <v>291.18</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>220.77</v>
+        <v>221.5</v>
       </c>
       <c r="K57" t="n">
-        <v>85.41</v>
+        <v>85.69</v>
       </c>
       <c r="L57" t="n">
-        <v>236.72</v>
+        <v>237.49</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-134.04</v>
+        <v>-131.74</v>
       </c>
       <c r="K58" t="n">
-        <v>-217.5</v>
+        <v>-213.76</v>
       </c>
       <c r="L58" t="n">
-        <v>255.49</v>
+        <v>251.1</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-47.72</v>
+        <v>-49.92</v>
       </c>
       <c r="K59" t="n">
-        <v>-12.88</v>
+        <v>-13.47</v>
       </c>
       <c r="L59" t="n">
-        <v>49.42</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.21</v>
+        <v>-9.83</v>
       </c>
       <c r="K60" t="n">
-        <v>82.31999999999999</v>
+        <v>79.25</v>
       </c>
       <c r="L60" t="n">
-        <v>82.95</v>
+        <v>79.86</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>63.09</v>
+        <v>64.25</v>
       </c>
       <c r="K61" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="L61" t="n">
-        <v>63.15</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>62.1</v>
+        <v>65.12</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.87</v>
+        <v>-1.96</v>
       </c>
       <c r="L62" t="n">
-        <v>62.13</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-93.15000000000001</v>
+        <v>-92.08</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.26</v>
+        <v>-1.25</v>
       </c>
       <c r="L63" t="n">
-        <v>93.16</v>
+        <v>92.09</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>107</v>
+        <v>102.43</v>
       </c>
       <c r="K64" t="n">
-        <v>-44.42</v>
+        <v>-42.53</v>
       </c>
       <c r="L64" t="n">
-        <v>115.85</v>
+        <v>110.91</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>9.85</v>
+        <v>10.49</v>
       </c>
       <c r="K65" t="n">
-        <v>-11.4</v>
+        <v>-12.14</v>
       </c>
       <c r="L65" t="n">
-        <v>15.06</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-142.95</v>
+        <v>-138.14</v>
       </c>
       <c r="K66" t="n">
-        <v>-62.73</v>
+        <v>-60.61</v>
       </c>
       <c r="L66" t="n">
-        <v>156.11</v>
+        <v>150.86</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-109.52</v>
+        <v>-110.46</v>
       </c>
       <c r="K67" t="n">
-        <v>43.45</v>
+        <v>43.83</v>
       </c>
       <c r="L67" t="n">
-        <v>117.83</v>
+        <v>118.83</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-78.44</v>
+        <v>-84.59999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-93.69</v>
+        <v>-101.05</v>
       </c>
       <c r="L68" t="n">
-        <v>122.19</v>
+        <v>131.78</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-150.7</v>
+        <v>-148.06</v>
       </c>
       <c r="K69" t="n">
-        <v>-90.09999999999999</v>
+        <v>-88.53</v>
       </c>
       <c r="L69" t="n">
-        <v>175.58</v>
+        <v>172.51</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.22</v>
+        <v>-6.51</v>
       </c>
       <c r="K70" t="n">
-        <v>-7.25</v>
+        <v>-7.59</v>
       </c>
       <c r="L70" t="n">
-        <v>9.550000000000001</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>176.49</v>
+        <v>182.77</v>
       </c>
       <c r="K71" t="n">
-        <v>77.86</v>
+        <v>80.63</v>
       </c>
       <c r="L71" t="n">
-        <v>192.9</v>
+        <v>199.76</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-127.92</v>
+        <v>-125.91</v>
       </c>
       <c r="K72" t="n">
-        <v>226.49</v>
+        <v>222.93</v>
       </c>
       <c r="L72" t="n">
-        <v>260.12</v>
+        <v>256.03</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>6.46</v>
+        <v>6.36</v>
       </c>
       <c r="K73" t="n">
-        <v>261.54</v>
+        <v>257.32</v>
       </c>
       <c r="L73" t="n">
-        <v>261.62</v>
+        <v>257.4</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-32.29</v>
+        <v>-34.08</v>
       </c>
       <c r="K74" t="n">
-        <v>-43.88</v>
+        <v>-46.31</v>
       </c>
       <c r="L74" t="n">
-        <v>54.48</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-30.19</v>
+        <v>-31.36</v>
       </c>
       <c r="K75" t="n">
-        <v>43.12</v>
+        <v>44.79</v>
       </c>
       <c r="L75" t="n">
-        <v>52.63</v>
+        <v>54.68</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-43.25</v>
+        <v>-47.43</v>
       </c>
       <c r="K76" t="n">
-        <v>24.02</v>
+        <v>26.34</v>
       </c>
       <c r="L76" t="n">
-        <v>49.47</v>
+        <v>54.25</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>31.77</v>
+        <v>31.61</v>
       </c>
       <c r="K77" t="n">
-        <v>86.09</v>
+        <v>85.64</v>
       </c>
       <c r="L77" t="n">
-        <v>91.76000000000001</v>
+        <v>91.28</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>58.09</v>
+        <v>62.71</v>
       </c>
       <c r="K78" t="n">
-        <v>-7.82</v>
+        <v>-8.44</v>
       </c>
       <c r="L78" t="n">
-        <v>58.61</v>
+        <v>63.28</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>21.46</v>
+        <v>20.81</v>
       </c>
       <c r="K79" t="n">
-        <v>99.40000000000001</v>
+        <v>96.37</v>
       </c>
       <c r="L79" t="n">
-        <v>101.69</v>
+        <v>98.59</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>41.85</v>
+        <v>43.63</v>
       </c>
       <c r="K80" t="n">
-        <v>-83.43000000000001</v>
+        <v>-86.98</v>
       </c>
       <c r="L80" t="n">
-        <v>93.34</v>
+        <v>97.31</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>53.63</v>
+        <v>55.11</v>
       </c>
       <c r="K81" t="n">
-        <v>100.82</v>
+        <v>103.6</v>
       </c>
       <c r="L81" t="n">
-        <v>114.2</v>
+        <v>117.35</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-47.68</v>
+        <v>-50.88</v>
       </c>
       <c r="K82" t="n">
-        <v>74.65000000000001</v>
+        <v>79.66</v>
       </c>
       <c r="L82" t="n">
-        <v>88.58</v>
+        <v>94.52</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>218.27</v>
+        <v>210.45</v>
       </c>
       <c r="K83" t="n">
-        <v>-12.7</v>
+        <v>-12.25</v>
       </c>
       <c r="L83" t="n">
-        <v>218.64</v>
+        <v>210.8</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>40.24</v>
+        <v>40.36</v>
       </c>
       <c r="K84" t="n">
-        <v>136.68</v>
+        <v>137.09</v>
       </c>
       <c r="L84" t="n">
-        <v>142.48</v>
+        <v>142.91</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-54.95</v>
+        <v>-55.82</v>
       </c>
       <c r="K85" t="n">
-        <v>140.04</v>
+        <v>142.24</v>
       </c>
       <c r="L85" t="n">
-        <v>150.43</v>
+        <v>152.8</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>133.9</v>
+        <v>145.89</v>
       </c>
       <c r="K86" t="n">
-        <v>-53.35</v>
+        <v>-58.12</v>
       </c>
       <c r="L86" t="n">
-        <v>144.14</v>
+        <v>157.04</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-92.2</v>
+        <v>-88.26000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>295.66</v>
+        <v>283.02</v>
       </c>
       <c r="L87" t="n">
-        <v>309.7</v>
+        <v>296.46</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-222.56</v>
+        <v>-222.87</v>
       </c>
       <c r="K88" t="n">
-        <v>66.17</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>232.19</v>
+        <v>232.51</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-09.xlsx
+++ b/output/2025-08-09.xlsx
@@ -628,25 +628,25 @@
         <v>2.26</v>
       </c>
       <c r="F14" t="n">
-        <v>8.640000000000001</v>
+        <v>5.38</v>
       </c>
       <c r="G14" t="n">
-        <v>310.4</v>
+        <v>277.6</v>
       </c>
       <c r="H14" t="n">
-        <v>85.5</v>
+        <v>99.3</v>
       </c>
       <c r="I14" t="n">
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>17.82</v>
+        <v>19.06</v>
       </c>
       <c r="K14" t="n">
-        <v>55.31</v>
+        <v>61.77</v>
       </c>
       <c r="L14" t="n">
-        <v>58.11</v>
+        <v>64.64</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>2.41</v>
       </c>
       <c r="F15" t="n">
-        <v>9.92</v>
+        <v>8.58</v>
       </c>
       <c r="G15" t="n">
-        <v>299.1</v>
+        <v>303.1</v>
       </c>
       <c r="H15" t="n">
-        <v>94.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>34.66</v>
+        <v>44.57</v>
       </c>
       <c r="K15" t="n">
-        <v>-32.68</v>
+        <v>-42.21</v>
       </c>
       <c r="L15" t="n">
-        <v>47.64</v>
+        <v>61.39</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>2.35</v>
       </c>
       <c r="F16" t="n">
-        <v>9.66</v>
+        <v>3.38</v>
       </c>
       <c r="G16" t="n">
-        <v>289.7</v>
+        <v>297.9</v>
       </c>
       <c r="H16" t="n">
-        <v>81.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-45.07</v>
+        <v>-45.31</v>
       </c>
       <c r="K16" t="n">
-        <v>52.21</v>
+        <v>52.32</v>
       </c>
       <c r="L16" t="n">
-        <v>68.97</v>
+        <v>69.20999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>2.72</v>
       </c>
       <c r="F17" t="n">
-        <v>9.09</v>
+        <v>9.52</v>
       </c>
       <c r="G17" t="n">
-        <v>300.2</v>
+        <v>286.5</v>
       </c>
       <c r="H17" t="n">
-        <v>89.2</v>
+        <v>94.2</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>78.47</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-59.01</v>
+        <v>-69.65000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>98.18000000000001</v>
+        <v>114.04</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>2.18</v>
       </c>
       <c r="F18" t="n">
-        <v>9.02</v>
+        <v>10.63</v>
       </c>
       <c r="G18" t="n">
-        <v>281.3</v>
+        <v>285.1</v>
       </c>
       <c r="H18" t="n">
-        <v>95.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>65.03</v>
+        <v>85.03</v>
       </c>
       <c r="K18" t="n">
-        <v>19.57</v>
+        <v>27.65</v>
       </c>
       <c r="L18" t="n">
-        <v>67.91</v>
+        <v>89.41</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>2.29</v>
       </c>
       <c r="F19" t="n">
-        <v>8.77</v>
+        <v>4.46</v>
       </c>
       <c r="G19" t="n">
-        <v>302.7</v>
+        <v>280.2</v>
       </c>
       <c r="H19" t="n">
-        <v>89.90000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I19" t="n">
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-49.59</v>
+        <v>-55.93</v>
       </c>
       <c r="K19" t="n">
-        <v>-37.58</v>
+        <v>-39.96</v>
       </c>
       <c r="L19" t="n">
-        <v>62.22</v>
+        <v>68.73</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>2.89</v>
       </c>
       <c r="F20" t="n">
-        <v>9.039999999999999</v>
+        <v>7.33</v>
       </c>
       <c r="G20" t="n">
-        <v>297</v>
+        <v>285.6</v>
       </c>
       <c r="H20" t="n">
-        <v>85</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-42.78</v>
+        <v>-63.66</v>
       </c>
       <c r="K20" t="n">
-        <v>80.7</v>
+        <v>87.59</v>
       </c>
       <c r="L20" t="n">
-        <v>91.33</v>
+        <v>108.28</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>2.5</v>
       </c>
       <c r="F21" t="n">
-        <v>9.59</v>
+        <v>7.91</v>
       </c>
       <c r="G21" t="n">
-        <v>292.5</v>
+        <v>296.6</v>
       </c>
       <c r="H21" t="n">
-        <v>84.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>105.55</v>
+        <v>123.38</v>
       </c>
       <c r="K21" t="n">
-        <v>-46.07</v>
+        <v>-52.64</v>
       </c>
       <c r="L21" t="n">
-        <v>115.16</v>
+        <v>134.14</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>2.58</v>
       </c>
       <c r="F22" t="n">
-        <v>9.199999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G22" t="n">
-        <v>292.6</v>
+        <v>288.9</v>
       </c>
       <c r="H22" t="n">
-        <v>93.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-125.89</v>
+        <v>-162.08</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.82</v>
+        <v>-11.31</v>
       </c>
       <c r="L22" t="n">
-        <v>126.44</v>
+        <v>162.47</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>2.7</v>
       </c>
       <c r="F23" t="n">
-        <v>8.81</v>
+        <v>7.83</v>
       </c>
       <c r="G23" t="n">
-        <v>290.5</v>
+        <v>280.9</v>
       </c>
       <c r="H23" t="n">
-        <v>86.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I23" t="n">
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>158.9</v>
+        <v>164.48</v>
       </c>
       <c r="K23" t="n">
-        <v>-110.52</v>
+        <v>-128.67</v>
       </c>
       <c r="L23" t="n">
-        <v>193.56</v>
+        <v>208.83</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>2.13</v>
       </c>
       <c r="F24" t="n">
-        <v>9.65</v>
+        <v>6.3</v>
       </c>
       <c r="G24" t="n">
-        <v>291.5</v>
+        <v>297.7</v>
       </c>
       <c r="H24" t="n">
-        <v>87.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>102.16</v>
+        <v>107.35</v>
       </c>
       <c r="K24" t="n">
-        <v>-83.03</v>
+        <v>-92.23999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>131.65</v>
+        <v>141.54</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>2.28</v>
       </c>
       <c r="F25" t="n">
-        <v>9.029999999999999</v>
+        <v>4.74</v>
       </c>
       <c r="G25" t="n">
-        <v>299.8</v>
+        <v>285.3</v>
       </c>
       <c r="H25" t="n">
-        <v>91.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-73.83</v>
+        <v>-97.37</v>
       </c>
       <c r="K25" t="n">
-        <v>-108.25</v>
+        <v>-102.06</v>
       </c>
       <c r="L25" t="n">
-        <v>131.03</v>
+        <v>141.06</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>2.4</v>
       </c>
       <c r="F26" t="n">
-        <v>9.859999999999999</v>
+        <v>7.42</v>
       </c>
       <c r="G26" t="n">
-        <v>298.2</v>
+        <v>302</v>
       </c>
       <c r="H26" t="n">
-        <v>88</v>
+        <v>93.2</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>112.43</v>
+        <v>94.08</v>
       </c>
       <c r="K26" t="n">
-        <v>-143.59</v>
+        <v>-173.9</v>
       </c>
       <c r="L26" t="n">
-        <v>182.37</v>
+        <v>197.72</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>1.6</v>
       </c>
       <c r="F27" t="n">
-        <v>9.08</v>
+        <v>7.19</v>
       </c>
       <c r="G27" t="n">
-        <v>298.1</v>
+        <v>286.4</v>
       </c>
       <c r="H27" t="n">
-        <v>90.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>203.92</v>
+        <v>252.92</v>
       </c>
       <c r="K27" t="n">
-        <v>102.17</v>
+        <v>149.79</v>
       </c>
       <c r="L27" t="n">
-        <v>228.08</v>
+        <v>293.95</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>2.79</v>
       </c>
       <c r="F28" t="n">
-        <v>9.050000000000001</v>
+        <v>6.91</v>
       </c>
       <c r="G28" t="n">
-        <v>296.6</v>
+        <v>285.7</v>
       </c>
       <c r="H28" t="n">
-        <v>84.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>-60.91</v>
+        <v>-101.6</v>
       </c>
       <c r="K28" t="n">
-        <v>270.77</v>
+        <v>282.1</v>
       </c>
       <c r="L28" t="n">
-        <v>277.53</v>
+        <v>299.84</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>2.25</v>
       </c>
       <c r="F29" t="n">
-        <v>8.48</v>
+        <v>4.63</v>
       </c>
       <c r="G29" t="n">
-        <v>284.7</v>
+        <v>274.5</v>
       </c>
       <c r="H29" t="n">
-        <v>91.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>10.28</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>53.43</v>
+        <v>56.33</v>
       </c>
       <c r="L29" t="n">
-        <v>54.41</v>
+        <v>57.21</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>2.28</v>
       </c>
       <c r="F30" t="n">
-        <v>9.25</v>
+        <v>9.85</v>
       </c>
       <c r="G30" t="n">
-        <v>284.5</v>
+        <v>289.8</v>
       </c>
       <c r="H30" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>35.91</v>
+        <v>46.07</v>
       </c>
       <c r="K30" t="n">
-        <v>-41.78</v>
+        <v>-54.27</v>
       </c>
       <c r="L30" t="n">
-        <v>55.09</v>
+        <v>71.19</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>2.61</v>
       </c>
       <c r="F31" t="n">
-        <v>9.32</v>
+        <v>10.13</v>
       </c>
       <c r="G31" t="n">
-        <v>298.2</v>
+        <v>291.1</v>
       </c>
       <c r="H31" t="n">
-        <v>93.5</v>
+        <v>93.2</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-39.87</v>
+        <v>-50.9</v>
       </c>
       <c r="K31" t="n">
-        <v>-70.94</v>
+        <v>-88.94</v>
       </c>
       <c r="L31" t="n">
-        <v>81.38</v>
+        <v>102.48</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>2.79</v>
       </c>
       <c r="F32" t="n">
-        <v>9.34</v>
+        <v>5.98</v>
       </c>
       <c r="G32" t="n">
-        <v>300.7</v>
+        <v>291.6</v>
       </c>
       <c r="H32" t="n">
-        <v>82.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I32" t="n">
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-27.07</v>
+        <v>-33.3</v>
       </c>
       <c r="K32" t="n">
-        <v>-72.14</v>
+        <v>-78.31</v>
       </c>
       <c r="L32" t="n">
-        <v>77.05</v>
+        <v>85.09</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>2.57</v>
       </c>
       <c r="F33" t="n">
-        <v>9.529999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="G33" t="n">
-        <v>298.4</v>
+        <v>295.3</v>
       </c>
       <c r="H33" t="n">
-        <v>94.8</v>
+        <v>93.3</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-74.06999999999999</v>
+        <v>-87.95</v>
       </c>
       <c r="K33" t="n">
-        <v>70.31999999999999</v>
+        <v>82.41</v>
       </c>
       <c r="L33" t="n">
-        <v>102.14</v>
+        <v>120.52</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>1.79</v>
       </c>
       <c r="F34" t="n">
-        <v>9.289999999999999</v>
+        <v>6.54</v>
       </c>
       <c r="G34" t="n">
-        <v>286.9</v>
+        <v>290.5</v>
       </c>
       <c r="H34" t="n">
-        <v>90.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-42.12</v>
+        <v>-50.72</v>
       </c>
       <c r="K34" t="n">
-        <v>61.48</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>74.52</v>
+        <v>88.33</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>2.62</v>
       </c>
       <c r="F35" t="n">
-        <v>9</v>
+        <v>7.34</v>
       </c>
       <c r="G35" t="n">
-        <v>307.7</v>
+        <v>284.7</v>
       </c>
       <c r="H35" t="n">
-        <v>89.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I35" t="n">
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-141.43</v>
+        <v>-163.12</v>
       </c>
       <c r="K35" t="n">
-        <v>-64.31</v>
+        <v>-69.98</v>
       </c>
       <c r="L35" t="n">
-        <v>155.37</v>
+        <v>177.49</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>2.29</v>
       </c>
       <c r="F36" t="n">
-        <v>9.17</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>301.3</v>
+        <v>288.1</v>
       </c>
       <c r="H36" t="n">
-        <v>89.7</v>
+        <v>94.7</v>
       </c>
       <c r="I36" t="n">
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-27.37</v>
+        <v>-39.37</v>
       </c>
       <c r="K36" t="n">
-        <v>149.29</v>
+        <v>176.16</v>
       </c>
       <c r="L36" t="n">
-        <v>151.78</v>
+        <v>180.51</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>2.12</v>
       </c>
       <c r="F37" t="n">
-        <v>10.03</v>
+        <v>5.28</v>
       </c>
       <c r="G37" t="n">
-        <v>281.7</v>
+        <v>305.4</v>
       </c>
       <c r="H37" t="n">
-        <v>91.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I37" t="n">
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>56.15</v>
+        <v>51.93</v>
       </c>
       <c r="K37" t="n">
-        <v>73.61</v>
+        <v>91.41</v>
       </c>
       <c r="L37" t="n">
-        <v>92.58</v>
+        <v>105.13</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>2.46</v>
       </c>
       <c r="F38" t="n">
-        <v>8.970000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>295</v>
+        <v>284.2</v>
       </c>
       <c r="H38" t="n">
-        <v>89.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I38" t="n">
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>136.7</v>
+        <v>159.15</v>
       </c>
       <c r="K38" t="n">
-        <v>6.75</v>
+        <v>16.96</v>
       </c>
       <c r="L38" t="n">
-        <v>136.87</v>
+        <v>160.05</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>1.88</v>
       </c>
       <c r="F39" t="n">
-        <v>8.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="G39" t="n">
-        <v>286.6</v>
+        <v>278.8</v>
       </c>
       <c r="H39" t="n">
-        <v>88.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-142.66</v>
+        <v>-197.22</v>
       </c>
       <c r="K39" t="n">
-        <v>52.07</v>
+        <v>66.72</v>
       </c>
       <c r="L39" t="n">
-        <v>151.86</v>
+        <v>208.2</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>2.49</v>
       </c>
       <c r="F40" t="n">
-        <v>9.02</v>
+        <v>7.09</v>
       </c>
       <c r="G40" t="n">
-        <v>303</v>
+        <v>285.2</v>
       </c>
       <c r="H40" t="n">
-        <v>86.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I40" t="n">
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-112.41</v>
+        <v>-147.09</v>
       </c>
       <c r="K40" t="n">
-        <v>-18.63</v>
+        <v>-10.45</v>
       </c>
       <c r="L40" t="n">
-        <v>113.95</v>
+        <v>147.46</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>2.64</v>
       </c>
       <c r="F41" t="n">
-        <v>9.390000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G41" t="n">
-        <v>277.3</v>
+        <v>292.6</v>
       </c>
       <c r="H41" t="n">
-        <v>99.2</v>
+        <v>82.7</v>
       </c>
       <c r="I41" t="n">
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>290.33</v>
+        <v>325.49</v>
       </c>
       <c r="K41" t="n">
-        <v>29.66</v>
+        <v>65.34</v>
       </c>
       <c r="L41" t="n">
-        <v>291.84</v>
+        <v>331.99</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>1.89</v>
       </c>
       <c r="F42" t="n">
-        <v>9.01</v>
+        <v>7.24</v>
       </c>
       <c r="G42" t="n">
-        <v>296.9</v>
+        <v>285</v>
       </c>
       <c r="H42" t="n">
-        <v>90.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-87.65000000000001</v>
+        <v>-163.67</v>
       </c>
       <c r="K42" t="n">
-        <v>-156.04</v>
+        <v>-178.67</v>
       </c>
       <c r="L42" t="n">
-        <v>178.97</v>
+        <v>242.31</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>2.6</v>
       </c>
       <c r="F43" t="n">
-        <v>8.82</v>
+        <v>10.7</v>
       </c>
       <c r="G43" t="n">
-        <v>295.6</v>
+        <v>281.1</v>
       </c>
       <c r="H43" t="n">
-        <v>89.59999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>-164.46</v>
+        <v>-238.9</v>
       </c>
       <c r="K43" t="n">
-        <v>176.54</v>
+        <v>200.92</v>
       </c>
       <c r="L43" t="n">
-        <v>241.27</v>
+        <v>312.15</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>2.6</v>
       </c>
       <c r="F44" t="n">
-        <v>9.07</v>
+        <v>10.7</v>
       </c>
       <c r="G44" t="n">
-        <v>273.7</v>
+        <v>286.2</v>
       </c>
       <c r="H44" t="n">
-        <v>92.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I44" t="n">
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>83.73999999999999</v>
+        <v>101.48</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.02</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>83.73999999999999</v>
+        <v>101.49</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>1.8</v>
       </c>
       <c r="F45" t="n">
-        <v>8.789999999999999</v>
+        <v>6.26</v>
       </c>
       <c r="G45" t="n">
-        <v>291.2</v>
+        <v>280.6</v>
       </c>
       <c r="H45" t="n">
-        <v>93.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="I45" t="n">
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>30.21</v>
+        <v>36.07</v>
       </c>
       <c r="K45" t="n">
-        <v>-37.73</v>
+        <v>-45.94</v>
       </c>
       <c r="L45" t="n">
-        <v>48.33</v>
+        <v>58.41</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>2.74</v>
       </c>
       <c r="F46" t="n">
-        <v>9.18</v>
+        <v>9.1</v>
       </c>
       <c r="G46" t="n">
-        <v>286.6</v>
+        <v>288.3</v>
       </c>
       <c r="H46" t="n">
-        <v>88.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-75.22</v>
+        <v>-89.91</v>
       </c>
       <c r="K46" t="n">
-        <v>46.25</v>
+        <v>55.11</v>
       </c>
       <c r="L46" t="n">
-        <v>88.3</v>
+        <v>105.46</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>2.59</v>
       </c>
       <c r="F47" t="n">
-        <v>8.949999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>277.7</v>
+        <v>283.8</v>
       </c>
       <c r="H47" t="n">
-        <v>85.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-71.87</v>
+        <v>-84.34999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-84.03</v>
+        <v>-95.78</v>
       </c>
       <c r="L47" t="n">
-        <v>110.58</v>
+        <v>127.63</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>2.91</v>
       </c>
       <c r="F48" t="n">
-        <v>9.640000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="G48" t="n">
-        <v>299.7</v>
+        <v>297.6</v>
       </c>
       <c r="H48" t="n">
-        <v>89.3</v>
+        <v>94</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-51.95</v>
+        <v>-69.81</v>
       </c>
       <c r="K48" t="n">
-        <v>31.96</v>
+        <v>42.05</v>
       </c>
       <c r="L48" t="n">
-        <v>61</v>
+        <v>81.48999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>3.17</v>
       </c>
       <c r="F49" t="n">
-        <v>9.76</v>
+        <v>10.7</v>
       </c>
       <c r="G49" t="n">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="H49" t="n">
-        <v>98.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I49" t="n">
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>35.64</v>
+        <v>39.96</v>
       </c>
       <c r="K49" t="n">
-        <v>-79.09</v>
+        <v>-93.55</v>
       </c>
       <c r="L49" t="n">
-        <v>86.75</v>
+        <v>101.73</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>2.22</v>
       </c>
       <c r="F50" t="n">
-        <v>9.83</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>297.5</v>
+        <v>301.5</v>
       </c>
       <c r="H50" t="n">
-        <v>93</v>
+        <v>92.8</v>
       </c>
       <c r="I50" t="n">
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>63.43</v>
+        <v>72.72</v>
       </c>
       <c r="K50" t="n">
-        <v>73.53</v>
+        <v>105.89</v>
       </c>
       <c r="L50" t="n">
-        <v>97.11</v>
+        <v>128.46</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>2.53</v>
       </c>
       <c r="F51" t="n">
-        <v>9.75</v>
+        <v>5.86</v>
       </c>
       <c r="G51" t="n">
-        <v>290</v>
+        <v>299.9</v>
       </c>
       <c r="H51" t="n">
-        <v>88.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I51" t="n">
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>6.42</v>
+        <v>0.82</v>
       </c>
       <c r="K51" t="n">
-        <v>153.53</v>
+        <v>164.02</v>
       </c>
       <c r="L51" t="n">
-        <v>153.66</v>
+        <v>164.02</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>2.62</v>
       </c>
       <c r="F52" t="n">
-        <v>9.130000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="G52" t="n">
-        <v>281.7</v>
+        <v>287.4</v>
       </c>
       <c r="H52" t="n">
-        <v>89.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I52" t="n">
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-54.48</v>
+        <v>-82.38</v>
       </c>
       <c r="K52" t="n">
-        <v>-75.47</v>
+        <v>-82.42</v>
       </c>
       <c r="L52" t="n">
-        <v>93.08</v>
+        <v>116.53</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>2.57</v>
       </c>
       <c r="F53" t="n">
-        <v>9.52</v>
+        <v>10.7</v>
       </c>
       <c r="G53" t="n">
-        <v>290.8</v>
+        <v>295.1</v>
       </c>
       <c r="H53" t="n">
-        <v>97</v>
+        <v>89.5</v>
       </c>
       <c r="I53" t="n">
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>3.35</v>
+        <v>-30.76</v>
       </c>
       <c r="K53" t="n">
-        <v>-142.56</v>
+        <v>-175.32</v>
       </c>
       <c r="L53" t="n">
-        <v>142.6</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>2.46</v>
       </c>
       <c r="F54" t="n">
-        <v>9.130000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>276.5</v>
+        <v>287.3</v>
       </c>
       <c r="H54" t="n">
-        <v>91.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="I54" t="n">
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>113.2</v>
+        <v>126.59</v>
       </c>
       <c r="K54" t="n">
-        <v>-98.31999999999999</v>
+        <v>-123.52</v>
       </c>
       <c r="L54" t="n">
-        <v>149.94</v>
+        <v>176.87</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>2.45</v>
       </c>
       <c r="F55" t="n">
-        <v>9.74</v>
+        <v>10.55</v>
       </c>
       <c r="G55" t="n">
-        <v>294.7</v>
+        <v>299.7</v>
       </c>
       <c r="H55" t="n">
-        <v>93.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>-184.32</v>
+        <v>-241.56</v>
       </c>
       <c r="K55" t="n">
-        <v>61.33</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>194.26</v>
+        <v>256.21</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>2.48</v>
       </c>
       <c r="F56" t="n">
-        <v>9.880000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>296.6</v>
+        <v>302.4</v>
       </c>
       <c r="H56" t="n">
-        <v>88.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>71.17</v>
+        <v>45.98</v>
       </c>
       <c r="K56" t="n">
-        <v>282.34</v>
+        <v>330.89</v>
       </c>
       <c r="L56" t="n">
-        <v>291.18</v>
+        <v>334.07</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>3.14</v>
       </c>
       <c r="F57" t="n">
-        <v>8.380000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G57" t="n">
-        <v>298.5</v>
+        <v>272.3</v>
       </c>
       <c r="H57" t="n">
-        <v>98.2</v>
+        <v>93.3</v>
       </c>
       <c r="I57" t="n">
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>221.5</v>
+        <v>237.3</v>
       </c>
       <c r="K57" t="n">
-        <v>85.69</v>
+        <v>104.08</v>
       </c>
       <c r="L57" t="n">
-        <v>237.49</v>
+        <v>259.12</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>2.43</v>
       </c>
       <c r="F58" t="n">
-        <v>9.25</v>
+        <v>9.99</v>
       </c>
       <c r="G58" t="n">
-        <v>286.2</v>
+        <v>289.8</v>
       </c>
       <c r="H58" t="n">
-        <v>91.7</v>
+        <v>87.2</v>
       </c>
       <c r="I58" t="n">
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-131.74</v>
+        <v>-205.03</v>
       </c>
       <c r="K58" t="n">
-        <v>-213.76</v>
+        <v>-241.25</v>
       </c>
       <c r="L58" t="n">
-        <v>251.1</v>
+        <v>316.61</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>2.43</v>
       </c>
       <c r="F59" t="n">
-        <v>9.65</v>
+        <v>7.54</v>
       </c>
       <c r="G59" t="n">
-        <v>292.7</v>
+        <v>297.7</v>
       </c>
       <c r="H59" t="n">
-        <v>82.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-49.92</v>
+        <v>-61.61</v>
       </c>
       <c r="K59" t="n">
-        <v>-13.47</v>
+        <v>-15.67</v>
       </c>
       <c r="L59" t="n">
-        <v>51.7</v>
+        <v>63.58</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>2.35</v>
       </c>
       <c r="F60" t="n">
-        <v>8.99</v>
+        <v>6.64</v>
       </c>
       <c r="G60" t="n">
-        <v>286.6</v>
+        <v>284.7</v>
       </c>
       <c r="H60" t="n">
-        <v>85.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I60" t="n">
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.83</v>
+        <v>-11.42</v>
       </c>
       <c r="K60" t="n">
-        <v>79.25</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>79.86</v>
+        <v>88.53</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>2.73</v>
       </c>
       <c r="F61" t="n">
-        <v>9.029999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="G61" t="n">
-        <v>290.5</v>
+        <v>285.4</v>
       </c>
       <c r="H61" t="n">
-        <v>85.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>64.25</v>
+        <v>75.91</v>
       </c>
       <c r="K61" t="n">
-        <v>2.57</v>
+        <v>3.26</v>
       </c>
       <c r="L61" t="n">
-        <v>64.3</v>
+        <v>75.98</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>2.42</v>
       </c>
       <c r="F62" t="n">
-        <v>9.470000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="G62" t="n">
-        <v>302.1</v>
+        <v>294.3</v>
       </c>
       <c r="H62" t="n">
-        <v>89.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>65.12</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.96</v>
+        <v>-1.46</v>
       </c>
       <c r="L62" t="n">
-        <v>65.15000000000001</v>
+        <v>84.36</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>2.69</v>
       </c>
       <c r="F63" t="n">
-        <v>9.19</v>
+        <v>7.32</v>
       </c>
       <c r="G63" t="n">
-        <v>287.4</v>
+        <v>288.6</v>
       </c>
       <c r="H63" t="n">
-        <v>86</v>
+        <v>87.8</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-92.08</v>
+        <v>-100.17</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.25</v>
+        <v>-0.55</v>
       </c>
       <c r="L63" t="n">
-        <v>92.09</v>
+        <v>100.17</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>2.48</v>
       </c>
       <c r="F64" t="n">
-        <v>9.69</v>
+        <v>10.7</v>
       </c>
       <c r="G64" t="n">
-        <v>292.7</v>
+        <v>298.6</v>
       </c>
       <c r="H64" t="n">
-        <v>93</v>
+        <v>90.5</v>
       </c>
       <c r="I64" t="n">
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>102.43</v>
+        <v>126.42</v>
       </c>
       <c r="K64" t="n">
-        <v>-42.53</v>
+        <v>-52.04</v>
       </c>
       <c r="L64" t="n">
-        <v>110.91</v>
+        <v>136.71</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>3.02</v>
       </c>
       <c r="F65" t="n">
-        <v>9.34</v>
+        <v>10.7</v>
       </c>
       <c r="G65" t="n">
-        <v>298.8</v>
+        <v>291.7</v>
       </c>
       <c r="H65" t="n">
-        <v>94.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>10.49</v>
+        <v>-9.49</v>
       </c>
       <c r="K65" t="n">
-        <v>-12.14</v>
+        <v>-6.52</v>
       </c>
       <c r="L65" t="n">
-        <v>16.04</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>2.76</v>
       </c>
       <c r="F66" t="n">
-        <v>9.039999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G66" t="n">
-        <v>292.3</v>
+        <v>285.6</v>
       </c>
       <c r="H66" t="n">
-        <v>91.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="I66" t="n">
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-138.14</v>
+        <v>-172.61</v>
       </c>
       <c r="K66" t="n">
-        <v>-60.61</v>
+        <v>-69.79000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>150.86</v>
+        <v>186.19</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>2.84</v>
       </c>
       <c r="F67" t="n">
-        <v>9.57</v>
+        <v>10.39</v>
       </c>
       <c r="G67" t="n">
-        <v>293.8</v>
+        <v>296.3</v>
       </c>
       <c r="H67" t="n">
-        <v>90.3</v>
+        <v>91</v>
       </c>
       <c r="I67" t="n">
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-110.46</v>
+        <v>-138.93</v>
       </c>
       <c r="K67" t="n">
-        <v>43.83</v>
+        <v>56.64</v>
       </c>
       <c r="L67" t="n">
-        <v>118.83</v>
+        <v>150.04</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>3.25</v>
       </c>
       <c r="F68" t="n">
-        <v>10.27</v>
+        <v>10.7</v>
       </c>
       <c r="G68" t="n">
-        <v>287.7</v>
+        <v>310.1</v>
       </c>
       <c r="H68" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I68" t="n">
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-84.59999999999999</v>
+        <v>-154.18</v>
       </c>
       <c r="K68" t="n">
-        <v>-101.05</v>
+        <v>-53.81</v>
       </c>
       <c r="L68" t="n">
-        <v>131.78</v>
+        <v>163.3</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>2.29</v>
       </c>
       <c r="F69" t="n">
-        <v>9.859999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="G69" t="n">
-        <v>286.3</v>
+        <v>302.1</v>
       </c>
       <c r="H69" t="n">
-        <v>92.3</v>
+        <v>87.3</v>
       </c>
       <c r="I69" t="n">
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-148.06</v>
+        <v>-197.6</v>
       </c>
       <c r="K69" t="n">
-        <v>-88.53</v>
+        <v>-94.40000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>172.51</v>
+        <v>218.99</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>2.67</v>
       </c>
       <c r="F70" t="n">
-        <v>9.880000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="G70" t="n">
-        <v>294.7</v>
+        <v>302.5</v>
       </c>
       <c r="H70" t="n">
-        <v>88.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I70" t="n">
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.51</v>
+        <v>-76.67</v>
       </c>
       <c r="K70" t="n">
-        <v>-7.59</v>
+        <v>29.8</v>
       </c>
       <c r="L70" t="n">
-        <v>9.99</v>
+        <v>82.25</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>3.01</v>
       </c>
       <c r="F71" t="n">
-        <v>9.529999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G71" t="n">
-        <v>292.9</v>
+        <v>295.4</v>
       </c>
       <c r="H71" t="n">
-        <v>87.5</v>
+        <v>90.5</v>
       </c>
       <c r="I71" t="n">
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>182.77</v>
+        <v>178.59</v>
       </c>
       <c r="K71" t="n">
-        <v>80.63</v>
+        <v>154.23</v>
       </c>
       <c r="L71" t="n">
-        <v>199.76</v>
+        <v>235.96</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>3.03</v>
       </c>
       <c r="F72" t="n">
-        <v>9.31</v>
+        <v>7.44</v>
       </c>
       <c r="G72" t="n">
-        <v>287.7</v>
+        <v>291</v>
       </c>
       <c r="H72" t="n">
-        <v>82.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I72" t="n">
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-125.91</v>
+        <v>-167.47</v>
       </c>
       <c r="K72" t="n">
-        <v>222.93</v>
+        <v>243.37</v>
       </c>
       <c r="L72" t="n">
-        <v>256.03</v>
+        <v>295.43</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>2.84</v>
       </c>
       <c r="F73" t="n">
-        <v>9.34</v>
+        <v>8.23</v>
       </c>
       <c r="G73" t="n">
-        <v>287.5</v>
+        <v>291.6</v>
       </c>
       <c r="H73" t="n">
-        <v>94.5</v>
+        <v>87.8</v>
       </c>
       <c r="I73" t="n">
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>6.36</v>
+        <v>-36.09</v>
       </c>
       <c r="K73" t="n">
-        <v>257.32</v>
+        <v>294.79</v>
       </c>
       <c r="L73" t="n">
-        <v>257.4</v>
+        <v>296.99</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>2.88</v>
       </c>
       <c r="F74" t="n">
-        <v>9.220000000000001</v>
+        <v>10.53</v>
       </c>
       <c r="G74" t="n">
-        <v>294.3</v>
+        <v>289.1</v>
       </c>
       <c r="H74" t="n">
-        <v>89.2</v>
+        <v>91.2</v>
       </c>
       <c r="I74" t="n">
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-34.08</v>
+        <v>-44.38</v>
       </c>
       <c r="K74" t="n">
-        <v>-46.31</v>
+        <v>-57.4</v>
       </c>
       <c r="L74" t="n">
-        <v>57.5</v>
+        <v>72.56</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>2.44</v>
       </c>
       <c r="F75" t="n">
-        <v>9.699999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>305.4</v>
+        <v>289.7</v>
       </c>
       <c r="H75" t="n">
-        <v>88.5</v>
+        <v>93.5</v>
       </c>
       <c r="I75" t="n">
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-31.36</v>
+        <v>27.78</v>
       </c>
       <c r="K75" t="n">
-        <v>44.79</v>
+        <v>92.67</v>
       </c>
       <c r="L75" t="n">
-        <v>54.68</v>
+        <v>96.73999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3229,28 +3229,28 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.29</v>
+        <v>2.95</v>
       </c>
       <c r="F76" t="n">
-        <v>9.720000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G76" t="n">
-        <v>297.7</v>
+        <v>308.4</v>
       </c>
       <c r="H76" t="n">
-        <v>82.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J76" t="n">
-        <v>-47.43</v>
+        <v>15.48</v>
       </c>
       <c r="K76" t="n">
-        <v>26.34</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>54.25</v>
+        <v>69.16</v>
       </c>
     </row>
     <row r="77">
@@ -3271,28 +3271,28 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="F77" t="n">
-        <v>8.77</v>
+        <v>10.16</v>
       </c>
       <c r="G77" t="n">
-        <v>278.5</v>
+        <v>297.3</v>
       </c>
       <c r="H77" t="n">
-        <v>91.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>31.61</v>
+        <v>97.13</v>
       </c>
       <c r="K77" t="n">
-        <v>85.64</v>
+        <v>39.99</v>
       </c>
       <c r="L77" t="n">
-        <v>91.28</v>
+        <v>105.04</v>
       </c>
     </row>
     <row r="78">
@@ -3313,28 +3313,28 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="F78" t="n">
-        <v>9.17</v>
+        <v>9.25</v>
       </c>
       <c r="G78" t="n">
-        <v>287.4</v>
+        <v>290.3</v>
       </c>
       <c r="H78" t="n">
-        <v>94.7</v>
+        <v>88.2</v>
       </c>
       <c r="I78" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>62.71</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-8.44</v>
+        <v>-109.64</v>
       </c>
       <c r="L78" t="n">
-        <v>63.28</v>
+        <v>110.07</v>
       </c>
     </row>
     <row r="79">
@@ -3355,28 +3355,28 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="F79" t="n">
-        <v>9.5</v>
+        <v>10.16</v>
       </c>
       <c r="G79" t="n">
-        <v>287.2</v>
+        <v>277.9</v>
       </c>
       <c r="H79" t="n">
-        <v>90</v>
+        <v>91.5</v>
       </c>
       <c r="I79" t="n">
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>20.81</v>
+        <v>118.06</v>
       </c>
       <c r="K79" t="n">
-        <v>96.37</v>
+        <v>-40.85</v>
       </c>
       <c r="L79" t="n">
-        <v>98.59</v>
+        <v>124.93</v>
       </c>
     </row>
     <row r="80">
@@ -3397,28 +3397,28 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="F80" t="n">
-        <v>8.890000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="G80" t="n">
-        <v>289</v>
+        <v>306.7</v>
       </c>
       <c r="H80" t="n">
-        <v>88.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>43.63</v>
+        <v>-105.9</v>
       </c>
       <c r="K80" t="n">
-        <v>-86.98</v>
+        <v>-89.75</v>
       </c>
       <c r="L80" t="n">
-        <v>97.31</v>
+        <v>138.82</v>
       </c>
     </row>
     <row r="81">
@@ -3439,28 +3439,28 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="F81" t="n">
-        <v>9.470000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G81" t="n">
-        <v>293.9</v>
+        <v>294.3</v>
       </c>
       <c r="H81" t="n">
-        <v>87.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>55.11</v>
+        <v>51.14</v>
       </c>
       <c r="K81" t="n">
-        <v>103.6</v>
+        <v>123.08</v>
       </c>
       <c r="L81" t="n">
-        <v>117.35</v>
+        <v>133.28</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>3.05</v>
       </c>
       <c r="F82" t="n">
-        <v>9.289999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G82" t="n">
-        <v>293.6</v>
+        <v>290.6</v>
       </c>
       <c r="H82" t="n">
-        <v>98.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I82" t="n">
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-50.88</v>
+        <v>-76.56</v>
       </c>
       <c r="K82" t="n">
-        <v>79.66</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>94.52</v>
+        <v>120.92</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>2.78</v>
       </c>
       <c r="F83" t="n">
-        <v>10.17</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G83" t="n">
-        <v>281.8</v>
+        <v>308.3</v>
       </c>
       <c r="H83" t="n">
-        <v>92.2</v>
+        <v>85</v>
       </c>
       <c r="I83" t="n">
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>210.45</v>
+        <v>236.17</v>
       </c>
       <c r="K83" t="n">
-        <v>-12.25</v>
+        <v>5.6</v>
       </c>
       <c r="L83" t="n">
-        <v>210.8</v>
+        <v>236.23</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>2.09</v>
       </c>
       <c r="F84" t="n">
-        <v>9.56</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>287.2</v>
+        <v>295.9</v>
       </c>
       <c r="H84" t="n">
-        <v>89.8</v>
+        <v>87.7</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>40.36</v>
+        <v>32.36</v>
       </c>
       <c r="K84" t="n">
-        <v>137.09</v>
+        <v>182.12</v>
       </c>
       <c r="L84" t="n">
-        <v>142.91</v>
+        <v>184.98</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>2.83</v>
       </c>
       <c r="F85" t="n">
-        <v>8.85</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G85" t="n">
-        <v>286.7</v>
+        <v>281.8</v>
       </c>
       <c r="H85" t="n">
-        <v>92.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-55.82</v>
+        <v>-96.68000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>142.24</v>
+        <v>169.21</v>
       </c>
       <c r="L85" t="n">
-        <v>152.8</v>
+        <v>194.89</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>2.34</v>
       </c>
       <c r="F86" t="n">
-        <v>8.82</v>
+        <v>7.5</v>
       </c>
       <c r="G86" t="n">
-        <v>271.1</v>
+        <v>281.1</v>
       </c>
       <c r="H86" t="n">
-        <v>87</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J86" t="n">
-        <v>145.89</v>
+        <v>41.2</v>
       </c>
       <c r="K86" t="n">
-        <v>-58.12</v>
+        <v>-27.83</v>
       </c>
       <c r="L86" t="n">
-        <v>157.04</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>2.41</v>
       </c>
       <c r="F87" t="n">
-        <v>9.550000000000001</v>
+        <v>6.53</v>
       </c>
       <c r="G87" t="n">
-        <v>290.1</v>
+        <v>295.7</v>
       </c>
       <c r="H87" t="n">
-        <v>90.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I87" t="n">
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-88.26000000000001</v>
+        <v>-123.4</v>
       </c>
       <c r="K87" t="n">
-        <v>283.02</v>
+        <v>312.72</v>
       </c>
       <c r="L87" t="n">
-        <v>296.46</v>
+        <v>336.18</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>2.96</v>
       </c>
       <c r="F88" t="n">
-        <v>9.91</v>
+        <v>9.07</v>
       </c>
       <c r="G88" t="n">
-        <v>299.7</v>
+        <v>303.1</v>
       </c>
       <c r="H88" t="n">
-        <v>85.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I88" t="n">
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-222.87</v>
+        <v>-274.72</v>
       </c>
       <c r="K88" t="n">
-        <v>66.26000000000001</v>
+        <v>98.33</v>
       </c>
       <c r="L88" t="n">
-        <v>232.51</v>
+        <v>291.79</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-09.xlsx
+++ b/output/2025-08-09.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>19.06</v>
+        <v>21.69</v>
       </c>
       <c r="K14" t="n">
-        <v>61.77</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>64.64</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>44.57</v>
+        <v>50.72</v>
       </c>
       <c r="K15" t="n">
-        <v>-42.21</v>
+        <v>-48.04</v>
       </c>
       <c r="L15" t="n">
-        <v>61.39</v>
+        <v>69.86</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-45.31</v>
+        <v>-51.56</v>
       </c>
       <c r="K16" t="n">
-        <v>52.32</v>
+        <v>59.53</v>
       </c>
       <c r="L16" t="n">
-        <v>69.20999999999999</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>90.29000000000001</v>
+        <v>101.38</v>
       </c>
       <c r="K17" t="n">
-        <v>-69.65000000000001</v>
+        <v>-78.20999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>114.04</v>
+        <v>128.04</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>85.03</v>
+        <v>95.47</v>
       </c>
       <c r="K18" t="n">
-        <v>27.65</v>
+        <v>31.04</v>
       </c>
       <c r="L18" t="n">
-        <v>89.41</v>
+        <v>100.39</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-55.93</v>
+        <v>-63.64</v>
       </c>
       <c r="K19" t="n">
-        <v>-39.96</v>
+        <v>-45.47</v>
       </c>
       <c r="L19" t="n">
-        <v>68.73</v>
+        <v>78.20999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-63.66</v>
+        <v>-70.48</v>
       </c>
       <c r="K20" t="n">
-        <v>87.59</v>
+        <v>96.97</v>
       </c>
       <c r="L20" t="n">
-        <v>108.28</v>
+        <v>119.88</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>123.38</v>
+        <v>140.39</v>
       </c>
       <c r="K21" t="n">
-        <v>-52.64</v>
+        <v>-59.9</v>
       </c>
       <c r="L21" t="n">
-        <v>134.14</v>
+        <v>152.64</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-162.08</v>
+        <v>-184.44</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.31</v>
+        <v>-12.87</v>
       </c>
       <c r="L22" t="n">
-        <v>162.47</v>
+        <v>184.89</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>164.48</v>
+        <v>187.17</v>
       </c>
       <c r="K23" t="n">
-        <v>-128.67</v>
+        <v>-146.42</v>
       </c>
       <c r="L23" t="n">
-        <v>208.83</v>
+        <v>237.64</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>107.35</v>
+        <v>118.85</v>
       </c>
       <c r="K24" t="n">
-        <v>-92.23999999999999</v>
+        <v>-102.13</v>
       </c>
       <c r="L24" t="n">
-        <v>141.54</v>
+        <v>156.7</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-97.37</v>
+        <v>-107.8</v>
       </c>
       <c r="K25" t="n">
-        <v>-102.06</v>
+        <v>-113</v>
       </c>
       <c r="L25" t="n">
-        <v>141.06</v>
+        <v>156.17</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>94.08</v>
+        <v>105.64</v>
       </c>
       <c r="K26" t="n">
-        <v>-173.9</v>
+        <v>-195.25</v>
       </c>
       <c r="L26" t="n">
-        <v>197.72</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>252.92</v>
+        <v>287.81</v>
       </c>
       <c r="K27" t="n">
-        <v>149.79</v>
+        <v>170.45</v>
       </c>
       <c r="L27" t="n">
-        <v>293.95</v>
+        <v>334.49</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>-101.6</v>
+        <v>-112.48</v>
       </c>
       <c r="K28" t="n">
-        <v>282.1</v>
+        <v>312.33</v>
       </c>
       <c r="L28" t="n">
-        <v>299.84</v>
+        <v>331.96</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>9.949999999999999</v>
+        <v>11.17</v>
       </c>
       <c r="K29" t="n">
-        <v>56.33</v>
+        <v>63.25</v>
       </c>
       <c r="L29" t="n">
-        <v>57.21</v>
+        <v>64.23</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>46.07</v>
+        <v>52.43</v>
       </c>
       <c r="K30" t="n">
-        <v>-54.27</v>
+        <v>-61.76</v>
       </c>
       <c r="L30" t="n">
-        <v>71.19</v>
+        <v>81.01000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-50.9</v>
+        <v>-57.92</v>
       </c>
       <c r="K31" t="n">
-        <v>-88.94</v>
+        <v>-101.21</v>
       </c>
       <c r="L31" t="n">
-        <v>102.48</v>
+        <v>116.61</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-33.3</v>
+        <v>-37.89</v>
       </c>
       <c r="K32" t="n">
-        <v>-78.31</v>
+        <v>-89.11</v>
       </c>
       <c r="L32" t="n">
-        <v>85.09</v>
+        <v>96.83</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-87.95</v>
+        <v>-100.08</v>
       </c>
       <c r="K33" t="n">
-        <v>82.41</v>
+        <v>93.77</v>
       </c>
       <c r="L33" t="n">
-        <v>120.52</v>
+        <v>137.15</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-50.72</v>
+        <v>-56.15</v>
       </c>
       <c r="K34" t="n">
-        <v>72.31999999999999</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>88.33</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-163.12</v>
+        <v>-185.61</v>
       </c>
       <c r="K35" t="n">
-        <v>-69.98</v>
+        <v>-79.63</v>
       </c>
       <c r="L35" t="n">
-        <v>177.49</v>
+        <v>201.97</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-39.37</v>
+        <v>-44.2</v>
       </c>
       <c r="K36" t="n">
-        <v>176.16</v>
+        <v>197.79</v>
       </c>
       <c r="L36" t="n">
-        <v>180.51</v>
+        <v>202.67</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>51.93</v>
+        <v>59.09</v>
       </c>
       <c r="K37" t="n">
-        <v>91.41</v>
+        <v>104.01</v>
       </c>
       <c r="L37" t="n">
-        <v>105.13</v>
+        <v>119.63</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>159.15</v>
+        <v>181.1</v>
       </c>
       <c r="K38" t="n">
-        <v>16.96</v>
+        <v>19.3</v>
       </c>
       <c r="L38" t="n">
-        <v>160.05</v>
+        <v>182.13</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-197.22</v>
+        <v>-218.35</v>
       </c>
       <c r="K39" t="n">
-        <v>66.72</v>
+        <v>73.86</v>
       </c>
       <c r="L39" t="n">
-        <v>208.2</v>
+        <v>230.51</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-147.09</v>
+        <v>-167.37</v>
       </c>
       <c r="K40" t="n">
-        <v>-10.45</v>
+        <v>-11.89</v>
       </c>
       <c r="L40" t="n">
-        <v>147.46</v>
+        <v>167.79</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>325.49</v>
+        <v>370.39</v>
       </c>
       <c r="K41" t="n">
-        <v>65.34</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>331.99</v>
+        <v>377.78</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-163.67</v>
+        <v>-186.25</v>
       </c>
       <c r="K42" t="n">
-        <v>-178.67</v>
+        <v>-203.32</v>
       </c>
       <c r="L42" t="n">
-        <v>242.31</v>
+        <v>275.73</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>-238.9</v>
+        <v>-264.49</v>
       </c>
       <c r="K43" t="n">
-        <v>200.92</v>
+        <v>222.44</v>
       </c>
       <c r="L43" t="n">
-        <v>312.15</v>
+        <v>345.6</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>101.48</v>
+        <v>115.48</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.92</v>
       </c>
       <c r="L44" t="n">
-        <v>101.49</v>
+        <v>115.49</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>36.07</v>
+        <v>41.04</v>
       </c>
       <c r="K45" t="n">
-        <v>-45.94</v>
+        <v>-52.28</v>
       </c>
       <c r="L45" t="n">
-        <v>58.41</v>
+        <v>66.45999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-89.91</v>
+        <v>-102.31</v>
       </c>
       <c r="K46" t="n">
-        <v>55.11</v>
+        <v>62.72</v>
       </c>
       <c r="L46" t="n">
-        <v>105.46</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-84.34999999999999</v>
+        <v>-94.70999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-95.78</v>
+        <v>-107.54</v>
       </c>
       <c r="L47" t="n">
-        <v>127.63</v>
+        <v>143.3</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-69.81</v>
+        <v>-79.43000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>42.05</v>
+        <v>47.85</v>
       </c>
       <c r="L48" t="n">
-        <v>81.48999999999999</v>
+        <v>92.73</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>39.96</v>
+        <v>45.47</v>
       </c>
       <c r="K49" t="n">
-        <v>-93.55</v>
+        <v>-106.45</v>
       </c>
       <c r="L49" t="n">
-        <v>101.73</v>
+        <v>115.76</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>72.72</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>105.89</v>
+        <v>120.5</v>
       </c>
       <c r="L50" t="n">
-        <v>128.46</v>
+        <v>146.18</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>164.02</v>
+        <v>186.64</v>
       </c>
       <c r="L51" t="n">
-        <v>164.02</v>
+        <v>186.65</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-82.38</v>
+        <v>-93.73999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-82.42</v>
+        <v>-93.79000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>116.53</v>
+        <v>132.6</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-30.76</v>
+        <v>-35</v>
       </c>
       <c r="K53" t="n">
-        <v>-175.32</v>
+        <v>-199.5</v>
       </c>
       <c r="L53" t="n">
-        <v>178</v>
+        <v>202.55</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>126.59</v>
+        <v>144.05</v>
       </c>
       <c r="K54" t="n">
-        <v>-123.52</v>
+        <v>-140.56</v>
       </c>
       <c r="L54" t="n">
-        <v>176.87</v>
+        <v>201.27</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>-241.56</v>
+        <v>-271.22</v>
       </c>
       <c r="K55" t="n">
-        <v>85.40000000000001</v>
+        <v>95.89</v>
       </c>
       <c r="L55" t="n">
-        <v>256.21</v>
+        <v>287.68</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>45.98</v>
+        <v>50.91</v>
       </c>
       <c r="K56" t="n">
-        <v>330.89</v>
+        <v>366.34</v>
       </c>
       <c r="L56" t="n">
-        <v>334.07</v>
+        <v>369.86</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>237.3</v>
+        <v>270.03</v>
       </c>
       <c r="K57" t="n">
-        <v>104.08</v>
+        <v>118.43</v>
       </c>
       <c r="L57" t="n">
-        <v>259.12</v>
+        <v>294.86</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-205.03</v>
+        <v>-233.31</v>
       </c>
       <c r="K58" t="n">
-        <v>-241.25</v>
+        <v>-274.53</v>
       </c>
       <c r="L58" t="n">
-        <v>316.61</v>
+        <v>360.28</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-61.61</v>
+        <v>-70.11</v>
       </c>
       <c r="K59" t="n">
-        <v>-15.67</v>
+        <v>-17.83</v>
       </c>
       <c r="L59" t="n">
-        <v>63.58</v>
+        <v>72.34</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.42</v>
+        <v>-13</v>
       </c>
       <c r="K60" t="n">
-        <v>87.79000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>88.53</v>
+        <v>100.74</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>75.91</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="L61" t="n">
-        <v>75.98</v>
+        <v>85.31999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>84.34999999999999</v>
+        <v>95.98</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.46</v>
+        <v>-1.67</v>
       </c>
       <c r="L62" t="n">
-        <v>84.36</v>
+        <v>95.98999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-100.17</v>
+        <v>-110.91</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.55</v>
+        <v>-0.6</v>
       </c>
       <c r="L63" t="n">
-        <v>100.17</v>
+        <v>110.91</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>126.42</v>
+        <v>143.86</v>
       </c>
       <c r="K64" t="n">
-        <v>-52.04</v>
+        <v>-59.22</v>
       </c>
       <c r="L64" t="n">
-        <v>136.71</v>
+        <v>155.57</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.49</v>
+        <v>-10.66</v>
       </c>
       <c r="K65" t="n">
-        <v>-6.52</v>
+        <v>-7.32</v>
       </c>
       <c r="L65" t="n">
-        <v>11.52</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-172.61</v>
+        <v>-196.42</v>
       </c>
       <c r="K66" t="n">
-        <v>-69.79000000000001</v>
+        <v>-79.42</v>
       </c>
       <c r="L66" t="n">
-        <v>186.19</v>
+        <v>211.87</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-138.93</v>
+        <v>-158.1</v>
       </c>
       <c r="K67" t="n">
-        <v>56.64</v>
+        <v>64.45</v>
       </c>
       <c r="L67" t="n">
-        <v>150.04</v>
+        <v>170.73</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-154.18</v>
+        <v>-175.44</v>
       </c>
       <c r="K68" t="n">
-        <v>-53.81</v>
+        <v>-61.23</v>
       </c>
       <c r="L68" t="n">
-        <v>163.3</v>
+        <v>185.82</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-197.6</v>
+        <v>-224.85</v>
       </c>
       <c r="K69" t="n">
-        <v>-94.40000000000001</v>
+        <v>-107.43</v>
       </c>
       <c r="L69" t="n">
-        <v>218.99</v>
+        <v>249.2</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-76.67</v>
+        <v>-87.23999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>29.8</v>
+        <v>33.91</v>
       </c>
       <c r="L70" t="n">
-        <v>82.25</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>178.59</v>
+        <v>203.22</v>
       </c>
       <c r="K71" t="n">
-        <v>154.23</v>
+        <v>175.5</v>
       </c>
       <c r="L71" t="n">
-        <v>235.96</v>
+        <v>268.51</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-167.47</v>
+        <v>-190.57</v>
       </c>
       <c r="K72" t="n">
-        <v>243.37</v>
+        <v>276.94</v>
       </c>
       <c r="L72" t="n">
-        <v>295.43</v>
+        <v>336.18</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-36.09</v>
+        <v>-41.07</v>
       </c>
       <c r="K73" t="n">
-        <v>294.79</v>
+        <v>335.45</v>
       </c>
       <c r="L73" t="n">
-        <v>296.99</v>
+        <v>337.96</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-44.38</v>
+        <v>-50.5</v>
       </c>
       <c r="K74" t="n">
-        <v>-57.4</v>
+        <v>-65.31999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>72.56</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>27.78</v>
+        <v>31.61</v>
       </c>
       <c r="K75" t="n">
-        <v>92.67</v>
+        <v>105.45</v>
       </c>
       <c r="L75" t="n">
-        <v>96.73999999999999</v>
+        <v>110.08</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>17</v>
       </c>
       <c r="J76" t="n">
-        <v>15.48</v>
+        <v>17.38</v>
       </c>
       <c r="K76" t="n">
-        <v>67.40000000000001</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>69.16</v>
+        <v>77.65000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>97.13</v>
+        <v>109.06</v>
       </c>
       <c r="K77" t="n">
-        <v>39.99</v>
+        <v>44.9</v>
       </c>
       <c r="L77" t="n">
-        <v>105.04</v>
+        <v>117.94</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-9.779999999999999</v>
+        <v>-11.13</v>
       </c>
       <c r="K78" t="n">
-        <v>-109.64</v>
+        <v>-124.76</v>
       </c>
       <c r="L78" t="n">
-        <v>110.07</v>
+        <v>125.25</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>118.06</v>
+        <v>134.34</v>
       </c>
       <c r="K79" t="n">
-        <v>-40.85</v>
+        <v>-46.49</v>
       </c>
       <c r="L79" t="n">
-        <v>124.93</v>
+        <v>142.16</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-105.9</v>
+        <v>-120.51</v>
       </c>
       <c r="K80" t="n">
-        <v>-89.75</v>
+        <v>-102.13</v>
       </c>
       <c r="L80" t="n">
-        <v>138.82</v>
+        <v>157.97</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>51.14</v>
+        <v>57.42</v>
       </c>
       <c r="K81" t="n">
-        <v>123.08</v>
+        <v>138.19</v>
       </c>
       <c r="L81" t="n">
-        <v>133.28</v>
+        <v>149.64</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-76.56</v>
+        <v>-85.97</v>
       </c>
       <c r="K82" t="n">
-        <v>93.59999999999999</v>
+        <v>105.09</v>
       </c>
       <c r="L82" t="n">
-        <v>120.92</v>
+        <v>135.77</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>236.17</v>
+        <v>268.74</v>
       </c>
       <c r="K83" t="n">
-        <v>5.6</v>
+        <v>6.37</v>
       </c>
       <c r="L83" t="n">
-        <v>236.23</v>
+        <v>268.82</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>32.36</v>
+        <v>36.82</v>
       </c>
       <c r="K84" t="n">
-        <v>182.12</v>
+        <v>207.24</v>
       </c>
       <c r="L84" t="n">
-        <v>184.98</v>
+        <v>210.49</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-96.68000000000001</v>
+        <v>-110.02</v>
       </c>
       <c r="K85" t="n">
-        <v>169.21</v>
+        <v>192.55</v>
       </c>
       <c r="L85" t="n">
-        <v>194.89</v>
+        <v>221.77</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>17</v>
       </c>
       <c r="J86" t="n">
-        <v>41.2</v>
+        <v>46.26</v>
       </c>
       <c r="K86" t="n">
-        <v>-27.83</v>
+        <v>-31.25</v>
       </c>
       <c r="L86" t="n">
-        <v>49.72</v>
+        <v>55.83</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-123.4</v>
+        <v>-140.42</v>
       </c>
       <c r="K87" t="n">
-        <v>312.72</v>
+        <v>355.85</v>
       </c>
       <c r="L87" t="n">
-        <v>336.18</v>
+        <v>382.56</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-274.72</v>
+        <v>-312.61</v>
       </c>
       <c r="K88" t="n">
-        <v>98.33</v>
+        <v>111.9</v>
       </c>
       <c r="L88" t="n">
-        <v>291.79</v>
+        <v>332.04</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-09.xlsx
+++ b/output/2025-08-09.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="F14" t="n">
-        <v>5.38</v>
+        <v>7.55</v>
       </c>
       <c r="G14" t="n">
-        <v>277.6</v>
+        <v>286.9</v>
       </c>
       <c r="H14" t="n">
-        <v>99.3</v>
+        <v>59</v>
       </c>
       <c r="I14" t="n">
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>21.69</v>
+        <v>-12.27</v>
       </c>
       <c r="K14" t="n">
-        <v>70.29000000000001</v>
+        <v>-28.65</v>
       </c>
       <c r="L14" t="n">
-        <v>73.56</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:36:57</t>
+          <t>05:37:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="F15" t="n">
-        <v>8.58</v>
+        <v>6.96</v>
       </c>
       <c r="G15" t="n">
-        <v>303.1</v>
+        <v>316.8</v>
       </c>
       <c r="H15" t="n">
-        <v>93.7</v>
+        <v>63.1</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>50.72</v>
+        <v>-11.73</v>
       </c>
       <c r="K15" t="n">
-        <v>-48.04</v>
+        <v>32.67</v>
       </c>
       <c r="L15" t="n">
-        <v>69.86</v>
+        <v>34.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:38:53</t>
+          <t>05:38:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="F16" t="n">
-        <v>3.38</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>297.9</v>
+        <v>275.7</v>
       </c>
       <c r="H16" t="n">
-        <v>88.90000000000001</v>
+        <v>43.9</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-51.56</v>
+        <v>40.91</v>
       </c>
       <c r="K16" t="n">
-        <v>59.53</v>
+        <v>25.71</v>
       </c>
       <c r="L16" t="n">
-        <v>78.75</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:43:15</t>
+          <t>05:43:06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.72</v>
+        <v>2.25</v>
       </c>
       <c r="F17" t="n">
-        <v>9.52</v>
+        <v>7.27</v>
       </c>
       <c r="G17" t="n">
-        <v>286.5</v>
+        <v>280.9</v>
       </c>
       <c r="H17" t="n">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>101.38</v>
+        <v>-52.7</v>
       </c>
       <c r="K17" t="n">
-        <v>-78.20999999999999</v>
+        <v>-13.71</v>
       </c>
       <c r="L17" t="n">
-        <v>128.04</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:45:14</t>
+          <t>05:44:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="F18" t="n">
-        <v>10.63</v>
+        <v>7.1</v>
       </c>
       <c r="G18" t="n">
-        <v>285.1</v>
+        <v>292.1</v>
       </c>
       <c r="H18" t="n">
-        <v>84.7</v>
+        <v>46.2</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>95.47</v>
+        <v>-32.88</v>
       </c>
       <c r="K18" t="n">
-        <v>31.04</v>
+        <v>72.97</v>
       </c>
       <c r="L18" t="n">
-        <v>100.39</v>
+        <v>80.04000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:47:15</t>
+          <t>05:45:20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.29</v>
+        <v>3.6</v>
       </c>
       <c r="F19" t="n">
-        <v>4.46</v>
+        <v>7.94</v>
       </c>
       <c r="G19" t="n">
-        <v>280.2</v>
+        <v>291.2</v>
       </c>
       <c r="H19" t="n">
-        <v>95.40000000000001</v>
+        <v>55.8</v>
       </c>
       <c r="I19" t="n">
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-63.64</v>
+        <v>-34.39</v>
       </c>
       <c r="K19" t="n">
-        <v>-45.47</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>78.20999999999999</v>
+        <v>81.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:52:07</t>
+          <t>05:49:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.89</v>
+        <v>1.84</v>
       </c>
       <c r="F20" t="n">
-        <v>7.33</v>
+        <v>3.95</v>
       </c>
       <c r="G20" t="n">
-        <v>285.6</v>
+        <v>288.3</v>
       </c>
       <c r="H20" t="n">
-        <v>92.59999999999999</v>
+        <v>33.9</v>
       </c>
       <c r="I20" t="n">
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-70.48</v>
+        <v>-10.88</v>
       </c>
       <c r="K20" t="n">
-        <v>96.97</v>
+        <v>-60.29</v>
       </c>
       <c r="L20" t="n">
-        <v>119.88</v>
+        <v>61.26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:53:14</t>
+          <t>05:50:48</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="F21" t="n">
-        <v>7.91</v>
+        <v>7.61</v>
       </c>
       <c r="G21" t="n">
-        <v>296.6</v>
+        <v>269</v>
       </c>
       <c r="H21" t="n">
-        <v>90.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>140.39</v>
+        <v>-3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>-59.9</v>
+        <v>97.78</v>
       </c>
       <c r="L21" t="n">
-        <v>152.64</v>
+        <v>97.84999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:54:56</t>
+          <t>05:52:38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="F22" t="n">
-        <v>10.7</v>
+        <v>10.31</v>
       </c>
       <c r="G22" t="n">
-        <v>288.9</v>
+        <v>287.3</v>
       </c>
       <c r="H22" t="n">
-        <v>90.40000000000001</v>
+        <v>15.8</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-184.44</v>
+        <v>-73.95</v>
       </c>
       <c r="K22" t="n">
-        <v>-12.87</v>
+        <v>75.5</v>
       </c>
       <c r="L22" t="n">
-        <v>184.89</v>
+        <v>105.69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:00:12</t>
+          <t>05:58:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="F23" t="n">
-        <v>7.83</v>
+        <v>6.56</v>
       </c>
       <c r="G23" t="n">
-        <v>280.9</v>
+        <v>284.9</v>
       </c>
       <c r="H23" t="n">
-        <v>89.40000000000001</v>
+        <v>51.3</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>187.17</v>
+        <v>-103.93</v>
       </c>
       <c r="K23" t="n">
-        <v>-146.42</v>
+        <v>-48.62</v>
       </c>
       <c r="L23" t="n">
-        <v>237.64</v>
+        <v>114.74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:01:34</t>
+          <t>06:00:23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="F24" t="n">
-        <v>6.3</v>
+        <v>8.76</v>
       </c>
       <c r="G24" t="n">
-        <v>297.7</v>
+        <v>282</v>
       </c>
       <c r="H24" t="n">
-        <v>89.90000000000001</v>
+        <v>49.1</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>118.85</v>
+        <v>36.94</v>
       </c>
       <c r="K24" t="n">
-        <v>-102.13</v>
+        <v>-108.77</v>
       </c>
       <c r="L24" t="n">
-        <v>156.7</v>
+        <v>114.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:03:19</t>
+          <t>06:01:58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="F25" t="n">
-        <v>4.74</v>
+        <v>6.96</v>
       </c>
       <c r="G25" t="n">
-        <v>285.3</v>
+        <v>284.6</v>
       </c>
       <c r="H25" t="n">
-        <v>94</v>
+        <v>60.7</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-107.8</v>
+        <v>-16.29</v>
       </c>
       <c r="K25" t="n">
-        <v>-113</v>
+        <v>-0.28</v>
       </c>
       <c r="L25" t="n">
-        <v>156.17</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:06:58</t>
+          <t>06:06:23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1132,31 +1132,31 @@
         <v>2.4</v>
       </c>
       <c r="F26" t="n">
-        <v>7.42</v>
+        <v>7.87</v>
       </c>
       <c r="G26" t="n">
-        <v>302</v>
+        <v>293.1</v>
       </c>
       <c r="H26" t="n">
-        <v>93.2</v>
+        <v>54.1</v>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>105.64</v>
+        <v>-112.19</v>
       </c>
       <c r="K26" t="n">
-        <v>-195.25</v>
+        <v>143.2</v>
       </c>
       <c r="L26" t="n">
-        <v>222</v>
+        <v>181.92</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:08:00</t>
+          <t>06:08:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6</v>
+        <v>3.02</v>
       </c>
       <c r="F27" t="n">
-        <v>7.19</v>
+        <v>8.69</v>
       </c>
       <c r="G27" t="n">
-        <v>286.4</v>
+        <v>289.3</v>
       </c>
       <c r="H27" t="n">
-        <v>93.09999999999999</v>
+        <v>60.5</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>287.81</v>
+        <v>164.98</v>
       </c>
       <c r="K27" t="n">
-        <v>170.45</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>334.49</v>
+        <v>188.38</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:09:53</t>
+          <t>06:09:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.79</v>
+        <v>2.13</v>
       </c>
       <c r="F28" t="n">
-        <v>6.91</v>
+        <v>5.85</v>
       </c>
       <c r="G28" t="n">
-        <v>285.7</v>
+        <v>302.8</v>
       </c>
       <c r="H28" t="n">
-        <v>92.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-112.48</v>
+        <v>-99.77</v>
       </c>
       <c r="K28" t="n">
-        <v>312.33</v>
+        <v>-112.06</v>
       </c>
       <c r="L28" t="n">
-        <v>331.96</v>
+        <v>150.04</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:19:58</t>
+          <t>06:19:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="F29" t="n">
-        <v>4.63</v>
+        <v>10.7</v>
       </c>
       <c r="G29" t="n">
-        <v>274.5</v>
+        <v>287.8</v>
       </c>
       <c r="H29" t="n">
-        <v>86.5</v>
+        <v>47.1</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>11.17</v>
+        <v>-34.76</v>
       </c>
       <c r="K29" t="n">
-        <v>63.25</v>
+        <v>9.17</v>
       </c>
       <c r="L29" t="n">
-        <v>64.23</v>
+        <v>35.95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:21:50</t>
+          <t>06:21:10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.28</v>
+        <v>2.61</v>
       </c>
       <c r="F30" t="n">
-        <v>9.85</v>
+        <v>10.7</v>
       </c>
       <c r="G30" t="n">
-        <v>289.8</v>
+        <v>300.3</v>
       </c>
       <c r="H30" t="n">
-        <v>86.40000000000001</v>
+        <v>36.2</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>52.43</v>
+        <v>2.64</v>
       </c>
       <c r="K30" t="n">
-        <v>-61.76</v>
+        <v>38.13</v>
       </c>
       <c r="L30" t="n">
-        <v>81.01000000000001</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:23:39</t>
+          <t>06:22:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,28 +1339,28 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="F31" t="n">
-        <v>10.13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>291.1</v>
+        <v>266.7</v>
       </c>
       <c r="H31" t="n">
-        <v>93.2</v>
+        <v>70.8</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-57.92</v>
+        <v>-26.76</v>
       </c>
       <c r="K31" t="n">
-        <v>-101.21</v>
+        <v>19.85</v>
       </c>
       <c r="L31" t="n">
-        <v>116.61</v>
+        <v>33.32</v>
       </c>
     </row>
     <row r="32">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.79</v>
+        <v>2.51</v>
       </c>
       <c r="F32" t="n">
-        <v>5.98</v>
+        <v>10.7</v>
       </c>
       <c r="G32" t="n">
-        <v>291.6</v>
+        <v>279.7</v>
       </c>
       <c r="H32" t="n">
-        <v>94.40000000000001</v>
+        <v>33.4</v>
       </c>
       <c r="I32" t="n">
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-37.89</v>
+        <v>-39.77</v>
       </c>
       <c r="K32" t="n">
-        <v>-89.11</v>
+        <v>54.11</v>
       </c>
       <c r="L32" t="n">
-        <v>96.83</v>
+        <v>67.15000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:28:59</t>
+          <t>06:30:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.57</v>
+        <v>2.11</v>
       </c>
       <c r="F33" t="n">
-        <v>8.31</v>
+        <v>10.63</v>
       </c>
       <c r="G33" t="n">
-        <v>295.3</v>
+        <v>291.3</v>
       </c>
       <c r="H33" t="n">
-        <v>93.3</v>
+        <v>66</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>-100.08</v>
+        <v>24.11</v>
       </c>
       <c r="K33" t="n">
-        <v>93.77</v>
+        <v>47.26</v>
       </c>
       <c r="L33" t="n">
-        <v>137.15</v>
+        <v>53.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:31:11</t>
+          <t>06:32:39</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="F34" t="n">
-        <v>6.54</v>
+        <v>6.13</v>
       </c>
       <c r="G34" t="n">
-        <v>290.5</v>
+        <v>287.3</v>
       </c>
       <c r="H34" t="n">
-        <v>87.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-56.15</v>
+        <v>-71.58</v>
       </c>
       <c r="K34" t="n">
-        <v>80.06999999999999</v>
+        <v>-13.15</v>
       </c>
       <c r="L34" t="n">
-        <v>97.8</v>
+        <v>72.78</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:35:14</t>
+          <t>06:37:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.62</v>
+        <v>3.03</v>
       </c>
       <c r="F35" t="n">
-        <v>7.34</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>284.7</v>
+        <v>299.5</v>
       </c>
       <c r="H35" t="n">
-        <v>97.90000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>-185.61</v>
+        <v>-106.41</v>
       </c>
       <c r="K35" t="n">
-        <v>-79.63</v>
+        <v>24.69</v>
       </c>
       <c r="L35" t="n">
-        <v>201.97</v>
+        <v>109.24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:36:45</t>
+          <t>06:40:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.29</v>
+        <v>2.53</v>
       </c>
       <c r="F36" t="n">
-        <v>8.109999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>288.1</v>
+        <v>268.8</v>
       </c>
       <c r="H36" t="n">
-        <v>94.7</v>
+        <v>77.7</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-44.2</v>
+        <v>83.2</v>
       </c>
       <c r="K36" t="n">
-        <v>197.79</v>
+        <v>-57.41</v>
       </c>
       <c r="L36" t="n">
-        <v>202.67</v>
+        <v>101.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:37:19</t>
+          <t>06:41:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="F37" t="n">
-        <v>5.28</v>
+        <v>7.77</v>
       </c>
       <c r="G37" t="n">
-        <v>305.4</v>
+        <v>290.6</v>
       </c>
       <c r="H37" t="n">
-        <v>84.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="I37" t="n">
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>59.09</v>
+        <v>-64.05</v>
       </c>
       <c r="K37" t="n">
-        <v>104.01</v>
+        <v>5.24</v>
       </c>
       <c r="L37" t="n">
-        <v>119.63</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:42:11</t>
+          <t>06:46:24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="F38" t="n">
-        <v>8.789999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="G38" t="n">
-        <v>284.2</v>
+        <v>294.1</v>
       </c>
       <c r="H38" t="n">
-        <v>91.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>181.1</v>
+        <v>98.73</v>
       </c>
       <c r="K38" t="n">
-        <v>19.3</v>
+        <v>89</v>
       </c>
       <c r="L38" t="n">
-        <v>182.13</v>
+        <v>132.93</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>06:47:51</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="F39" t="n">
-        <v>9.9</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>278.8</v>
+        <v>294.1</v>
       </c>
       <c r="H39" t="n">
-        <v>87.40000000000001</v>
+        <v>54.1</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-218.35</v>
+        <v>-72.29000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>73.86</v>
+        <v>-93.40000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>230.51</v>
+        <v>118.11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:46:45</t>
+          <t>06:49:28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.49</v>
+        <v>2.12</v>
       </c>
       <c r="F40" t="n">
-        <v>7.09</v>
+        <v>9.69</v>
       </c>
       <c r="G40" t="n">
-        <v>285.2</v>
+        <v>274.6</v>
       </c>
       <c r="H40" t="n">
-        <v>95.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I40" t="n">
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-167.37</v>
+        <v>-55.65</v>
       </c>
       <c r="K40" t="n">
-        <v>-11.89</v>
+        <v>-212.5</v>
       </c>
       <c r="L40" t="n">
-        <v>167.79</v>
+        <v>219.67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:52:19</t>
+          <t>06:54:41</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="F41" t="n">
-        <v>10.7</v>
+        <v>9.82</v>
       </c>
       <c r="G41" t="n">
-        <v>292.6</v>
+        <v>287.8</v>
       </c>
       <c r="H41" t="n">
-        <v>82.7</v>
+        <v>70.3</v>
       </c>
       <c r="I41" t="n">
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>370.39</v>
+        <v>-198.4</v>
       </c>
       <c r="K41" t="n">
-        <v>74.34999999999999</v>
+        <v>-22.92</v>
       </c>
       <c r="L41" t="n">
-        <v>377.78</v>
+        <v>199.72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:52:59</t>
+          <t>06:56:41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="F42" t="n">
-        <v>7.24</v>
+        <v>10.7</v>
       </c>
       <c r="G42" t="n">
-        <v>285</v>
+        <v>300.6</v>
       </c>
       <c r="H42" t="n">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-186.25</v>
+        <v>-13.71</v>
       </c>
       <c r="K42" t="n">
-        <v>-203.32</v>
+        <v>190.51</v>
       </c>
       <c r="L42" t="n">
-        <v>275.73</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:55:03</t>
+          <t>06:57:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="F43" t="n">
         <v>10.7</v>
       </c>
       <c r="G43" t="n">
-        <v>281.1</v>
+        <v>292.5</v>
       </c>
       <c r="H43" t="n">
-        <v>91.90000000000001</v>
+        <v>55.8</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-264.49</v>
+        <v>-2.05</v>
       </c>
       <c r="K43" t="n">
-        <v>222.44</v>
+        <v>200.05</v>
       </c>
       <c r="L43" t="n">
-        <v>345.6</v>
+        <v>200.06</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:05:04</t>
+          <t>07:09:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="F44" t="n">
         <v>10.7</v>
       </c>
       <c r="G44" t="n">
-        <v>286.2</v>
+        <v>291.3</v>
       </c>
       <c r="H44" t="n">
-        <v>80.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>115.48</v>
+        <v>-23.98</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.92</v>
+        <v>21.35</v>
       </c>
       <c r="L44" t="n">
-        <v>115.49</v>
+        <v>32.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:05:55</t>
+          <t>07:10:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.8</v>
+        <v>2.59</v>
       </c>
       <c r="F45" t="n">
-        <v>6.26</v>
+        <v>10.7</v>
       </c>
       <c r="G45" t="n">
-        <v>280.6</v>
+        <v>281.5</v>
       </c>
       <c r="H45" t="n">
-        <v>89.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>41.04</v>
+        <v>-19.18</v>
       </c>
       <c r="K45" t="n">
-        <v>-52.28</v>
+        <v>36.66</v>
       </c>
       <c r="L45" t="n">
-        <v>66.45999999999999</v>
+        <v>41.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:07:09</t>
+          <t>07:12:29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.74</v>
+        <v>2.32</v>
       </c>
       <c r="F46" t="n">
-        <v>9.1</v>
+        <v>8.09</v>
       </c>
       <c r="G46" t="n">
-        <v>288.3</v>
+        <v>288.5</v>
       </c>
       <c r="H46" t="n">
-        <v>87.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="I46" t="n">
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-102.31</v>
+        <v>-25.13</v>
       </c>
       <c r="K46" t="n">
-        <v>62.72</v>
+        <v>-13.67</v>
       </c>
       <c r="L46" t="n">
-        <v>120</v>
+        <v>28.61</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:11:39</t>
+          <t>07:18:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.59</v>
+        <v>2.37</v>
       </c>
       <c r="F47" t="n">
-        <v>9.279999999999999</v>
+        <v>7.36</v>
       </c>
       <c r="G47" t="n">
-        <v>283.8</v>
+        <v>291.7</v>
       </c>
       <c r="H47" t="n">
-        <v>83</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-94.70999999999999</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-107.54</v>
+        <v>19.25</v>
       </c>
       <c r="L47" t="n">
-        <v>143.3</v>
+        <v>67.14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:13:31</t>
+          <t>07:20:48</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="F48" t="n">
-        <v>10.3</v>
+        <v>7.98</v>
       </c>
       <c r="G48" t="n">
-        <v>297.6</v>
+        <v>289.9</v>
       </c>
       <c r="H48" t="n">
-        <v>94</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-79.43000000000001</v>
+        <v>77.67</v>
       </c>
       <c r="K48" t="n">
-        <v>47.85</v>
+        <v>-2.72</v>
       </c>
       <c r="L48" t="n">
-        <v>92.73</v>
+        <v>77.70999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:15:08</t>
+          <t>07:22:31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.17</v>
+        <v>2.41</v>
       </c>
       <c r="F49" t="n">
         <v>10.7</v>
       </c>
       <c r="G49" t="n">
-        <v>300</v>
+        <v>290.6</v>
       </c>
       <c r="H49" t="n">
-        <v>90.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I49" t="n">
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>45.47</v>
+        <v>11.19</v>
       </c>
       <c r="K49" t="n">
-        <v>-106.45</v>
+        <v>-59.5</v>
       </c>
       <c r="L49" t="n">
-        <v>115.76</v>
+        <v>60.54</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:19:50</t>
+          <t>07:27:50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="F50" t="n">
-        <v>9.859999999999999</v>
+        <v>7.57</v>
       </c>
       <c r="G50" t="n">
-        <v>301.5</v>
+        <v>286</v>
       </c>
       <c r="H50" t="n">
-        <v>92.8</v>
+        <v>31.2</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>82.76000000000001</v>
+        <v>77.33</v>
       </c>
       <c r="K50" t="n">
-        <v>120.5</v>
+        <v>-16.27</v>
       </c>
       <c r="L50" t="n">
-        <v>146.18</v>
+        <v>79.02</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:21:36</t>
+          <t>07:29:05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="F51" t="n">
-        <v>5.86</v>
+        <v>6.02</v>
       </c>
       <c r="G51" t="n">
-        <v>299.9</v>
+        <v>281.1</v>
       </c>
       <c r="H51" t="n">
-        <v>89.09999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="I51" t="n">
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9399999999999999</v>
+        <v>-37.54</v>
       </c>
       <c r="K51" t="n">
-        <v>186.64</v>
+        <v>-56.98</v>
       </c>
       <c r="L51" t="n">
-        <v>186.65</v>
+        <v>68.23999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:22:52</t>
+          <t>07:30:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.62</v>
+        <v>3.09</v>
       </c>
       <c r="F52" t="n">
-        <v>9.19</v>
+        <v>4.31</v>
       </c>
       <c r="G52" t="n">
-        <v>287.4</v>
+        <v>318.8</v>
       </c>
       <c r="H52" t="n">
-        <v>84.90000000000001</v>
+        <v>37.5</v>
       </c>
       <c r="I52" t="n">
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-93.73999999999999</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-93.79000000000001</v>
+        <v>140.86</v>
       </c>
       <c r="L52" t="n">
-        <v>132.6</v>
+        <v>141.18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:27:49</t>
+          <t>07:36:19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="F53" t="n">
-        <v>10.7</v>
+        <v>10.49</v>
       </c>
       <c r="G53" t="n">
-        <v>295.1</v>
+        <v>294.7</v>
       </c>
       <c r="H53" t="n">
-        <v>89.5</v>
+        <v>48.8</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-35</v>
+        <v>-17.2</v>
       </c>
       <c r="K53" t="n">
-        <v>-199.5</v>
+        <v>133.24</v>
       </c>
       <c r="L53" t="n">
-        <v>202.55</v>
+        <v>134.34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>07:38:16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.46</v>
+        <v>2.84</v>
       </c>
       <c r="F54" t="n">
-        <v>9.720000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G54" t="n">
-        <v>287.3</v>
+        <v>293.2</v>
       </c>
       <c r="H54" t="n">
-        <v>82.3</v>
+        <v>28</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>144.05</v>
+        <v>-155.42</v>
       </c>
       <c r="K54" t="n">
-        <v>-140.56</v>
+        <v>39.23</v>
       </c>
       <c r="L54" t="n">
-        <v>201.27</v>
+        <v>160.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:31:50</t>
+          <t>07:40:48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="F55" t="n">
-        <v>10.55</v>
+        <v>7.89</v>
       </c>
       <c r="G55" t="n">
-        <v>299.7</v>
+        <v>279.7</v>
       </c>
       <c r="H55" t="n">
-        <v>91.5</v>
+        <v>70.7</v>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>-271.22</v>
+        <v>144.7</v>
       </c>
       <c r="K55" t="n">
-        <v>95.89</v>
+        <v>18.63</v>
       </c>
       <c r="L55" t="n">
-        <v>287.68</v>
+        <v>145.89</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:36:33</t>
+          <t>07:45:25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="F56" t="n">
-        <v>8.279999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="G56" t="n">
-        <v>302.4</v>
+        <v>296.8</v>
       </c>
       <c r="H56" t="n">
-        <v>92.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>50.91</v>
+        <v>-210.11</v>
       </c>
       <c r="K56" t="n">
-        <v>366.34</v>
+        <v>14.45</v>
       </c>
       <c r="L56" t="n">
-        <v>369.86</v>
+        <v>210.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:38:29</t>
+          <t>07:46:07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.14</v>
+        <v>3.03</v>
       </c>
       <c r="F57" t="n">
         <v>10.7</v>
       </c>
       <c r="G57" t="n">
-        <v>272.3</v>
+        <v>296.6</v>
       </c>
       <c r="H57" t="n">
-        <v>93.3</v>
+        <v>62.8</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>270.03</v>
+        <v>-113.5</v>
       </c>
       <c r="K57" t="n">
-        <v>118.43</v>
+        <v>120.3</v>
       </c>
       <c r="L57" t="n">
-        <v>294.86</v>
+        <v>165.39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:39:40</t>
+          <t>07:47:55</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.43</v>
+        <v>2.89</v>
       </c>
       <c r="F58" t="n">
-        <v>9.99</v>
+        <v>10.7</v>
       </c>
       <c r="G58" t="n">
-        <v>289.8</v>
+        <v>320.6</v>
       </c>
       <c r="H58" t="n">
-        <v>87.2</v>
+        <v>76.8</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-233.31</v>
+        <v>-111.69</v>
       </c>
       <c r="K58" t="n">
-        <v>-274.53</v>
+        <v>225.61</v>
       </c>
       <c r="L58" t="n">
-        <v>360.28</v>
+        <v>251.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:46:58</t>
+          <t>07:57:45</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="F59" t="n">
-        <v>7.54</v>
+        <v>8.94</v>
       </c>
       <c r="G59" t="n">
-        <v>297.7</v>
+        <v>289.9</v>
       </c>
       <c r="H59" t="n">
-        <v>90.40000000000001</v>
+        <v>50.2</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-70.11</v>
+        <v>34.08</v>
       </c>
       <c r="K59" t="n">
-        <v>-17.83</v>
+        <v>17.71</v>
       </c>
       <c r="L59" t="n">
-        <v>72.34</v>
+        <v>38.41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:47:52</t>
+          <t>07:59:15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="F60" t="n">
-        <v>6.64</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G60" t="n">
         <v>284.7</v>
       </c>
       <c r="H60" t="n">
-        <v>87.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="I60" t="n">
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-13</v>
+        <v>14.29</v>
       </c>
       <c r="K60" t="n">
-        <v>99.90000000000001</v>
+        <v>28.7</v>
       </c>
       <c r="L60" t="n">
-        <v>100.74</v>
+        <v>32.06</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:50:30</t>
+          <t>08:00:08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.73</v>
+        <v>2.33</v>
       </c>
       <c r="F61" t="n">
-        <v>9.25</v>
+        <v>10.7</v>
       </c>
       <c r="G61" t="n">
-        <v>285.4</v>
+        <v>304.1</v>
       </c>
       <c r="H61" t="n">
-        <v>89.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="I61" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>85.23999999999999</v>
+        <v>-44.11</v>
       </c>
       <c r="K61" t="n">
-        <v>3.66</v>
+        <v>7.9</v>
       </c>
       <c r="L61" t="n">
-        <v>85.31999999999999</v>
+        <v>44.81</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:54:06</t>
+          <t>08:04:20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="F62" t="n">
-        <v>8.94</v>
+        <v>10.7</v>
       </c>
       <c r="G62" t="n">
-        <v>294.3</v>
+        <v>291</v>
       </c>
       <c r="H62" t="n">
-        <v>95.09999999999999</v>
+        <v>53.1</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>95.98</v>
+        <v>51.74</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.67</v>
+        <v>-9.34</v>
       </c>
       <c r="L62" t="n">
-        <v>95.98999999999999</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:56:36</t>
+          <t>08:06:39</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="F63" t="n">
-        <v>7.32</v>
+        <v>8.17</v>
       </c>
       <c r="G63" t="n">
-        <v>288.6</v>
+        <v>283.8</v>
       </c>
       <c r="H63" t="n">
-        <v>87.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-110.91</v>
+        <v>-62.54</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.6</v>
+        <v>38.19</v>
       </c>
       <c r="L63" t="n">
-        <v>110.91</v>
+        <v>73.27</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:57:23</t>
+          <t>08:08:19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="F64" t="n">
         <v>10.7</v>
       </c>
       <c r="G64" t="n">
-        <v>298.6</v>
+        <v>291.6</v>
       </c>
       <c r="H64" t="n">
-        <v>90.5</v>
+        <v>62.3</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>143.86</v>
+        <v>2.48</v>
       </c>
       <c r="K64" t="n">
-        <v>-59.22</v>
+        <v>-66.59999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>155.57</v>
+        <v>66.65000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:01:29</t>
+          <t>08:12:16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.02</v>
+        <v>2.46</v>
       </c>
       <c r="F65" t="n">
-        <v>10.7</v>
+        <v>10.13</v>
       </c>
       <c r="G65" t="n">
-        <v>291.7</v>
+        <v>300.5</v>
       </c>
       <c r="H65" t="n">
-        <v>93.5</v>
+        <v>62.1</v>
       </c>
       <c r="I65" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.66</v>
+        <v>-88.64</v>
       </c>
       <c r="K65" t="n">
-        <v>-7.32</v>
+        <v>-54.77</v>
       </c>
       <c r="L65" t="n">
-        <v>12.93</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:03:31</t>
+          <t>08:13:34</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.76</v>
+        <v>1.87</v>
       </c>
       <c r="F66" t="n">
-        <v>10.7</v>
+        <v>5.55</v>
       </c>
       <c r="G66" t="n">
-        <v>285.6</v>
+        <v>292.8</v>
       </c>
       <c r="H66" t="n">
-        <v>90.2</v>
+        <v>87.2</v>
       </c>
       <c r="I66" t="n">
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-196.42</v>
+        <v>-81.59</v>
       </c>
       <c r="K66" t="n">
-        <v>-79.42</v>
+        <v>-7.73</v>
       </c>
       <c r="L66" t="n">
-        <v>211.87</v>
+        <v>81.95999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:04:47</t>
+          <t>08:15:29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="F67" t="n">
-        <v>10.39</v>
+        <v>10.7</v>
       </c>
       <c r="G67" t="n">
-        <v>296.3</v>
+        <v>286</v>
       </c>
       <c r="H67" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="I67" t="n">
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-158.1</v>
+        <v>-134.81</v>
       </c>
       <c r="K67" t="n">
-        <v>64.45</v>
+        <v>11.83</v>
       </c>
       <c r="L67" t="n">
-        <v>170.73</v>
+        <v>135.33</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:09:18</t>
+          <t>08:20:21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="F68" t="n">
         <v>10.7</v>
       </c>
       <c r="G68" t="n">
-        <v>310.1</v>
+        <v>288.8</v>
       </c>
       <c r="H68" t="n">
-        <v>88</v>
+        <v>38.5</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-175.44</v>
+        <v>-99.31</v>
       </c>
       <c r="K68" t="n">
-        <v>-61.23</v>
+        <v>-158</v>
       </c>
       <c r="L68" t="n">
-        <v>185.82</v>
+        <v>186.62</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:10:24</t>
+          <t>08:22:43</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="F69" t="n">
-        <v>9.67</v>
+        <v>10.7</v>
       </c>
       <c r="G69" t="n">
-        <v>302.1</v>
+        <v>290.5</v>
       </c>
       <c r="H69" t="n">
-        <v>87.3</v>
+        <v>91.3</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-224.85</v>
+        <v>-108.72</v>
       </c>
       <c r="K69" t="n">
-        <v>-107.43</v>
+        <v>59.11</v>
       </c>
       <c r="L69" t="n">
-        <v>249.2</v>
+        <v>123.75</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:11:24</t>
+          <t>08:24:04</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="F70" t="n">
-        <v>9.41</v>
+        <v>10.56</v>
       </c>
       <c r="G70" t="n">
-        <v>302.5</v>
+        <v>303</v>
       </c>
       <c r="H70" t="n">
-        <v>91.40000000000001</v>
+        <v>38.5</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-87.23999999999999</v>
+        <v>-7.45</v>
       </c>
       <c r="K70" t="n">
-        <v>33.91</v>
+        <v>136.03</v>
       </c>
       <c r="L70" t="n">
-        <v>93.59999999999999</v>
+        <v>136.23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:15:57</t>
+          <t>08:29:06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.01</v>
+        <v>2.78</v>
       </c>
       <c r="F71" t="n">
         <v>10.7</v>
       </c>
       <c r="G71" t="n">
-        <v>295.4</v>
+        <v>290.2</v>
       </c>
       <c r="H71" t="n">
-        <v>90.5</v>
+        <v>94.2</v>
       </c>
       <c r="I71" t="n">
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>203.22</v>
+        <v>158.91</v>
       </c>
       <c r="K71" t="n">
-        <v>175.5</v>
+        <v>109.21</v>
       </c>
       <c r="L71" t="n">
-        <v>268.51</v>
+        <v>192.82</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:16:34</t>
+          <t>08:30:33</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="F72" t="n">
-        <v>7.44</v>
+        <v>10.7</v>
       </c>
       <c r="G72" t="n">
-        <v>291</v>
+        <v>278.2</v>
       </c>
       <c r="H72" t="n">
-        <v>87.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-190.57</v>
+        <v>223.83</v>
       </c>
       <c r="K72" t="n">
-        <v>276.94</v>
+        <v>34.95</v>
       </c>
       <c r="L72" t="n">
-        <v>336.18</v>
+        <v>226.55</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:18:03</t>
+          <t>08:31:48</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="F73" t="n">
-        <v>8.23</v>
+        <v>8.4</v>
       </c>
       <c r="G73" t="n">
-        <v>291.6</v>
+        <v>284.4</v>
       </c>
       <c r="H73" t="n">
-        <v>87.8</v>
+        <v>45.4</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-41.07</v>
+        <v>-177.58</v>
       </c>
       <c r="K73" t="n">
-        <v>335.45</v>
+        <v>4.95</v>
       </c>
       <c r="L73" t="n">
-        <v>337.96</v>
+        <v>177.64</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:28:36</t>
+          <t>08:41:44</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="F74" t="n">
-        <v>10.53</v>
+        <v>10.7</v>
       </c>
       <c r="G74" t="n">
-        <v>289.1</v>
+        <v>292.8</v>
       </c>
       <c r="H74" t="n">
-        <v>91.2</v>
+        <v>92.2</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>-50.5</v>
+        <v>-31.05</v>
       </c>
       <c r="K74" t="n">
-        <v>-65.31999999999999</v>
+        <v>24.74</v>
       </c>
       <c r="L74" t="n">
-        <v>82.56</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:30:43</t>
+          <t>08:43:16</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="F75" t="n">
-        <v>8.359999999999999</v>
+        <v>7.57</v>
       </c>
       <c r="G75" t="n">
-        <v>289.7</v>
+        <v>292.5</v>
       </c>
       <c r="H75" t="n">
-        <v>93.5</v>
+        <v>64.5</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>31.61</v>
+        <v>43.03</v>
       </c>
       <c r="K75" t="n">
-        <v>105.45</v>
+        <v>2.91</v>
       </c>
       <c r="L75" t="n">
-        <v>110.08</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:31:38</t>
+          <t>08:45:14</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="F76" t="n">
-        <v>10.7</v>
+        <v>9.23</v>
       </c>
       <c r="G76" t="n">
-        <v>308.4</v>
+        <v>294.5</v>
       </c>
       <c r="H76" t="n">
-        <v>93.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>17.38</v>
+        <v>-43.09</v>
       </c>
       <c r="K76" t="n">
-        <v>75.68000000000001</v>
+        <v>-27.91</v>
       </c>
       <c r="L76" t="n">
-        <v>77.65000000000001</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:36:51</t>
+          <t>08:50:04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.49</v>
+        <v>2.93</v>
       </c>
       <c r="F77" t="n">
-        <v>10.16</v>
+        <v>7.38</v>
       </c>
       <c r="G77" t="n">
-        <v>297.3</v>
+        <v>295.5</v>
       </c>
       <c r="H77" t="n">
-        <v>84.2</v>
+        <v>75.8</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>109.06</v>
+        <v>-70.98999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>44.9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>117.94</v>
+        <v>71.58</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:37:38</t>
+          <t>08:52:04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="F78" t="n">
-        <v>9.25</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>290.3</v>
+        <v>291.3</v>
       </c>
       <c r="H78" t="n">
-        <v>88.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-11.13</v>
+        <v>54.23</v>
       </c>
       <c r="K78" t="n">
-        <v>-124.76</v>
+        <v>36.21</v>
       </c>
       <c r="L78" t="n">
-        <v>125.25</v>
+        <v>65.20999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:39:26</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="F79" t="n">
-        <v>10.16</v>
+        <v>6.29</v>
       </c>
       <c r="G79" t="n">
-        <v>277.9</v>
+        <v>294.9</v>
       </c>
       <c r="H79" t="n">
-        <v>91.5</v>
+        <v>80.2</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>134.34</v>
+        <v>-62.35</v>
       </c>
       <c r="K79" t="n">
-        <v>-46.49</v>
+        <v>36.31</v>
       </c>
       <c r="L79" t="n">
-        <v>142.16</v>
+        <v>72.16</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:45:28</t>
+          <t>08:59:06</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="F80" t="n">
-        <v>9.82</v>
+        <v>10.7</v>
       </c>
       <c r="G80" t="n">
-        <v>306.7</v>
+        <v>282.5</v>
       </c>
       <c r="H80" t="n">
-        <v>85.40000000000001</v>
+        <v>55.9</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-120.51</v>
+        <v>-37.18</v>
       </c>
       <c r="K80" t="n">
-        <v>-102.13</v>
+        <v>87.52</v>
       </c>
       <c r="L80" t="n">
-        <v>157.97</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:47:16</t>
+          <t>09:00:17</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="F81" t="n">
         <v>10.7</v>
       </c>
       <c r="G81" t="n">
-        <v>294.3</v>
+        <v>290.4</v>
       </c>
       <c r="H81" t="n">
-        <v>91.09999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>57.42</v>
+        <v>14.54</v>
       </c>
       <c r="K81" t="n">
-        <v>138.19</v>
+        <v>-67.53</v>
       </c>
       <c r="L81" t="n">
-        <v>149.64</v>
+        <v>69.06999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:49:54</t>
+          <t>09:01:40</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="F82" t="n">
-        <v>10.7</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>290.6</v>
+        <v>278.1</v>
       </c>
       <c r="H82" t="n">
-        <v>90.90000000000001</v>
+        <v>37.3</v>
       </c>
       <c r="I82" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-85.97</v>
+        <v>46.03</v>
       </c>
       <c r="K82" t="n">
-        <v>105.09</v>
+        <v>-80.95999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>135.77</v>
+        <v>93.13</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:54:19</t>
+          <t>09:06:52</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.78</v>
+        <v>3.59</v>
       </c>
       <c r="F83" t="n">
-        <v>9.619999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G83" t="n">
-        <v>308.3</v>
+        <v>302.1</v>
       </c>
       <c r="H83" t="n">
-        <v>85</v>
+        <v>77.2</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>268.74</v>
+        <v>129.89</v>
       </c>
       <c r="K83" t="n">
-        <v>6.37</v>
+        <v>-133.59</v>
       </c>
       <c r="L83" t="n">
-        <v>268.82</v>
+        <v>186.32</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:55:45</t>
+          <t>09:08:11</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.09</v>
+        <v>2.7</v>
       </c>
       <c r="F84" t="n">
-        <v>8.050000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G84" t="n">
-        <v>295.9</v>
+        <v>300.6</v>
       </c>
       <c r="H84" t="n">
-        <v>87.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I84" t="n">
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>36.82</v>
+        <v>146.66</v>
       </c>
       <c r="K84" t="n">
-        <v>207.24</v>
+        <v>50.93</v>
       </c>
       <c r="L84" t="n">
-        <v>210.49</v>
+        <v>155.25</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:57:05</t>
+          <t>09:10:07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.83</v>
+        <v>2.21</v>
       </c>
       <c r="F85" t="n">
-        <v>9.539999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="G85" t="n">
-        <v>281.8</v>
+        <v>295.6</v>
       </c>
       <c r="H85" t="n">
-        <v>87.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-110.02</v>
+        <v>-14.44</v>
       </c>
       <c r="K85" t="n">
-        <v>192.55</v>
+        <v>-84.39</v>
       </c>
       <c r="L85" t="n">
-        <v>221.77</v>
+        <v>85.61</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:02:51</t>
+          <t>09:15:45</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.34</v>
+        <v>3.09</v>
       </c>
       <c r="F86" t="n">
-        <v>7.5</v>
+        <v>10.66</v>
       </c>
       <c r="G86" t="n">
-        <v>281.1</v>
+        <v>288.2</v>
       </c>
       <c r="H86" t="n">
-        <v>79.59999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="I86" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>46.26</v>
+        <v>-152.91</v>
       </c>
       <c r="K86" t="n">
-        <v>-31.25</v>
+        <v>-144.02</v>
       </c>
       <c r="L86" t="n">
-        <v>55.83</v>
+        <v>210.05</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:03:47</t>
+          <t>09:17:31</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="F87" t="n">
-        <v>6.53</v>
+        <v>10.7</v>
       </c>
       <c r="G87" t="n">
-        <v>295.7</v>
+        <v>284.5</v>
       </c>
       <c r="H87" t="n">
-        <v>89.09999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-140.42</v>
+        <v>-94.65000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>355.85</v>
+        <v>165.55</v>
       </c>
       <c r="L87" t="n">
-        <v>382.56</v>
+        <v>190.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:05:37</t>
+          <t>09:19:16</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="F88" t="n">
-        <v>9.07</v>
+        <v>10.7</v>
       </c>
       <c r="G88" t="n">
-        <v>303.1</v>
+        <v>289.8</v>
       </c>
       <c r="H88" t="n">
-        <v>93.90000000000001</v>
+        <v>58</v>
       </c>
       <c r="I88" t="n">
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-312.61</v>
+        <v>-107.33</v>
       </c>
       <c r="K88" t="n">
-        <v>111.9</v>
+        <v>-53.88</v>
       </c>
       <c r="L88" t="n">
-        <v>332.04</v>
+        <v>120.09</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-09.xlsx
+++ b/output/2025-08-09.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="F14" t="n">
-        <v>7.55</v>
+        <v>5.7</v>
       </c>
       <c r="G14" t="n">
-        <v>286.9</v>
+        <v>293.2</v>
       </c>
       <c r="H14" t="n">
-        <v>59</v>
+        <v>60.1</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.27</v>
+        <v>4.71</v>
       </c>
       <c r="K14" t="n">
-        <v>-28.65</v>
+        <v>12.84</v>
       </c>
       <c r="L14" t="n">
-        <v>31.17</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:37:22</t>
+          <t>05:36:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="F15" t="n">
-        <v>6.96</v>
+        <v>7.67</v>
       </c>
       <c r="G15" t="n">
-        <v>316.8</v>
+        <v>303.4</v>
       </c>
       <c r="H15" t="n">
-        <v>63.1</v>
+        <v>36.3</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.73</v>
+        <v>-20.59</v>
       </c>
       <c r="K15" t="n">
-        <v>32.67</v>
+        <v>37.33</v>
       </c>
       <c r="L15" t="n">
-        <v>34.72</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:38:43</t>
+          <t>05:36:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.28</v>
+        <v>1.71</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>6.13</v>
       </c>
       <c r="G16" t="n">
-        <v>275.7</v>
+        <v>297.2</v>
       </c>
       <c r="H16" t="n">
-        <v>43.9</v>
+        <v>82</v>
       </c>
       <c r="I16" t="n">
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>40.91</v>
+        <v>-22.6</v>
       </c>
       <c r="K16" t="n">
-        <v>25.71</v>
+        <v>-12.43</v>
       </c>
       <c r="L16" t="n">
-        <v>48.32</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:43:06</t>
+          <t>05:42:05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="F17" t="n">
-        <v>7.27</v>
+        <v>7.53</v>
       </c>
       <c r="G17" t="n">
-        <v>280.9</v>
+        <v>288.9</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-52.7</v>
+        <v>28.5</v>
       </c>
       <c r="K17" t="n">
-        <v>-13.71</v>
+        <v>-42.41</v>
       </c>
       <c r="L17" t="n">
-        <v>54.45</v>
+        <v>51.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:44:34</t>
+          <t>05:43:42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="F18" t="n">
-        <v>7.1</v>
+        <v>7.46</v>
       </c>
       <c r="G18" t="n">
-        <v>292.1</v>
+        <v>295.3</v>
       </c>
       <c r="H18" t="n">
-        <v>46.2</v>
+        <v>60.3</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-32.88</v>
+        <v>49.87</v>
       </c>
       <c r="K18" t="n">
-        <v>72.97</v>
+        <v>24.08</v>
       </c>
       <c r="L18" t="n">
-        <v>80.04000000000001</v>
+        <v>55.38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:45:20</t>
+          <t>05:45:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="F19" t="n">
-        <v>7.94</v>
+        <v>2.15</v>
       </c>
       <c r="G19" t="n">
-        <v>291.2</v>
+        <v>317.4</v>
       </c>
       <c r="H19" t="n">
-        <v>55.8</v>
+        <v>67.2</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-34.39</v>
+        <v>22.8</v>
       </c>
       <c r="K19" t="n">
-        <v>73.43000000000001</v>
+        <v>-44.24</v>
       </c>
       <c r="L19" t="n">
-        <v>81.08</v>
+        <v>49.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:49:09</t>
+          <t>05:49:34</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.84</v>
+        <v>2.95</v>
       </c>
       <c r="F20" t="n">
-        <v>3.95</v>
+        <v>5.63</v>
       </c>
       <c r="G20" t="n">
-        <v>288.3</v>
+        <v>287.4</v>
       </c>
       <c r="H20" t="n">
-        <v>33.9</v>
+        <v>64.8</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>-10.88</v>
+        <v>-43.04</v>
       </c>
       <c r="K20" t="n">
-        <v>-60.29</v>
+        <v>-97.93000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>61.26</v>
+        <v>106.97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:50:48</t>
+          <t>05:51:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.82</v>
+        <v>3.02</v>
       </c>
       <c r="F21" t="n">
-        <v>7.61</v>
+        <v>10.7</v>
       </c>
       <c r="G21" t="n">
-        <v>269</v>
+        <v>290.3</v>
       </c>
       <c r="H21" t="n">
-        <v>67.2</v>
+        <v>73.7</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.7</v>
+        <v>-28.25</v>
       </c>
       <c r="K21" t="n">
-        <v>97.78</v>
+        <v>80.55</v>
       </c>
       <c r="L21" t="n">
-        <v>97.84999999999999</v>
+        <v>85.36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:52:38</t>
+          <t>05:52:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="F22" t="n">
-        <v>10.31</v>
+        <v>8.49</v>
       </c>
       <c r="G22" t="n">
-        <v>287.3</v>
+        <v>279.3</v>
       </c>
       <c r="H22" t="n">
-        <v>15.8</v>
+        <v>59.7</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J22" t="n">
-        <v>-73.95</v>
+        <v>14.74</v>
       </c>
       <c r="K22" t="n">
-        <v>75.5</v>
+        <v>64.98</v>
       </c>
       <c r="L22" t="n">
-        <v>105.69</v>
+        <v>66.63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:58:26</t>
+          <t>05:55:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="F23" t="n">
-        <v>6.56</v>
+        <v>8.01</v>
       </c>
       <c r="G23" t="n">
-        <v>284.9</v>
+        <v>295.4</v>
       </c>
       <c r="H23" t="n">
-        <v>51.3</v>
+        <v>79.8</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-103.93</v>
+        <v>48.34</v>
       </c>
       <c r="K23" t="n">
-        <v>-48.62</v>
+        <v>-136.28</v>
       </c>
       <c r="L23" t="n">
-        <v>114.74</v>
+        <v>144.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:00:23</t>
+          <t>05:57:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.33</v>
+        <v>2.61</v>
       </c>
       <c r="F24" t="n">
-        <v>8.76</v>
+        <v>4.78</v>
       </c>
       <c r="G24" t="n">
-        <v>282</v>
+        <v>291.5</v>
       </c>
       <c r="H24" t="n">
-        <v>49.1</v>
+        <v>47.3</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>36.94</v>
+        <v>4.85</v>
       </c>
       <c r="K24" t="n">
-        <v>-108.77</v>
+        <v>157.69</v>
       </c>
       <c r="L24" t="n">
-        <v>114.87</v>
+        <v>157.76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:01:58</t>
+          <t>05:59:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.99</v>
+        <v>2.74</v>
       </c>
       <c r="F25" t="n">
-        <v>6.96</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>284.6</v>
+        <v>282</v>
       </c>
       <c r="H25" t="n">
-        <v>60.7</v>
+        <v>46</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-16.29</v>
+        <v>-99.23999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.28</v>
+        <v>-98.44</v>
       </c>
       <c r="L25" t="n">
-        <v>16.29</v>
+        <v>139.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:06:23</t>
+          <t>06:03:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="F26" t="n">
-        <v>7.87</v>
+        <v>2.57</v>
       </c>
       <c r="G26" t="n">
-        <v>293.1</v>
+        <v>290.5</v>
       </c>
       <c r="H26" t="n">
-        <v>54.1</v>
+        <v>82.8</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-112.19</v>
+        <v>136.58</v>
       </c>
       <c r="K26" t="n">
-        <v>143.2</v>
+        <v>-130.79</v>
       </c>
       <c r="L26" t="n">
-        <v>181.92</v>
+        <v>189.11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:08:15</t>
+          <t>06:04:38</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.02</v>
+        <v>2.66</v>
       </c>
       <c r="F27" t="n">
-        <v>8.69</v>
+        <v>7.28</v>
       </c>
       <c r="G27" t="n">
-        <v>289.3</v>
+        <v>286.9</v>
       </c>
       <c r="H27" t="n">
-        <v>60.5</v>
+        <v>27.8</v>
       </c>
       <c r="I27" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>164.98</v>
+        <v>-65.01000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>90.93000000000001</v>
+        <v>174.45</v>
       </c>
       <c r="L27" t="n">
-        <v>188.38</v>
+        <v>186.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:09:03</t>
+          <t>06:06:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="F28" t="n">
-        <v>5.85</v>
+        <v>6.49</v>
       </c>
       <c r="G28" t="n">
-        <v>302.8</v>
+        <v>295.9</v>
       </c>
       <c r="H28" t="n">
-        <v>87</v>
+        <v>11.3</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J28" t="n">
-        <v>-99.77</v>
+        <v>127.98</v>
       </c>
       <c r="K28" t="n">
-        <v>-112.06</v>
+        <v>58.3</v>
       </c>
       <c r="L28" t="n">
-        <v>150.04</v>
+        <v>140.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:19:52</t>
+          <t>06:14:51</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.46</v>
+        <v>2.14</v>
       </c>
       <c r="F29" t="n">
-        <v>10.7</v>
+        <v>9.01</v>
       </c>
       <c r="G29" t="n">
-        <v>287.8</v>
+        <v>285</v>
       </c>
       <c r="H29" t="n">
-        <v>47.1</v>
+        <v>55</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-34.76</v>
+        <v>-41.72</v>
       </c>
       <c r="K29" t="n">
-        <v>9.17</v>
+        <v>-13.61</v>
       </c>
       <c r="L29" t="n">
-        <v>35.95</v>
+        <v>43.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:21:10</t>
+          <t>06:16:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.61</v>
+        <v>2.22</v>
       </c>
       <c r="F30" t="n">
-        <v>10.7</v>
+        <v>7.2</v>
       </c>
       <c r="G30" t="n">
-        <v>300.3</v>
+        <v>290.7</v>
       </c>
       <c r="H30" t="n">
-        <v>36.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>2.64</v>
+        <v>-34</v>
       </c>
       <c r="K30" t="n">
-        <v>38.13</v>
+        <v>7.16</v>
       </c>
       <c r="L30" t="n">
-        <v>38.22</v>
+        <v>34.74</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:22:45</t>
+          <t>06:17:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="F31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="G31" t="n">
-        <v>266.7</v>
+        <v>288.6</v>
       </c>
       <c r="H31" t="n">
-        <v>70.8</v>
+        <v>38.5</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-26.76</v>
+        <v>-22.03</v>
       </c>
       <c r="K31" t="n">
-        <v>19.85</v>
+        <v>-24.17</v>
       </c>
       <c r="L31" t="n">
-        <v>33.32</v>
+        <v>32.71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:27:52</t>
+          <t>06:22:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.51</v>
+        <v>1.63</v>
       </c>
       <c r="F32" t="n">
-        <v>10.7</v>
+        <v>2.32</v>
       </c>
       <c r="G32" t="n">
-        <v>279.7</v>
+        <v>278.8</v>
       </c>
       <c r="H32" t="n">
-        <v>33.4</v>
+        <v>51.8</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-39.77</v>
+        <v>-1.38</v>
       </c>
       <c r="K32" t="n">
-        <v>54.11</v>
+        <v>58.2</v>
       </c>
       <c r="L32" t="n">
-        <v>67.15000000000001</v>
+        <v>58.22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:30:01</t>
+          <t>06:25:26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.11</v>
+        <v>2.57</v>
       </c>
       <c r="F33" t="n">
-        <v>10.63</v>
+        <v>7.33</v>
       </c>
       <c r="G33" t="n">
-        <v>291.3</v>
+        <v>287.9</v>
       </c>
       <c r="H33" t="n">
-        <v>66</v>
+        <v>24.7</v>
       </c>
       <c r="I33" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>24.11</v>
+        <v>-62.96</v>
       </c>
       <c r="K33" t="n">
-        <v>47.26</v>
+        <v>-44.13</v>
       </c>
       <c r="L33" t="n">
-        <v>53.05</v>
+        <v>76.89</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:32:39</t>
+          <t>06:27:08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.16</v>
+        <v>1.61</v>
       </c>
       <c r="F34" t="n">
-        <v>6.13</v>
+        <v>7.29</v>
       </c>
       <c r="G34" t="n">
-        <v>287.3</v>
+        <v>285.8</v>
       </c>
       <c r="H34" t="n">
-        <v>65.59999999999999</v>
+        <v>39.2</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-71.58</v>
+        <v>8.01</v>
       </c>
       <c r="K34" t="n">
-        <v>-13.15</v>
+        <v>43.18</v>
       </c>
       <c r="L34" t="n">
-        <v>72.78</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:37:32</t>
+          <t>06:30:07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="F35" t="n">
-        <v>8.789999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G35" t="n">
-        <v>299.5</v>
+        <v>291.3</v>
       </c>
       <c r="H35" t="n">
-        <v>62.5</v>
+        <v>57.1</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-106.41</v>
+        <v>27.8</v>
       </c>
       <c r="K35" t="n">
-        <v>24.69</v>
+        <v>-67.61</v>
       </c>
       <c r="L35" t="n">
-        <v>109.24</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:40:15</t>
+          <t>06:32:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="F36" t="n">
-        <v>9.789999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>268.8</v>
+        <v>287.4</v>
       </c>
       <c r="H36" t="n">
-        <v>77.7</v>
+        <v>60.5</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>83.2</v>
+        <v>-0.23</v>
       </c>
       <c r="K36" t="n">
-        <v>-57.41</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>101.08</v>
+        <v>87.70999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:41:32</t>
+          <t>06:33:31</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="F37" t="n">
-        <v>7.77</v>
+        <v>8.43</v>
       </c>
       <c r="G37" t="n">
-        <v>290.6</v>
+        <v>295.7</v>
       </c>
       <c r="H37" t="n">
-        <v>75</v>
+        <v>37.9</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>-64.05</v>
+        <v>73.05</v>
       </c>
       <c r="K37" t="n">
-        <v>5.24</v>
+        <v>70.05</v>
       </c>
       <c r="L37" t="n">
-        <v>64.26000000000001</v>
+        <v>101.21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:46:24</t>
+          <t>06:37:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="F38" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="G38" t="n">
-        <v>294.1</v>
+        <v>281</v>
       </c>
       <c r="H38" t="n">
-        <v>70.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>98.73</v>
+        <v>-206.53</v>
       </c>
       <c r="K38" t="n">
-        <v>89</v>
+        <v>-50.94</v>
       </c>
       <c r="L38" t="n">
-        <v>132.93</v>
+        <v>212.72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:47:51</t>
+          <t>06:39:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="F39" t="n">
-        <v>9.640000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>294.1</v>
+        <v>280.5</v>
       </c>
       <c r="H39" t="n">
-        <v>54.1</v>
+        <v>33.1</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-72.29000000000001</v>
+        <v>-175.06</v>
       </c>
       <c r="K39" t="n">
-        <v>-93.40000000000001</v>
+        <v>-57.46</v>
       </c>
       <c r="L39" t="n">
-        <v>118.11</v>
+        <v>184.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:49:28</t>
+          <t>06:40:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.12</v>
+        <v>2.72</v>
       </c>
       <c r="F40" t="n">
-        <v>9.69</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>274.6</v>
+        <v>288.1</v>
       </c>
       <c r="H40" t="n">
-        <v>68.09999999999999</v>
+        <v>45.1</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>-55.65</v>
+        <v>77.67</v>
       </c>
       <c r="K40" t="n">
-        <v>-212.5</v>
+        <v>40.6</v>
       </c>
       <c r="L40" t="n">
-        <v>219.67</v>
+        <v>87.64</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:54:41</t>
+          <t>06:45:22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>9.82</v>
+        <v>4.55</v>
       </c>
       <c r="G41" t="n">
-        <v>287.8</v>
+        <v>283</v>
       </c>
       <c r="H41" t="n">
-        <v>70.3</v>
+        <v>75.2</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>-198.4</v>
+        <v>-75.63</v>
       </c>
       <c r="K41" t="n">
-        <v>-22.92</v>
+        <v>162.42</v>
       </c>
       <c r="L41" t="n">
-        <v>199.72</v>
+        <v>179.17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:56:41</t>
+          <t>06:46:54</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="F42" t="n">
-        <v>10.7</v>
+        <v>7.39</v>
       </c>
       <c r="G42" t="n">
-        <v>300.6</v>
+        <v>280.5</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>-13.71</v>
+        <v>12.86</v>
       </c>
       <c r="K42" t="n">
-        <v>190.51</v>
+        <v>173.67</v>
       </c>
       <c r="L42" t="n">
-        <v>191</v>
+        <v>174.14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:57:52</t>
+          <t>06:48:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="F43" t="n">
-        <v>10.7</v>
+        <v>9.85</v>
       </c>
       <c r="G43" t="n">
-        <v>292.5</v>
+        <v>279.5</v>
       </c>
       <c r="H43" t="n">
-        <v>55.8</v>
+        <v>21.8</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.05</v>
+        <v>-27.23</v>
       </c>
       <c r="K43" t="n">
-        <v>200.05</v>
+        <v>181.84</v>
       </c>
       <c r="L43" t="n">
-        <v>200.06</v>
+        <v>183.87</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:09:00</t>
+          <t>06:56:51</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.39</v>
+        <v>2.76</v>
       </c>
       <c r="F44" t="n">
-        <v>10.7</v>
+        <v>10.69</v>
       </c>
       <c r="G44" t="n">
-        <v>291.3</v>
+        <v>280.9</v>
       </c>
       <c r="H44" t="n">
-        <v>82.5</v>
+        <v>51.1</v>
       </c>
       <c r="I44" t="n">
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-23.98</v>
+        <v>35.39</v>
       </c>
       <c r="K44" t="n">
-        <v>21.35</v>
+        <v>-33.37</v>
       </c>
       <c r="L44" t="n">
-        <v>32.11</v>
+        <v>48.64</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:10:36</t>
+          <t>06:58:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="F45" t="n">
-        <v>10.7</v>
+        <v>8.26</v>
       </c>
       <c r="G45" t="n">
-        <v>281.5</v>
+        <v>282.6</v>
       </c>
       <c r="H45" t="n">
-        <v>77.09999999999999</v>
+        <v>45.5</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-19.18</v>
+        <v>-5.89</v>
       </c>
       <c r="K45" t="n">
-        <v>36.66</v>
+        <v>-14.44</v>
       </c>
       <c r="L45" t="n">
-        <v>41.37</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:12:29</t>
+          <t>07:00:03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.32</v>
+        <v>2.71</v>
       </c>
       <c r="F46" t="n">
-        <v>8.09</v>
+        <v>8.52</v>
       </c>
       <c r="G46" t="n">
-        <v>288.5</v>
+        <v>298.4</v>
       </c>
       <c r="H46" t="n">
-        <v>85.7</v>
+        <v>38.2</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-25.13</v>
+        <v>42.33</v>
       </c>
       <c r="K46" t="n">
-        <v>-13.67</v>
+        <v>-8.9</v>
       </c>
       <c r="L46" t="n">
-        <v>28.61</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:18:15</t>
+          <t>07:04:13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.37</v>
+        <v>2.64</v>
       </c>
       <c r="F47" t="n">
-        <v>7.36</v>
+        <v>10.7</v>
       </c>
       <c r="G47" t="n">
-        <v>291.7</v>
+        <v>288.8</v>
       </c>
       <c r="H47" t="n">
-        <v>75.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I47" t="n">
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>64.31999999999999</v>
+        <v>34.43</v>
       </c>
       <c r="K47" t="n">
-        <v>19.25</v>
+        <v>-2.32</v>
       </c>
       <c r="L47" t="n">
-        <v>67.14</v>
+        <v>34.51</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:20:48</t>
+          <t>07:06:34</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.04</v>
+        <v>2.68</v>
       </c>
       <c r="F48" t="n">
-        <v>7.98</v>
+        <v>7.8</v>
       </c>
       <c r="G48" t="n">
-        <v>289.9</v>
+        <v>293.7</v>
       </c>
       <c r="H48" t="n">
-        <v>68.09999999999999</v>
+        <v>22.2</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>77.67</v>
+        <v>-13.62</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.72</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>77.70999999999999</v>
+        <v>76.45999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:22:31</t>
+          <t>07:08:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.41</v>
+        <v>2.87</v>
       </c>
       <c r="F49" t="n">
-        <v>10.7</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>290.6</v>
+        <v>309.1</v>
       </c>
       <c r="H49" t="n">
-        <v>73.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>11.19</v>
+        <v>-21.37</v>
       </c>
       <c r="K49" t="n">
-        <v>-59.5</v>
+        <v>-62.96</v>
       </c>
       <c r="L49" t="n">
-        <v>60.54</v>
+        <v>66.48</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:27:50</t>
+          <t>07:13:33</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="F50" t="n">
-        <v>7.57</v>
+        <v>8.17</v>
       </c>
       <c r="G50" t="n">
-        <v>286</v>
+        <v>285.3</v>
       </c>
       <c r="H50" t="n">
-        <v>31.2</v>
+        <v>51.5</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>77.33</v>
+        <v>23.01</v>
       </c>
       <c r="K50" t="n">
-        <v>-16.27</v>
+        <v>-24.15</v>
       </c>
       <c r="L50" t="n">
-        <v>79.02</v>
+        <v>33.36</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:29:05</t>
+          <t>07:15:01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.47</v>
+        <v>2.96</v>
       </c>
       <c r="F51" t="n">
-        <v>6.02</v>
+        <v>10.24</v>
       </c>
       <c r="G51" t="n">
-        <v>281.1</v>
+        <v>289.8</v>
       </c>
       <c r="H51" t="n">
-        <v>63.3</v>
+        <v>21.2</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>-37.54</v>
+        <v>57.75</v>
       </c>
       <c r="K51" t="n">
-        <v>-56.98</v>
+        <v>-82.19</v>
       </c>
       <c r="L51" t="n">
-        <v>68.23999999999999</v>
+        <v>100.45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:30:58</t>
+          <t>07:16:01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.09</v>
+        <v>2.54</v>
       </c>
       <c r="F52" t="n">
-        <v>4.31</v>
+        <v>5.48</v>
       </c>
       <c r="G52" t="n">
-        <v>318.8</v>
+        <v>282.4</v>
       </c>
       <c r="H52" t="n">
-        <v>37.5</v>
+        <v>51</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J52" t="n">
-        <v>-9.550000000000001</v>
+        <v>-44.17</v>
       </c>
       <c r="K52" t="n">
-        <v>140.86</v>
+        <v>101.86</v>
       </c>
       <c r="L52" t="n">
-        <v>141.18</v>
+        <v>111.02</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:36:19</t>
+          <t>07:21:19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="F53" t="n">
-        <v>10.49</v>
+        <v>10.7</v>
       </c>
       <c r="G53" t="n">
-        <v>294.7</v>
+        <v>285.5</v>
       </c>
       <c r="H53" t="n">
-        <v>48.8</v>
+        <v>42.2</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>-17.2</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>133.24</v>
+        <v>128.88</v>
       </c>
       <c r="L53" t="n">
-        <v>134.34</v>
+        <v>146.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:38:16</t>
+          <t>07:22:50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="F54" t="n">
-        <v>10.7</v>
+        <v>9.25</v>
       </c>
       <c r="G54" t="n">
-        <v>293.2</v>
+        <v>301.2</v>
       </c>
       <c r="H54" t="n">
-        <v>28</v>
+        <v>42.1</v>
       </c>
       <c r="I54" t="n">
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-155.42</v>
+        <v>-127.61</v>
       </c>
       <c r="K54" t="n">
-        <v>39.23</v>
+        <v>-62.97</v>
       </c>
       <c r="L54" t="n">
-        <v>160.3</v>
+        <v>142.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:40:48</t>
+          <t>07:25:18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.69</v>
+        <v>2.21</v>
       </c>
       <c r="F55" t="n">
-        <v>7.89</v>
+        <v>7.73</v>
       </c>
       <c r="G55" t="n">
-        <v>279.7</v>
+        <v>290.8</v>
       </c>
       <c r="H55" t="n">
-        <v>70.7</v>
+        <v>47.4</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>144.7</v>
+        <v>-99.59999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>18.63</v>
+        <v>-35.05</v>
       </c>
       <c r="L55" t="n">
-        <v>145.89</v>
+        <v>105.59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:45:25</t>
+          <t>07:30:14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.51</v>
+        <v>2.78</v>
       </c>
       <c r="F56" t="n">
-        <v>9.48</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>296.8</v>
+        <v>293.9</v>
       </c>
       <c r="H56" t="n">
-        <v>79.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-210.11</v>
+        <v>27.46</v>
       </c>
       <c r="K56" t="n">
-        <v>14.45</v>
+        <v>197.13</v>
       </c>
       <c r="L56" t="n">
-        <v>210.6</v>
+        <v>199.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:46:07</t>
+          <t>07:30:54</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.03</v>
+        <v>2.4</v>
       </c>
       <c r="F57" t="n">
-        <v>10.7</v>
+        <v>5.89</v>
       </c>
       <c r="G57" t="n">
-        <v>296.6</v>
+        <v>302.1</v>
       </c>
       <c r="H57" t="n">
-        <v>62.8</v>
+        <v>61.5</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>-113.5</v>
+        <v>-196.82</v>
       </c>
       <c r="K57" t="n">
-        <v>120.3</v>
+        <v>105.11</v>
       </c>
       <c r="L57" t="n">
-        <v>165.39</v>
+        <v>223.13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:47:55</t>
+          <t>07:33:02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.89</v>
+        <v>2.61</v>
       </c>
       <c r="F58" t="n">
-        <v>10.7</v>
+        <v>9.09</v>
       </c>
       <c r="G58" t="n">
-        <v>320.6</v>
+        <v>293.1</v>
       </c>
       <c r="H58" t="n">
-        <v>76.8</v>
+        <v>54.1</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>-111.69</v>
+        <v>-110.65</v>
       </c>
       <c r="K58" t="n">
-        <v>225.61</v>
+        <v>173.2</v>
       </c>
       <c r="L58" t="n">
-        <v>251.75</v>
+        <v>205.52</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:57:45</t>
+          <t>07:42:27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.54</v>
+        <v>3.25</v>
       </c>
       <c r="F59" t="n">
-        <v>8.94</v>
+        <v>10.16</v>
       </c>
       <c r="G59" t="n">
-        <v>289.9</v>
+        <v>289.3</v>
       </c>
       <c r="H59" t="n">
-        <v>50.2</v>
+        <v>60.5</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J59" t="n">
-        <v>34.08</v>
+        <v>49.58</v>
       </c>
       <c r="K59" t="n">
-        <v>17.71</v>
+        <v>18.2</v>
       </c>
       <c r="L59" t="n">
-        <v>38.41</v>
+        <v>52.82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:59:15</t>
+          <t>07:44:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="F60" t="n">
-        <v>8.970000000000001</v>
+        <v>7.14</v>
       </c>
       <c r="G60" t="n">
-        <v>284.7</v>
+        <v>302.8</v>
       </c>
       <c r="H60" t="n">
-        <v>79.2</v>
+        <v>87</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J60" t="n">
-        <v>14.29</v>
+        <v>-18.66</v>
       </c>
       <c r="K60" t="n">
-        <v>28.7</v>
+        <v>-29.53</v>
       </c>
       <c r="L60" t="n">
-        <v>32.06</v>
+        <v>34.94</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:00:08</t>
+          <t>07:46:16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.33</v>
+        <v>2.66</v>
       </c>
       <c r="F61" t="n">
         <v>10.7</v>
       </c>
       <c r="G61" t="n">
-        <v>304.1</v>
+        <v>287.8</v>
       </c>
       <c r="H61" t="n">
-        <v>80.2</v>
+        <v>47.1</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-44.11</v>
+        <v>-37.66</v>
       </c>
       <c r="K61" t="n">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="L61" t="n">
-        <v>44.81</v>
+        <v>38.84</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:04:20</t>
+          <t>07:51:01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="F62" t="n">
         <v>10.7</v>
       </c>
       <c r="G62" t="n">
-        <v>291</v>
+        <v>300.3</v>
       </c>
       <c r="H62" t="n">
-        <v>53.1</v>
+        <v>36.2</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J62" t="n">
-        <v>51.74</v>
+        <v>15.46</v>
       </c>
       <c r="K62" t="n">
-        <v>-9.34</v>
+        <v>58.37</v>
       </c>
       <c r="L62" t="n">
-        <v>52.58</v>
+        <v>60.38</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:06:39</t>
+          <t>07:53:29</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.67</v>
+        <v>2.93</v>
       </c>
       <c r="F63" t="n">
-        <v>8.17</v>
+        <v>10.11</v>
       </c>
       <c r="G63" t="n">
-        <v>283.8</v>
+        <v>266.7</v>
       </c>
       <c r="H63" t="n">
-        <v>66.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-62.54</v>
+        <v>-30.91</v>
       </c>
       <c r="K63" t="n">
-        <v>38.19</v>
+        <v>33.93</v>
       </c>
       <c r="L63" t="n">
-        <v>73.27</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:08:19</t>
+          <t>07:53:58</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="F64" t="n">
         <v>10.7</v>
       </c>
       <c r="G64" t="n">
-        <v>291.6</v>
+        <v>279.7</v>
       </c>
       <c r="H64" t="n">
-        <v>62.3</v>
+        <v>33.4</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>2.48</v>
+        <v>-33.75</v>
       </c>
       <c r="K64" t="n">
-        <v>-66.59999999999999</v>
+        <v>63.02</v>
       </c>
       <c r="L64" t="n">
-        <v>66.65000000000001</v>
+        <v>71.48999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:12:16</t>
+          <t>07:58:30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.46</v>
+        <v>2.31</v>
       </c>
       <c r="F65" t="n">
-        <v>10.13</v>
+        <v>10.7</v>
       </c>
       <c r="G65" t="n">
-        <v>300.5</v>
+        <v>291.3</v>
       </c>
       <c r="H65" t="n">
-        <v>62.1</v>
+        <v>66</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-88.64</v>
+        <v>49.31</v>
       </c>
       <c r="K65" t="n">
-        <v>-54.77</v>
+        <v>67.09</v>
       </c>
       <c r="L65" t="n">
-        <v>104.2</v>
+        <v>83.27</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:13:34</t>
+          <t>08:00:56</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="F66" t="n">
-        <v>5.55</v>
+        <v>7.28</v>
       </c>
       <c r="G66" t="n">
-        <v>292.8</v>
+        <v>287.3</v>
       </c>
       <c r="H66" t="n">
-        <v>87.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-81.59</v>
+        <v>-109.82</v>
       </c>
       <c r="K66" t="n">
-        <v>-7.73</v>
+        <v>-29.93</v>
       </c>
       <c r="L66" t="n">
-        <v>81.95999999999999</v>
+        <v>113.83</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:15:29</t>
+          <t>08:02:17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="F67" t="n">
-        <v>10.7</v>
+        <v>10.04</v>
       </c>
       <c r="G67" t="n">
-        <v>286</v>
+        <v>299.5</v>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-134.81</v>
+        <v>-111.47</v>
       </c>
       <c r="K67" t="n">
-        <v>11.83</v>
+        <v>17.73</v>
       </c>
       <c r="L67" t="n">
-        <v>135.33</v>
+        <v>112.87</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:20:21</t>
+          <t>08:06:55</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.32</v>
+        <v>2.72</v>
       </c>
       <c r="F68" t="n">
         <v>10.7</v>
       </c>
       <c r="G68" t="n">
-        <v>288.8</v>
+        <v>268.8</v>
       </c>
       <c r="H68" t="n">
-        <v>38.5</v>
+        <v>77.7</v>
       </c>
       <c r="I68" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-99.31</v>
+        <v>143.67</v>
       </c>
       <c r="K68" t="n">
-        <v>-158</v>
+        <v>-78.39</v>
       </c>
       <c r="L68" t="n">
-        <v>186.62</v>
+        <v>163.66</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:22:43</t>
+          <t>08:08:11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="F69" t="n">
-        <v>10.7</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>290.5</v>
+        <v>290.6</v>
       </c>
       <c r="H69" t="n">
-        <v>91.3</v>
+        <v>75</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-108.72</v>
+        <v>-105.79</v>
       </c>
       <c r="K69" t="n">
-        <v>59.11</v>
+        <v>2.26</v>
       </c>
       <c r="L69" t="n">
-        <v>123.75</v>
+        <v>105.81</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:24:04</t>
+          <t>08:10:02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="F70" t="n">
-        <v>10.56</v>
+        <v>10.62</v>
       </c>
       <c r="G70" t="n">
-        <v>303</v>
+        <v>294.1</v>
       </c>
       <c r="H70" t="n">
-        <v>38.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.45</v>
+        <v>127.98</v>
       </c>
       <c r="K70" t="n">
-        <v>136.03</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>136.23</v>
+        <v>151.07</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:29:06</t>
+          <t>08:13:01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="F71" t="n">
         <v>10.7</v>
       </c>
       <c r="G71" t="n">
-        <v>290.2</v>
+        <v>294.1</v>
       </c>
       <c r="H71" t="n">
-        <v>94.2</v>
+        <v>54.1</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J71" t="n">
-        <v>158.91</v>
+        <v>-78.06999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>109.21</v>
+        <v>-152.73</v>
       </c>
       <c r="L71" t="n">
-        <v>192.82</v>
+        <v>171.53</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:30:33</t>
+          <t>08:15:13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.98</v>
+        <v>2.31</v>
       </c>
       <c r="F72" t="n">
         <v>10.7</v>
       </c>
       <c r="G72" t="n">
-        <v>278.2</v>
+        <v>274.6</v>
       </c>
       <c r="H72" t="n">
-        <v>70</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>223.83</v>
+        <v>-54.38</v>
       </c>
       <c r="K72" t="n">
-        <v>34.95</v>
+        <v>-310.66</v>
       </c>
       <c r="L72" t="n">
-        <v>226.55</v>
+        <v>315.38</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:31:48</t>
+          <t>08:16:31</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="F73" t="n">
-        <v>8.4</v>
+        <v>10.7</v>
       </c>
       <c r="G73" t="n">
-        <v>284.4</v>
+        <v>287.8</v>
       </c>
       <c r="H73" t="n">
-        <v>45.4</v>
+        <v>70.3</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-177.58</v>
+        <v>-213.79</v>
       </c>
       <c r="K73" t="n">
-        <v>4.95</v>
+        <v>-43.15</v>
       </c>
       <c r="L73" t="n">
-        <v>177.64</v>
+        <v>218.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:41:44</t>
+          <t>08:23:40</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.61</v>
+        <v>2.94</v>
       </c>
       <c r="F74" t="n">
         <v>10.7</v>
       </c>
       <c r="G74" t="n">
-        <v>292.8</v>
+        <v>300.6</v>
       </c>
       <c r="H74" t="n">
-        <v>92.2</v>
+        <v>100</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-31.05</v>
+        <v>5.33</v>
       </c>
       <c r="K74" t="n">
-        <v>24.74</v>
+        <v>49.23</v>
       </c>
       <c r="L74" t="n">
-        <v>39.7</v>
+        <v>49.52</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:43:16</t>
+          <t>08:24:26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="F75" t="n">
-        <v>7.57</v>
+        <v>10.7</v>
       </c>
       <c r="G75" t="n">
         <v>292.5</v>
       </c>
       <c r="H75" t="n">
-        <v>64.5</v>
+        <v>55.8</v>
       </c>
       <c r="I75" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>43.03</v>
+        <v>9.6</v>
       </c>
       <c r="K75" t="n">
-        <v>2.91</v>
+        <v>50.78</v>
       </c>
       <c r="L75" t="n">
-        <v>43.13</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:45:14</t>
+          <t>08:26:58</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.96</v>
+        <v>2.56</v>
       </c>
       <c r="F76" t="n">
-        <v>9.23</v>
+        <v>10.7</v>
       </c>
       <c r="G76" t="n">
-        <v>294.5</v>
+        <v>291.3</v>
       </c>
       <c r="H76" t="n">
-        <v>95.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-43.09</v>
+        <v>-24.1</v>
       </c>
       <c r="K76" t="n">
-        <v>-27.91</v>
+        <v>24.7</v>
       </c>
       <c r="L76" t="n">
-        <v>51.34</v>
+        <v>34.51</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:50:04</t>
+          <t>08:31:04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.93</v>
+        <v>2.76</v>
       </c>
       <c r="F77" t="n">
-        <v>7.38</v>
+        <v>10.7</v>
       </c>
       <c r="G77" t="n">
-        <v>295.5</v>
+        <v>281.5</v>
       </c>
       <c r="H77" t="n">
-        <v>75.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J77" t="n">
-        <v>-70.98999999999999</v>
+        <v>-22.65</v>
       </c>
       <c r="K77" t="n">
-        <v>9.140000000000001</v>
+        <v>68.67</v>
       </c>
       <c r="L77" t="n">
-        <v>71.58</v>
+        <v>72.31</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:52:04</t>
+          <t>08:31:50</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="F78" t="n">
-        <v>9.119999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="G78" t="n">
-        <v>291.3</v>
+        <v>288.5</v>
       </c>
       <c r="H78" t="n">
-        <v>69.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>54.23</v>
+        <v>-40.38</v>
       </c>
       <c r="K78" t="n">
-        <v>36.21</v>
+        <v>-29.99</v>
       </c>
       <c r="L78" t="n">
-        <v>65.20999999999999</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>08:34:12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="F79" t="n">
-        <v>6.29</v>
+        <v>8.35</v>
       </c>
       <c r="G79" t="n">
-        <v>294.9</v>
+        <v>291.7</v>
       </c>
       <c r="H79" t="n">
-        <v>80.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J79" t="n">
-        <v>-62.35</v>
+        <v>71.36</v>
       </c>
       <c r="K79" t="n">
-        <v>36.31</v>
+        <v>13.32</v>
       </c>
       <c r="L79" t="n">
-        <v>72.16</v>
+        <v>72.59</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:59:06</t>
+          <t>08:38:52</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.72</v>
+        <v>3.21</v>
       </c>
       <c r="F80" t="n">
-        <v>10.7</v>
+        <v>9.08</v>
       </c>
       <c r="G80" t="n">
-        <v>282.5</v>
+        <v>289.9</v>
       </c>
       <c r="H80" t="n">
-        <v>55.9</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-37.18</v>
+        <v>114.73</v>
       </c>
       <c r="K80" t="n">
-        <v>87.52</v>
+        <v>-11.18</v>
       </c>
       <c r="L80" t="n">
-        <v>95.09999999999999</v>
+        <v>115.28</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:00:17</t>
+          <t>08:40:23</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="F81" t="n">
         <v>10.7</v>
       </c>
       <c r="G81" t="n">
-        <v>290.4</v>
+        <v>290.6</v>
       </c>
       <c r="H81" t="n">
-        <v>73.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>14.54</v>
+        <v>31.76</v>
       </c>
       <c r="K81" t="n">
-        <v>-67.53</v>
+        <v>-90.34</v>
       </c>
       <c r="L81" t="n">
-        <v>69.06999999999999</v>
+        <v>95.76000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:01:40</t>
+          <t>08:42:50</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.92</v>
+        <v>2.23</v>
       </c>
       <c r="F82" t="n">
-        <v>9.630000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="G82" t="n">
-        <v>278.1</v>
+        <v>286</v>
       </c>
       <c r="H82" t="n">
-        <v>37.3</v>
+        <v>31.2</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>46.03</v>
+        <v>82.08</v>
       </c>
       <c r="K82" t="n">
-        <v>-80.95999999999999</v>
+        <v>-18.21</v>
       </c>
       <c r="L82" t="n">
-        <v>93.13</v>
+        <v>84.08</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:06:52</t>
+          <t>08:46:26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.59</v>
+        <v>2.63</v>
       </c>
       <c r="F83" t="n">
-        <v>10.7</v>
+        <v>6.99</v>
       </c>
       <c r="G83" t="n">
-        <v>302.1</v>
+        <v>281.1</v>
       </c>
       <c r="H83" t="n">
-        <v>77.2</v>
+        <v>63.3</v>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>129.89</v>
+        <v>-43.86</v>
       </c>
       <c r="K83" t="n">
-        <v>-133.59</v>
+        <v>-103.77</v>
       </c>
       <c r="L83" t="n">
-        <v>186.32</v>
+        <v>112.66</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:08:11</t>
+          <t>08:48:31</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="F84" t="n">
-        <v>10.7</v>
+        <v>5.37</v>
       </c>
       <c r="G84" t="n">
-        <v>300.6</v>
+        <v>318.8</v>
       </c>
       <c r="H84" t="n">
-        <v>89.40000000000001</v>
+        <v>37.5</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>146.66</v>
+        <v>20.4</v>
       </c>
       <c r="K84" t="n">
-        <v>50.93</v>
+        <v>244.19</v>
       </c>
       <c r="L84" t="n">
-        <v>155.25</v>
+        <v>245.04</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:10:07</t>
+          <t>08:49:54</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.21</v>
+        <v>3.4</v>
       </c>
       <c r="F85" t="n">
-        <v>7.72</v>
+        <v>10.7</v>
       </c>
       <c r="G85" t="n">
-        <v>295.6</v>
+        <v>294.7</v>
       </c>
       <c r="H85" t="n">
-        <v>68.09999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-14.44</v>
+        <v>13.45</v>
       </c>
       <c r="K85" t="n">
-        <v>-84.39</v>
+        <v>159.38</v>
       </c>
       <c r="L85" t="n">
-        <v>85.61</v>
+        <v>159.95</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:15:45</t>
+          <t>08:55:41</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
-        <v>10.66</v>
+        <v>10.7</v>
       </c>
       <c r="G86" t="n">
-        <v>288.2</v>
+        <v>293.2</v>
       </c>
       <c r="H86" t="n">
-        <v>25.6</v>
+        <v>28</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J86" t="n">
-        <v>-152.91</v>
+        <v>-227.01</v>
       </c>
       <c r="K86" t="n">
-        <v>-144.02</v>
+        <v>48.36</v>
       </c>
       <c r="L86" t="n">
-        <v>210.05</v>
+        <v>232.11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:17:31</t>
+          <t>08:57:40</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="F87" t="n">
-        <v>10.7</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>284.5</v>
+        <v>279.7</v>
       </c>
       <c r="H87" t="n">
-        <v>93.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-94.65000000000001</v>
+        <v>213.49</v>
       </c>
       <c r="K87" t="n">
-        <v>165.55</v>
+        <v>29.04</v>
       </c>
       <c r="L87" t="n">
-        <v>190.7</v>
+        <v>215.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:19:16</t>
+          <t>08:58:57</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="F88" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="G88" t="n">
-        <v>289.8</v>
+        <v>292.1</v>
       </c>
       <c r="H88" t="n">
-        <v>58</v>
+        <v>53.6</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-107.33</v>
+        <v>-228.44</v>
       </c>
       <c r="K88" t="n">
-        <v>-53.88</v>
+        <v>130.97</v>
       </c>
       <c r="L88" t="n">
-        <v>120.09</v>
+        <v>263.32</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-09.xlsx
+++ b/output/2025-08-09.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>17.82</v>
+        <v>19.5</v>
       </c>
       <c r="K14" t="n">
-        <v>55.31</v>
+        <v>60.52</v>
       </c>
       <c r="L14" t="n">
-        <v>58.11</v>
+        <v>63.58</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>34.66</v>
+        <v>40.86</v>
       </c>
       <c r="K15" t="n">
-        <v>-32.68</v>
+        <v>-38.53</v>
       </c>
       <c r="L15" t="n">
-        <v>47.64</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-45.07</v>
+        <v>-47.62</v>
       </c>
       <c r="K16" t="n">
-        <v>52.21</v>
+        <v>55.16</v>
       </c>
       <c r="L16" t="n">
-        <v>68.97</v>
+        <v>72.87</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>78.47</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-59.01</v>
+        <v>-65.12</v>
       </c>
       <c r="L17" t="n">
-        <v>98.18000000000001</v>
+        <v>108.35</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>65.03</v>
+        <v>76.86</v>
       </c>
       <c r="K18" t="n">
-        <v>19.57</v>
+        <v>23.12</v>
       </c>
       <c r="L18" t="n">
-        <v>67.91</v>
+        <v>80.26000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-49.59</v>
+        <v>-60.02</v>
       </c>
       <c r="K19" t="n">
-        <v>-37.58</v>
+        <v>-45.48</v>
       </c>
       <c r="L19" t="n">
-        <v>62.22</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-42.78</v>
+        <v>-54.08</v>
       </c>
       <c r="K20" t="n">
-        <v>80.7</v>
+        <v>102.01</v>
       </c>
       <c r="L20" t="n">
-        <v>91.33</v>
+        <v>115.46</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>105.55</v>
+        <v>124.02</v>
       </c>
       <c r="K21" t="n">
-        <v>-46.07</v>
+        <v>-54.13</v>
       </c>
       <c r="L21" t="n">
-        <v>115.16</v>
+        <v>135.32</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-125.89</v>
+        <v>-147.75</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.82</v>
+        <v>-13.87</v>
       </c>
       <c r="L22" t="n">
-        <v>126.44</v>
+        <v>148.4</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>158.9</v>
+        <v>186.53</v>
       </c>
       <c r="K23" t="n">
-        <v>-110.52</v>
+        <v>-129.74</v>
       </c>
       <c r="L23" t="n">
-        <v>193.56</v>
+        <v>227.21</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>102.16</v>
+        <v>125.93</v>
       </c>
       <c r="K24" t="n">
-        <v>-83.03</v>
+        <v>-102.35</v>
       </c>
       <c r="L24" t="n">
-        <v>131.65</v>
+        <v>162.28</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-73.83</v>
+        <v>-92.84</v>
       </c>
       <c r="K25" t="n">
-        <v>-108.25</v>
+        <v>-136.12</v>
       </c>
       <c r="L25" t="n">
-        <v>131.03</v>
+        <v>164.77</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>112.43</v>
+        <v>149.65</v>
       </c>
       <c r="K26" t="n">
-        <v>-143.59</v>
+        <v>-191.12</v>
       </c>
       <c r="L26" t="n">
-        <v>182.37</v>
+        <v>242.74</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>203.92</v>
+        <v>247.49</v>
       </c>
       <c r="K27" t="n">
-        <v>102.17</v>
+        <v>124</v>
       </c>
       <c r="L27" t="n">
-        <v>228.08</v>
+        <v>276.81</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-60.91</v>
+        <v>-73.89</v>
       </c>
       <c r="K28" t="n">
-        <v>270.77</v>
+        <v>328.45</v>
       </c>
       <c r="L28" t="n">
-        <v>277.53</v>
+        <v>336.66</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>10.28</v>
+        <v>11.62</v>
       </c>
       <c r="K29" t="n">
-        <v>53.43</v>
+        <v>60.39</v>
       </c>
       <c r="L29" t="n">
-        <v>54.41</v>
+        <v>61.49</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>35.91</v>
+        <v>40.72</v>
       </c>
       <c r="K30" t="n">
-        <v>-41.78</v>
+        <v>-47.37</v>
       </c>
       <c r="L30" t="n">
-        <v>55.09</v>
+        <v>62.47</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-39.87</v>
+        <v>-42.4</v>
       </c>
       <c r="K31" t="n">
-        <v>-70.94</v>
+        <v>-75.44</v>
       </c>
       <c r="L31" t="n">
-        <v>81.38</v>
+        <v>86.54000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-27.07</v>
+        <v>-31.76</v>
       </c>
       <c r="K32" t="n">
-        <v>-72.14</v>
+        <v>-84.63</v>
       </c>
       <c r="L32" t="n">
-        <v>77.05</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-74.06999999999999</v>
+        <v>-81.2</v>
       </c>
       <c r="K33" t="n">
-        <v>70.31999999999999</v>
+        <v>77.09</v>
       </c>
       <c r="L33" t="n">
-        <v>102.14</v>
+        <v>111.96</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-42.12</v>
+        <v>-47.25</v>
       </c>
       <c r="K34" t="n">
-        <v>61.48</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>74.52</v>
+        <v>83.59</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-141.43</v>
+        <v>-159.31</v>
       </c>
       <c r="K35" t="n">
-        <v>-64.31</v>
+        <v>-72.44</v>
       </c>
       <c r="L35" t="n">
-        <v>155.37</v>
+        <v>175.01</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-27.37</v>
+        <v>-30.44</v>
       </c>
       <c r="K36" t="n">
-        <v>149.29</v>
+        <v>166.06</v>
       </c>
       <c r="L36" t="n">
-        <v>151.78</v>
+        <v>168.83</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>56.15</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>73.61</v>
+        <v>92.23</v>
       </c>
       <c r="L37" t="n">
-        <v>92.58</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>136.7</v>
+        <v>173.5</v>
       </c>
       <c r="K38" t="n">
-        <v>6.75</v>
+        <v>8.57</v>
       </c>
       <c r="L38" t="n">
-        <v>136.87</v>
+        <v>173.71</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-142.66</v>
+        <v>-172.38</v>
       </c>
       <c r="K39" t="n">
-        <v>52.07</v>
+        <v>62.92</v>
       </c>
       <c r="L39" t="n">
-        <v>151.86</v>
+        <v>183.5</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-112.41</v>
+        <v>-150.22</v>
       </c>
       <c r="K40" t="n">
-        <v>-18.63</v>
+        <v>-24.9</v>
       </c>
       <c r="L40" t="n">
-        <v>113.95</v>
+        <v>152.26</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>290.33</v>
+        <v>356.04</v>
       </c>
       <c r="K41" t="n">
-        <v>29.66</v>
+        <v>36.37</v>
       </c>
       <c r="L41" t="n">
-        <v>291.84</v>
+        <v>357.89</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-87.65000000000001</v>
+        <v>-115.08</v>
       </c>
       <c r="K42" t="n">
-        <v>-156.04</v>
+        <v>-204.88</v>
       </c>
       <c r="L42" t="n">
-        <v>178.97</v>
+        <v>234.99</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-164.46</v>
+        <v>-207.38</v>
       </c>
       <c r="K43" t="n">
-        <v>176.54</v>
+        <v>222.62</v>
       </c>
       <c r="L43" t="n">
-        <v>241.27</v>
+        <v>304.25</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>83.73999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.02</v>
+        <v>-1.08</v>
       </c>
       <c r="L44" t="n">
-        <v>83.73999999999999</v>
+        <v>88.70999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>30.21</v>
+        <v>34.47</v>
       </c>
       <c r="K45" t="n">
-        <v>-37.73</v>
+        <v>-43.05</v>
       </c>
       <c r="L45" t="n">
-        <v>48.33</v>
+        <v>55.14</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-75.22</v>
+        <v>-78.72</v>
       </c>
       <c r="K46" t="n">
-        <v>46.25</v>
+        <v>48.4</v>
       </c>
       <c r="L46" t="n">
-        <v>88.3</v>
+        <v>92.41</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-71.87</v>
+        <v>-76.65000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-84.03</v>
+        <v>-89.62</v>
       </c>
       <c r="L47" t="n">
-        <v>110.58</v>
+        <v>117.93</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-51.95</v>
+        <v>-64.84999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>31.96</v>
+        <v>39.89</v>
       </c>
       <c r="L48" t="n">
-        <v>61</v>
+        <v>76.14</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>35.64</v>
+        <v>41.97</v>
       </c>
       <c r="K49" t="n">
-        <v>-79.09</v>
+        <v>-93.13</v>
       </c>
       <c r="L49" t="n">
-        <v>86.75</v>
+        <v>102.15</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>63.43</v>
+        <v>78.31</v>
       </c>
       <c r="K50" t="n">
-        <v>73.53</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>97.11</v>
+        <v>119.9</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>6.42</v>
+        <v>7.18</v>
       </c>
       <c r="K51" t="n">
-        <v>153.53</v>
+        <v>171.69</v>
       </c>
       <c r="L51" t="n">
-        <v>153.66</v>
+        <v>171.84</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-54.48</v>
+        <v>-69.03</v>
       </c>
       <c r="K52" t="n">
-        <v>-75.47</v>
+        <v>-95.62</v>
       </c>
       <c r="L52" t="n">
-        <v>93.08</v>
+        <v>117.93</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>3.35</v>
+        <v>4.25</v>
       </c>
       <c r="K53" t="n">
-        <v>-142.56</v>
+        <v>-180.95</v>
       </c>
       <c r="L53" t="n">
-        <v>142.6</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>113.2</v>
+        <v>139.48</v>
       </c>
       <c r="K54" t="n">
-        <v>-98.31999999999999</v>
+        <v>-121.15</v>
       </c>
       <c r="L54" t="n">
-        <v>149.94</v>
+        <v>184.74</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-184.32</v>
+        <v>-212.42</v>
       </c>
       <c r="K55" t="n">
-        <v>61.33</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>194.26</v>
+        <v>223.87</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>71.17</v>
+        <v>85.17</v>
       </c>
       <c r="K56" t="n">
-        <v>282.34</v>
+        <v>337.9</v>
       </c>
       <c r="L56" t="n">
-        <v>291.18</v>
+        <v>348.47</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>221.5</v>
+        <v>286.74</v>
       </c>
       <c r="K57" t="n">
-        <v>85.69</v>
+        <v>110.93</v>
       </c>
       <c r="L57" t="n">
-        <v>237.49</v>
+        <v>307.45</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-131.74</v>
+        <v>-163.09</v>
       </c>
       <c r="K58" t="n">
-        <v>-213.76</v>
+        <v>-264.65</v>
       </c>
       <c r="L58" t="n">
-        <v>251.1</v>
+        <v>310.87</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-49.92</v>
+        <v>-57.07</v>
       </c>
       <c r="K59" t="n">
-        <v>-13.47</v>
+        <v>-15.41</v>
       </c>
       <c r="L59" t="n">
-        <v>51.7</v>
+        <v>59.11</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.83</v>
+        <v>-10.14</v>
       </c>
       <c r="K60" t="n">
-        <v>79.25</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>79.86</v>
+        <v>82.39</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>64.25</v>
+        <v>72.63</v>
       </c>
       <c r="K61" t="n">
-        <v>2.57</v>
+        <v>2.91</v>
       </c>
       <c r="L61" t="n">
-        <v>64.3</v>
+        <v>72.69</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>65.12</v>
+        <v>77.45</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.96</v>
+        <v>-2.33</v>
       </c>
       <c r="L62" t="n">
-        <v>65.15000000000001</v>
+        <v>77.48</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-92.08</v>
+        <v>-102.55</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.25</v>
+        <v>-1.39</v>
       </c>
       <c r="L63" t="n">
-        <v>92.09</v>
+        <v>102.56</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>102.43</v>
+        <v>109.58</v>
       </c>
       <c r="K64" t="n">
-        <v>-42.53</v>
+        <v>-45.5</v>
       </c>
       <c r="L64" t="n">
-        <v>110.91</v>
+        <v>118.65</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>10.49</v>
+        <v>13.5</v>
       </c>
       <c r="K65" t="n">
-        <v>-12.14</v>
+        <v>-15.62</v>
       </c>
       <c r="L65" t="n">
-        <v>16.04</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-138.14</v>
+        <v>-156.91</v>
       </c>
       <c r="K66" t="n">
-        <v>-60.61</v>
+        <v>-68.84999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>150.86</v>
+        <v>171.35</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-110.46</v>
+        <v>-132.59</v>
       </c>
       <c r="K67" t="n">
-        <v>43.83</v>
+        <v>52.61</v>
       </c>
       <c r="L67" t="n">
-        <v>118.83</v>
+        <v>142.64</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-84.59999999999999</v>
+        <v>-114.45</v>
       </c>
       <c r="K68" t="n">
-        <v>-101.05</v>
+        <v>-136.7</v>
       </c>
       <c r="L68" t="n">
-        <v>131.78</v>
+        <v>178.28</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-148.06</v>
+        <v>-174.43</v>
       </c>
       <c r="K69" t="n">
-        <v>-88.53</v>
+        <v>-104.29</v>
       </c>
       <c r="L69" t="n">
-        <v>172.51</v>
+        <v>203.23</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.51</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-7.59</v>
+        <v>-9.74</v>
       </c>
       <c r="L70" t="n">
-        <v>9.99</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>182.77</v>
+        <v>242.56</v>
       </c>
       <c r="K71" t="n">
-        <v>80.63</v>
+        <v>107</v>
       </c>
       <c r="L71" t="n">
-        <v>199.76</v>
+        <v>265.11</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-125.91</v>
+        <v>-156.24</v>
       </c>
       <c r="K72" t="n">
-        <v>222.93</v>
+        <v>276.63</v>
       </c>
       <c r="L72" t="n">
-        <v>256.03</v>
+        <v>317.7</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>6.36</v>
+        <v>7.96</v>
       </c>
       <c r="K73" t="n">
-        <v>257.32</v>
+        <v>322.15</v>
       </c>
       <c r="L73" t="n">
-        <v>257.4</v>
+        <v>322.25</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-34.08</v>
+        <v>-40.57</v>
       </c>
       <c r="K74" t="n">
-        <v>-46.31</v>
+        <v>-55.12</v>
       </c>
       <c r="L74" t="n">
-        <v>57.5</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-31.36</v>
+        <v>-35.87</v>
       </c>
       <c r="K75" t="n">
-        <v>44.79</v>
+        <v>51.23</v>
       </c>
       <c r="L75" t="n">
-        <v>54.68</v>
+        <v>62.54</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-47.43</v>
+        <v>-59.29</v>
       </c>
       <c r="K76" t="n">
-        <v>26.34</v>
+        <v>32.92</v>
       </c>
       <c r="L76" t="n">
-        <v>54.25</v>
+        <v>67.81999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>31.61</v>
+        <v>35.8</v>
       </c>
       <c r="K77" t="n">
-        <v>85.64</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>91.28</v>
+        <v>103.39</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>62.71</v>
+        <v>78.27</v>
       </c>
       <c r="K78" t="n">
-        <v>-8.44</v>
+        <v>-10.53</v>
       </c>
       <c r="L78" t="n">
-        <v>63.28</v>
+        <v>78.98</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>20.81</v>
+        <v>22.47</v>
       </c>
       <c r="K79" t="n">
-        <v>96.37</v>
+        <v>104.06</v>
       </c>
       <c r="L79" t="n">
-        <v>98.59</v>
+        <v>106.46</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>43.63</v>
+        <v>54.01</v>
       </c>
       <c r="K80" t="n">
-        <v>-86.98</v>
+        <v>-107.68</v>
       </c>
       <c r="L80" t="n">
-        <v>97.31</v>
+        <v>120.46</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>55.11</v>
+        <v>68.36</v>
       </c>
       <c r="K81" t="n">
-        <v>103.6</v>
+        <v>128.53</v>
       </c>
       <c r="L81" t="n">
-        <v>117.35</v>
+        <v>145.58</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-50.88</v>
+        <v>-65.84</v>
       </c>
       <c r="K82" t="n">
-        <v>79.66</v>
+        <v>103.09</v>
       </c>
       <c r="L82" t="n">
-        <v>94.52</v>
+        <v>122.32</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>210.45</v>
+        <v>245.98</v>
       </c>
       <c r="K83" t="n">
-        <v>-12.25</v>
+        <v>-14.31</v>
       </c>
       <c r="L83" t="n">
-        <v>210.8</v>
+        <v>246.4</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>40.36</v>
+        <v>48.16</v>
       </c>
       <c r="K84" t="n">
-        <v>137.09</v>
+        <v>163.6</v>
       </c>
       <c r="L84" t="n">
-        <v>142.91</v>
+        <v>170.54</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-55.82</v>
+        <v>-69.68000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>142.24</v>
+        <v>177.56</v>
       </c>
       <c r="L85" t="n">
-        <v>152.8</v>
+        <v>190.74</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>145.89</v>
+        <v>202.3</v>
       </c>
       <c r="K86" t="n">
-        <v>-58.12</v>
+        <v>-80.59</v>
       </c>
       <c r="L86" t="n">
-        <v>157.04</v>
+        <v>217.76</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-88.26000000000001</v>
+        <v>-105.3</v>
       </c>
       <c r="K87" t="n">
-        <v>283.02</v>
+        <v>337.67</v>
       </c>
       <c r="L87" t="n">
-        <v>296.46</v>
+        <v>353.71</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-222.87</v>
+        <v>-283.28</v>
       </c>
       <c r="K88" t="n">
-        <v>66.26000000000001</v>
+        <v>84.22</v>
       </c>
       <c r="L88" t="n">
-        <v>232.51</v>
+        <v>295.54</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-09.xlsx
+++ b/output/2025-08-09.xlsx
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>41.97</v>
+        <v>42.7</v>
       </c>
       <c r="K49" t="n">
-        <v>-93.13</v>
+        <v>-94.76000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>102.15</v>
+        <v>103.94</v>
       </c>
     </row>
     <row r="50">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-59.29</v>
+        <v>-62.05</v>
       </c>
       <c r="K76" t="n">
-        <v>32.92</v>
+        <v>34.46</v>
       </c>
       <c r="L76" t="n">
-        <v>67.81999999999999</v>
+        <v>70.98</v>
       </c>
     </row>
     <row r="77">
